--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ECD2511-B7A2-4002-A2D9-31006D36A507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFF569B4-4EA1-43EB-9CB3-03EB79740928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4395" yWindow="1590" windowWidth="21600" windowHeight="13665" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
+    <workbookView xWindow="3915" yWindow="5895" windowWidth="11160" windowHeight="6315" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
   <sheets>
-    <sheet name="코멘트" sheetId="1" r:id="rId1"/>
+    <sheet name="Summary" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="20">
   <si>
     <t>탭</t>
   </si>
@@ -48,7 +48,7 @@
     <t>구분</t>
   </si>
   <si>
-    <t>코멘트</t>
+    <t>Summary</t>
   </si>
   <si>
     <t>Humax합계</t>
@@ -87,10 +87,6 @@
     <t>HUMAX(공통)</t>
   </si>
   <si>
-    <t>- 누계 실적 3,666 / 예산 3,080, 집행률 119%(+587)로 예산을 초과했습니다.
-- Staff부문 +466(급여 +217), HBR +124 초과가 주원인으로, 감소 추세 관리가 필요합니다.</t>
-  </si>
-  <si>
     <t>건물</t>
   </si>
   <si>
@@ -98,10 +94,50 @@
 - 1~3월 평균 278 → 4~6월 평균 126으로 사옥 이전에 따른 계단식 감소가 확인됩니다.</t>
   </si>
   <si>
-    <t>- 누계 실적 2,916 / 예산 3,252, 집행률 90%(-336)로 예산에 미달합니다.
+    <r>
+      <t xml:space="preserve">- 누계 실적 2,916 / 예산 3,252, 집행률 90%(-336)로 예산에 미달합니다.
 - Media그룹 -454(외주개발용역비 -526)가 주원인이며, 월 배부액은 400~570에서 등락해 아직 감소 추세는 아닙니다.
-- 4월, 5월 트렌드 왜곡: STB License Fee/Nagra 84백만 4월 기표 후 5월 reverse (선급비용 조정 시기 오류)</t>
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- 4월, 5월 트렌드 왜곡: STB License Fee/Nagra 84백만 4월 기표 후 5월 reverse (선급비용 조정 시기 오류)</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">- 누계 실적 3,666 / 예산 3,080, 집행률 119%(+587)로 예산을 초과했습니다.
+- Staff부문 +466(급여 +217), HBR +124 초과가 주원인으로, 감소 추세 관리가 필요합니다.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- 1월, 5월 일회성 집행으로 배부액 상승: 26년 외부감사 착수금 200백만(1월), 15차 주식선택권 취소 216백만(5월)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>월별 배부액 추이</t>
+  </si>
+  <si>
+    <t>- 1월, 5월 일회성 집행: 26년 외부감사 착수금 200백만(1월), 15차 주식선택권 취소 216백만(5월). 제외 시 월 배부액 470 내외로 평탄합니다.</t>
   </si>
 </sst>
 </file>
@@ -513,7 +549,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05630F61-30FB-4CF7-B3FF-D0B93533C1C1}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.625" customWidth="1"/>
@@ -583,10 +619,10 @@
         <v>12</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="33" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="66" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>11</v>
       </c>
@@ -596,8 +632,8 @@
       <c r="C6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>14</v>
+      <c r="D6" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="33" x14ac:dyDescent="0.3">
@@ -608,10 +644,22 @@
         <v>7</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>16</v>
+    </row>
+    <row r="8" spans="1:4" ht="33" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFF569B4-4EA1-43EB-9CB3-03EB79740928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E6F98C2-D76B-4DC0-8E40-2B9119FE148F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3915" yWindow="5895" windowWidth="11160" windowHeight="6315" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
+    <workbookView xWindow="28680" yWindow="-885" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -54,30 +54,9 @@
     <t>Humax합계</t>
   </si>
   <si>
-    <t>6월</t>
-  </si>
-  <si>
-    <t>- 당월 집행률은 예산 범위 내에서 안정적으로 유지되고 있습니다.
-- 본사·법인 간 당월 집행 추이에 특이 편차는 없습니다.
-- 다음 달에는 계절적 요인으로 지급수수료 증가가 예상됩니다.</t>
-  </si>
-  <si>
-    <t>6월 누계</t>
-  </si>
-  <si>
-    <t>- 누계 집행률은 연간 계획 대비 정상 범위에서 관리되고 있습니다.
-- 본사가 누계 집행의 대부분을 차지하고 있습니다.
-- EVCS(해외) 배부 비중이 누계 기준으로 가장 크게 나타났습니다.</t>
-  </si>
-  <si>
     <t>EVCS사업부</t>
   </si>
   <si>
-    <t>- EVCS(국내) 배부 비용은 축소 기조에 맞춰 매월 감소 여부를 점검하고 있습니다.
-- EVCS(해외)는 연간 예산 대비 누계 집행률로 진척도를 관리하고 있습니다.
-- 비용 규모는 인건비 비중이 가장 크며, 인력 운영 계획에 따라 변동됩니다.</t>
-  </si>
-  <si>
     <t>Humax합계_상세</t>
   </si>
   <si>
@@ -90,54 +69,46 @@
     <t>건물</t>
   </si>
   <si>
-    <t>- 누계 실적 1,211 / 예산 1,810, 집행률 67%(-600)로 예산을 크게 밑돕니다.
-- 1~3월 평균 278 → 4~6월 평균 126으로 사옥 이전에 따른 계단식 감소가 확인됩니다.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">- 누계 실적 2,916 / 예산 3,252, 집행률 90%(-336)로 예산에 미달합니다.
-- Media그룹 -454(외주개발용역비 -526)가 주원인이며, 월 배부액은 400~570에서 등락해 아직 감소 추세는 아닙니다.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>- 4월, 5월 트렌드 왜곡: STB License Fee/Nagra 84백만 4월 기표 후 5월 reverse (선급비용 조정 시기 오류)</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">- 누계 실적 3,666 / 예산 3,080, 집행률 119%(+587)로 예산을 초과했습니다.
-- Staff부문 +466(급여 +217), HBR +124 초과가 주원인으로, 감소 추세 관리가 필요합니다.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>- 1월, 5월 일회성 집행으로 배부액 상승: 26년 외부감사 착수금 200백만(1월), 15차 주식선택권 취소 216백만(5월)</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>월별 배부액 추이</t>
   </si>
   <si>
-    <t>- 1월, 5월 일회성 집행: 26년 외부감사 착수금 200백만(1월), 15차 주식선택권 취소 216백만(5월). 제외 시 월 배부액 470 내외로 평탄합니다.</t>
+    <t>5월</t>
+  </si>
+  <si>
+    <t>- 당월 실적 2,444 / 예산 2,397, 집행률 102%(+47)로 예산 수준에서 집행되었습니다.
+- 본사 1,804/1,805(100%)는 계획대로이나, 법인이 640/592(108%, +48)로 초과했습니다.
+- HUMAX(공통)이 716으로 1~4월 평균 602를 웃돌았고, 건물은 121로 사옥 이전 후 낮은 수준을 유지합니다.</t>
+  </si>
+  <si>
+    <t>5월 누계</t>
+  </si>
+  <si>
+    <t>- 누계 실적 6,161(국내 1,612 / 해외 4,549), 연간 예산 14,637 대비 42% 집행으로 5개월 경과 진도(42%)에 부합합니다.
+- 국내는 46%로 진도를 앞서고 월 배부액도 269→343으로 늘어, 축소 기조와는 반대 방향입니다.
+- 해외는 41%로 진도에 부합하며, 비용의 56%(3,439)가 인건비로 인력 운영 계획에 따라 변동됩니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 2,381 / 예산 2,806, 집행률 85%(-425)로 예산에 미달합니다.
+- Media그룹 -469(외주개발용역비 -525)가 주원인이며, 왜곡 보정 후 월 441~493으로 평탄해 Closing에 따른 감소 추세는 아직 확인되지 않습니다.
+- 4월, 5월 트렌드 왜곡: STB License Fee/Nagra 84백만 4월 기표 후 5월 reverse (선급비용 조정 시기 오류)</t>
+  </si>
+  <si>
+    <t>- 누계 실적 3,125 / 예산 2,573, 집행률 121%(+552)로 예산을 초과했습니다.
+- Staff부문 +516이 대부분이며, 급여 +208·특허처리비 +106·지급수수료 +100 초과가 주원인입니다.
+- 1월, 5월 일회성 집행으로 배부액 상승: 26년 외부감사 착수금 200백만(1월), 15차 주식선택권 취소 216백만(5월)</t>
+  </si>
+  <si>
+    <t>- 누계 실적 1,089 / 예산 1,505, 집행률 72%(-416)로 예산을 크게 밑돕니다.
+- 감가상각비 -326, 수도광열비 -168 미달이 주원인입니다(임차료는 +91 초과).
+- 1~3월 평균 278 → 4~5월 평균 128로 사옥 이전에 따른 계단식 감소가 확인됩니다.</t>
+  </si>
+  <si>
+    <t>- 1월, 5월 일회성 집행: 26년 외부감사 착수금 200백만(1월), 15차 주식선택권 취소 216백만(5월). 제외 시 HUMAX(공통) 월 배부액은 467~598 범위입니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 13,012 / 예산 13,466, 집행률 97%(-454)로 예산 내 집행 중입니다.
+- 본사 9,318/10,059(93%, -741)는 미달, 법인 3,694/3,407(108%, +287)은 초과로 방향이 엇갈립니다.
+- 항목별로는 HUMAX(공통) 121%(+552)·EVCS(국내) 110%(+142)가 초과, 건물 72%·STB 85%·EVCS(해외) 92%가 미달입니다.</t>
   </si>
 </sst>
 </file>
@@ -213,7 +184,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -230,9 +201,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -554,7 +522,7 @@
   <cols>
     <col min="1" max="1" width="18.625" customWidth="1"/>
     <col min="2" max="2" width="12.625" customWidth="1"/>
-    <col min="3" max="3" width="16.625" customWidth="1"/>
+    <col min="3" max="3" width="18.625" customWidth="1"/>
     <col min="4" max="4" width="95.625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -577,89 +545,89 @@
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="66" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="66" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="66" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="66" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="4" t="s">
+    <row r="7" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="C7" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="33" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="33" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>18</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E6F98C2-D76B-4DC0-8E40-2B9119FE148F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F269C700-E516-4DCE-882B-581C113FDF2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-885" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
+    <workbookView xWindow="20415" yWindow="5835" windowWidth="11160" windowHeight="6315" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="28">
   <si>
     <t>탭</t>
   </si>
@@ -109,6 +109,42 @@
     <t>- 누계 실적 13,012 / 예산 13,466, 집행률 97%(-454)로 예산 내 집행 중입니다.
 - 본사 9,318/10,059(93%, -741)는 미달, 법인 3,694/3,407(108%, +287)은 초과로 방향이 엇갈립니다.
 - 항목별로는 HUMAX(공통) 121%(+552)·EVCS(국내) 110%(+142)가 초과, 건물 72%·STB 85%·EVCS(해외) 92%가 미달입니다.</t>
+  </si>
+  <si>
+    <t>6월</t>
+  </si>
+  <si>
+    <t>- 당월 실적 2,537 / 예산 2,526, 집행률 100%(+11)로 예산에 부합합니다.
+- 본사 1,747/1,923(91%, -176)은 미달, 법인 790/603(131%, +187)은 초과로 방향이 엇갈립니다.
+- HUMAX(공통)은 541로 5월(716) 대비 -175 낮아졌고, STB는 536으로 보정 후 1~5월 평균 476을 웃돌았습니다.</t>
+  </si>
+  <si>
+    <t>6월 누계</t>
+  </si>
+  <si>
+    <t>- 누계 실적 15,549 / 예산 15,992, 집행률 97%(-443)로 예산 내 집행 중입니다.
+- 본사 11,065/11,982(92%, -917)는 미달, 법인 4,484/4,010(112%, +474)은 초과로 방향이 엇갈립니다.
+- 항목별로는 HUMAX(공통) 119%(+586)·EVCS(국내) 108%(+147)가 초과, 건물 67%·STB 90%·EVCS(해외) 94%가 미달입니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 7,440(국내 1,973 / 해외 5,468), 연간 예산 14,637 대비 51% 집행으로 6개월 경과 진도(50%)에 부합합니다.
+- 국내는 57%로 진도를 앞서고 월 배부액도 269→361로 늘어, 축소 기조와는 반대 방향입니다.
+- 해외는 49%로 진도에 부합하며, 비용의 56%(4,130)가 인건비로 인력 운영 계획에 따라 변동됩니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 2,916 / 예산 3,252, 집행률 90%(-336)로 예산에 미달합니다.
+- Media그룹 -454(외주개발용역비 -526)가 주원인이며, 왜곡 보정 후 월 441~536으로 Closing에 따른 감소 추세는 아직 확인되지 않습니다.
+- 4월, 5월 트렌드 왜곡: STB License Fee/Nagra 84백만 4월 기표 후 5월 reverse (선급비용 조정 시기 오류)</t>
+  </si>
+  <si>
+    <t>- 누계 실적 3,666 / 예산 3,080, 집행률 119%(+586)로 예산을 초과했습니다.
+- Staff부문 +466(급여 +217, 특허처리비 +105), HBR +124 초과가 주원인으로, 감소 추세 관리가 필요합니다.
+- 1월, 5월 일회성 집행으로 배부액 상승: 26년 외부감사 착수금 200백만(1월), 15차 주식선택권 취소 216백만(5월)</t>
+  </si>
+  <si>
+    <t>- 누계 실적 1,211 / 예산 1,810, 집행률 67%(-599)로 예산을 크게 밑돕니다.
+- 감가상각비 -489, 수도광열비 -254 미달이 주원인입니다(임차료는 +136 초과).
+- 1~3월 평균 278 → 4~6월 평균 126으로 사옥 이전에 따른 계단식 감소가 확인됩니다.</t>
   </si>
 </sst>
 </file>
@@ -517,7 +553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05630F61-30FB-4CF7-B3FF-D0B93533C1C1}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.625" customWidth="1"/>
@@ -618,15 +654,93 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="33" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="66" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="66" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="4"/>
+      <c r="D10" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="66" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4" t="s">
+      <c r="B11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="33" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D14" s="5" t="s">
         <v>18</v>
       </c>
     </row>

--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F269C700-E516-4DCE-882B-581C113FDF2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A10900B-872E-4407-BDDC-D84968CA32F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20415" yWindow="5835" windowWidth="11160" windowHeight="6315" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
+    <workbookView xWindow="28680" yWindow="-885" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="60">
   <si>
     <t>탭</t>
   </si>
@@ -145,6 +145,144 @@
     <t>- 누계 실적 1,211 / 예산 1,810, 집행률 67%(-599)로 예산을 크게 밑돕니다.
 - 감가상각비 -489, 수도광열비 -254 미달이 주원인입니다(임차료는 +136 초과).
 - 1~3월 평균 278 → 4~6월 평균 126으로 사옥 이전에 따른 계단식 감소가 확인됩니다.</t>
+  </si>
+  <si>
+    <t>1월</t>
+  </si>
+  <si>
+    <t>- 당월 실적 2,818 / 예산 3,215, 집행률 88%(-397)로 예산에 미달합니다.
+- 본사 2,020/2,434(83%, -414)가 미달을 주도했고, 법인은 798/781(102%, +17)로 예산 수준입니다.
+- STB가 예산 1,014 대비 493(49%)에 그쳤고, HUMAX(공통)은 예산 622에 실적 760으로 외부감사 착수금 200이 반영됐습니다.</t>
+  </si>
+  <si>
+    <t>1월 누계</t>
+  </si>
+  <si>
+    <t>- 누계 실적 2,818 / 예산 3,215, 집행률 88%(-397)로 예산 내 집행 중입니다.
+- 본사 2,020/2,434(83%, -414)는 미달, 법인 798/781(102%, +17)은 예산 수준입니다.
+- 항목별로는 STB 49%(-521) 미달과 HUMAX(공통) 122%(+138) 초과가 차이의 대부분을 만듭니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 1,233(국내 269 / 해외 963), 연간 예산 14,637 대비 8% 집행으로 1개월 경과 진도(8%)에 부합합니다.
+- 국내 8%·해외 9%로 아직 진도 차이는 크지 않습니다.
+- 비용의 58%(720)가 인건비로 인력 운영 계획에 따라 변동됩니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 493 / 예산 1,014, 집행률 49%(-521)로 예산을 크게 밑돕니다.
+- Media그룹 -533(외주개발용역비 -509)이 주원인으로, 연초 외주개발 집행이 계획보다 늦습니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 760 / 예산 622, 집행률 122%(+138)로 예산을 초과했습니다.
+- Staff부문 +138이 대부분이며, 특허처리비 +64 초과가 주원인입니다.
+- 1월 일회성 집행으로 배부액 상승: 26년 외부감사 착수금 200백만(1월)</t>
+  </si>
+  <si>
+    <t>- 누계 실적 272 / 예산 299, 집행률 91%(-27)로 예산에 소폭 미달합니다.
+- Staff부문 -26으로 차이가 작아, 사옥 이전에 따른 감소는 아직 나타나지 않았습니다.</t>
+  </si>
+  <si>
+    <t>2월</t>
+  </si>
+  <si>
+    <t>- 당월 실적 2,633 / 예산 2,566, 집행률 103%(+67)로 예산을 소폭 초과했습니다.
+- 본사 1,752/1,839(95%, -87)는 미달이나, 법인이 881/727(121%, +154)로 초과했습니다.
+- HUMAX(공통)이 467로 1월(760) 대비 -293 낮아졌습니다(1월 외부감사 착수금 200 소멸).</t>
+  </si>
+  <si>
+    <t>2월 누계</t>
+  </si>
+  <si>
+    <t>- 누계 실적 5,451 / 예산 5,781, 집행률 94%(-330)로 예산 내 집행 중입니다.
+- 본사 3,772/4,273(88%, -501)는 미달, 법인 1,679/1,508(111%, +171)은 초과로 방향이 엇갈립니다.
+- 항목별로는 HUMAX(공통) 116%(+170) 초과와 STB 66%(-499) 미달이 차이의 대부분을 만듭니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 2,566(국내 583 / 해외 1,983), 연간 예산 14,637 대비 18% 집행으로 2개월 경과 진도(17%)에 부합합니다.
+- 국내 17%·해외 18%로 진도와 나란히 갑니다.
+- 비용의 58%(1,481)가 인건비로 인력 운영 계획에 따라 변동됩니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 975 / 예산 1,474, 집행률 66%(-499)로 예산에 미달합니다.
+- Media그룹 -527(외주개발용역비 -513)이 주원인이며, 월 배부액은 493→483으로 큰 변화가 없습니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 1,227 / 예산 1,057, 집행률 116%(+170)로 예산을 초과했습니다.
+- Staff부문 +180이 대부분이며, 특허처리비 +77 초과가 주원인입니다.
+- 1월 일회성(외부감사 착수금 200)을 빼면 월 560→467로 낮아지는 흐름입니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 572 / 예산 592, 집행률 97%(-20)로 예산에 근접합니다.
+- 월 배부액은 272→300으로, 사옥 이전에 따른 감소는 아직 나타나지 않았습니다.</t>
+  </si>
+  <si>
+    <t>3월</t>
+  </si>
+  <si>
+    <t>- 당월 실적 2,592 / 예산 2,669, 집행률 97%(-77)로 예산 내에서 집행되었습니다.
+- 본사 1,874/1,993(94%, -119)는 미달, 법인 718/676(106%, +42)은 초과입니다.
+- MOBILITY가 101로 1~2월(61·50) 대비 두 배 수준으로 올랐습니다.</t>
+  </si>
+  <si>
+    <t>3월 누계</t>
+  </si>
+  <si>
+    <t>- 누계 실적 8,043 / 예산 8,450, 집행률 95%(-407)로 예산 내 집행 중입니다.
+- 본사 5,646/6,266(90%, -620)는 미달, 법인 2,397/2,184(110%, +213)은 초과로 방향이 엇갈립니다.
+- 항목별로는 HUMAX(공통) 116%(+245)·MOBILITY 143%(+64)가 초과, STB 72%(-541)·건물 94%가 미달입니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 3,770(국내 904 / 해외 2,866), 연간 예산 14,637 대비 26% 집행으로 3개월 경과 진도(25%)에 부합합니다.
+- 국내·해외 모두 26%로 진도와 나란히 갑니다.
+- 비용의 58%(2,173)가 인건비로 인력 운영 계획에 따라 변동됩니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 1,417 / 예산 1,958, 집행률 72%(-541)로 예산에 미달합니다.
+- Media그룹 -522(외주개발용역비 -533)가 주원인이며, 월 배부액은 493→483→441로 완만히 낮아집니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 1,811 / 예산 1,566, 집행률 116%(+245)로 예산을 초과했습니다.
+- Staff부문 +240이 대부분이며, 특허처리비 +90 초과가 주원인입니다.
+- 1월 일회성(외부감사 착수금 200)을 빼면 월 560→467→584로, 감소 추세는 확인되지 않습니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 833 / 예산 890, 집행률 94%(-57)로 예산에 근접합니다.
+- 월 배부액은 272→300→261로, 사옥 이전에 따른 감소는 아직 나타나지 않았습니다.</t>
+  </si>
+  <si>
+    <t>4월</t>
+  </si>
+  <si>
+    <t>- 당월 실적 2,526 / 예산 2,619, 집행률 96%(-93)로 예산 내에서 집행되었습니다.
+- 본사 1,868/1,988(94%, -120)는 미달, 법인 658/631(104%, +27)은 소폭 초과입니다.
+- 건물이 135로 1~3월 평균 278의 절반 아래로 떨어져, 사옥 이전 효과가 나타나기 시작했습니다.</t>
+  </si>
+  <si>
+    <t>4월 누계</t>
+  </si>
+  <si>
+    <t>- 누계 실적 10,568 / 예산 11,069, 집행률 95%(-501)로 예산 내 집행 중입니다.
+- 본사 7,514/8,254(91%, -740)는 미달, 법인 3,055/2,815(109%, +240)은 초과로 방향이 엇갈립니다.
+- 항목별로는 HUMAX(공통) 115%(+321)·EVCS(국내) 107%(+82)가 초과, 건물 81%·STB 83%·EVCS(해외) 92%가 미달입니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 4,972(국내 1,269 / 해외 3,703), 연간 예산 14,637 대비 34% 집행으로 4개월 경과 진도(33%)에 부합합니다.
+- 국내는 36%로 진도를 앞서고 월 배부액도 269→365로 늘어, 축소 기조와는 반대 방향입니다.
+- 해외는 33%로 진도에 부합하며, 비용의 57%(2,817)가 인건비로 인력 운영 계획에 따라 변동됩니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 1,982 / 예산 2,392, 집행률 83%(-410)로 예산에 미달합니다.
+- Media그룹 -426(외주개발용역비 -533)이 주원인이며, HUK는 +79 초과입니다.
+- 4월 트렌드 왜곡: STB License Fee/Nagra 84백만이 4월에 기표돼 배부액이 565로 부풀었습니다(5월 reverse, 선급비용 조정 시기 오류)</t>
+  </si>
+  <si>
+    <t>- 누계 실적 2,409 / 예산 2,088, 집행률 115%(+321)로 예산을 초과했습니다.
+- Staff부문 +300이 대부분이며, 지급수수료 +106·특허처리비 +105 초과가 주원인입니다.
+- 1월 일회성 집행으로 배부액 상승: 26년 외부감사 착수금 200백만(1월). 제외 시 월 560→467→584→598입니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 968 / 예산 1,199, 집행률 81%(-231)로 예산을 밑돕니다.
+- 감가상각비 -163, 수도광열비 -75 미달이 주원인입니다.
+- 1~3월 평균 278 → 4월 135로 사옥 이전에 따른 감소가 시작됐습니다.</t>
   </si>
 </sst>
 </file>
@@ -553,7 +691,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05630F61-30FB-4CF7-B3FF-D0B93533C1C1}">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.625" customWidth="1"/>
@@ -576,54 +714,54 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="66" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="66" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="66" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="66" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="33" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -631,27 +769,27 @@
         <v>6</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="33" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -659,23 +797,23 @@
         <v>4</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="66" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="5" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="66" x14ac:dyDescent="0.3">
@@ -683,25 +821,25 @@
         <v>5</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="66" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="33" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -709,38 +847,350 @@
         <v>6</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="33" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D13" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="4"/>
+      <c r="D14" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="4"/>
+      <c r="D15" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="66" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="4"/>
+      <c r="D16" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="33" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="33" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" s="4"/>
+      <c r="D20" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="66" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" s="4"/>
+      <c r="D21" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="66" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="4"/>
+      <c r="D22" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="66" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A26" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="4"/>
+      <c r="D26" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="66" x14ac:dyDescent="0.3">
+      <c r="A27" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27" s="4"/>
+      <c r="D27" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="66" x14ac:dyDescent="0.3">
+      <c r="A28" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C28" s="4"/>
+      <c r="D28" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="66" x14ac:dyDescent="0.3">
+      <c r="A29" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A30" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A31" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A32" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" s="4"/>
+      <c r="D32" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="66" x14ac:dyDescent="0.3">
+      <c r="A33" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C33" s="4"/>
+      <c r="D33" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="66" x14ac:dyDescent="0.3">
+      <c r="A34" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C34" s="4"/>
+      <c r="D34" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="66" x14ac:dyDescent="0.3">
+      <c r="A35" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A36" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A37" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="33" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4" t="s">
+    <row r="38" spans="1:4" ht="33" x14ac:dyDescent="0.3">
+      <c r="A38" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D38" s="5" t="s">
         <v>18</v>
       </c>
     </row>

--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A10900B-872E-4407-BDDC-D84968CA32F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E342D7C-2226-4E28-A55B-D74D9B794AFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-885" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -75,214 +75,214 @@
     <t>5월</t>
   </si>
   <si>
-    <t>- 당월 실적 2,444 / 예산 2,397, 집행률 102%(+47)로 예산 수준에서 집행되었습니다.
-- 본사 1,804/1,805(100%)는 계획대로이나, 법인이 640/592(108%, +48)로 초과했습니다.
-- HUMAX(공통)이 716으로 1~4월 평균 602를 웃돌았고, 건물은 121로 사옥 이전 후 낮은 수준을 유지합니다.</t>
-  </si>
-  <si>
     <t>5월 누계</t>
   </si>
   <si>
-    <t>- 누계 실적 6,161(국내 1,612 / 해외 4,549), 연간 예산 14,637 대비 42% 집행으로 5개월 경과 진도(42%)에 부합합니다.
-- 국내는 46%로 진도를 앞서고 월 배부액도 269→343으로 늘어, 축소 기조와는 반대 방향입니다.
-- 해외는 41%로 진도에 부합하며, 비용의 56%(3,439)가 인건비로 인력 운영 계획에 따라 변동됩니다.</t>
-  </si>
-  <si>
-    <t>- 누계 실적 2,381 / 예산 2,806, 집행률 85%(-425)로 예산에 미달합니다.
-- Media그룹 -469(외주개발용역비 -525)가 주원인이며, 왜곡 보정 후 월 441~493으로 평탄해 Closing에 따른 감소 추세는 아직 확인되지 않습니다.
+    <t>6월</t>
+  </si>
+  <si>
+    <t>6월 누계</t>
+  </si>
+  <si>
+    <t>1월</t>
+  </si>
+  <si>
+    <t>1월 누계</t>
+  </si>
+  <si>
+    <t>2월</t>
+  </si>
+  <si>
+    <t>2월 누계</t>
+  </si>
+  <si>
+    <t>3월</t>
+  </si>
+  <si>
+    <t>3월 누계</t>
+  </si>
+  <si>
+    <t>4월</t>
+  </si>
+  <si>
+    <t>4월 누계</t>
+  </si>
+  <si>
+    <t>- 당월 실적 2,818백만(예산 대비 88%)으로 예산에 미달합니다.
+- 본사 2,020백만(예산 대비 83%)이 미달을 주도했고, 법인은 798백만(예산 대비 102%)으로 예산 수준입니다.
+- STB는 예산 대비 49%(493백만)에 그친 반면, HUMAX(공통)은 760백만으로 외부감사 착수금 200백만이 반영됐습니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 2,818백만(예산 대비 88%)으로 예산 내에서 집행 중입니다.
+- 본사 2,020백만(예산 대비 83%)은 미달, 법인 798백만(예산 대비 102%)은 예산 수준입니다.
+- 항목별로는 STB 49%의 미달과 HUMAX(공통) 122%의 초과가 차이의 대부분을 만듭니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 1,233백만(국내 269백만 / 해외 963백만), 연간 예산의 8%로 1개월 경과 진도(8%)에 부합합니다.
+- 국내 8%, 해외 9%로 아직 진도 차이는 크지 않습니다.
+- 비용의 58%인 720백만이 인건비라 인력 운영 계획에 따라 변동됩니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 760백만(예산 대비 122%)으로 예산을 138백만 초과했습니다.
+- Staff부문 +138백만이 대부분이며, 특허처리비 +64백만 초과가 주원인입니다.
+- 1월 일회성 집행으로 배부액 상승: 26년 외부감사 착수금 200백만(1월)</t>
+  </si>
+  <si>
+    <t>- 누계 실적 272백만(예산 대비 91%)으로 예산에 소폭 미달합니다.
+- Staff부문 -26백만으로 차이가 작아, 사옥 이전에 따른 감소는 아직 나타나지 않았습니다.</t>
+  </si>
+  <si>
+    <t>- 당월 실적 2,633백만(예산 대비 103%)으로 예산을 소폭 초과했습니다.
+- 본사 1,752백만(예산 대비 95%)은 미달이나, 법인이 881백만(예산 대비 121%)으로 초과했습니다.
+- HUMAX(공통)이 467백만으로 1월(760백만) 대비 293백만 낮아졌습니다(1월 외부감사 착수금 소멸).</t>
+  </si>
+  <si>
+    <t>- 누계 실적 5,451백만(예산 대비 94%)으로 예산 내에서 집행 중입니다.
+- 본사 3,772백만(예산 대비 88%)은 미달, 법인 1,679백만(예산 대비 111%)은 초과로 방향이 엇갈립니다.
+- 항목별로는 HUMAX(공통) 116%의 초과와 STB 66%의 미달이 차이의 대부분을 만듭니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 2,566백만(국내 583백만 / 해외 1,983백만), 연간 예산의 18%로 2개월 경과 진도(17%)에 부합합니다.
+- 국내 17%, 해외 18%로 진도와 나란히 갑니다.
+- 비용의 58%인 1,481백만이 인건비라 인력 운영 계획에 따라 변동됩니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 1,227백만(예산 대비 116%)으로 예산을 170백만 초과했습니다.
+- Staff부문 +180백만이 대부분이며, 특허처리비 +77백만 초과가 주원인입니다.
+- 1월 일회성(외부감사 착수금 200백만)을 빼면 월 560→467백만으로 낮아지는 흐름입니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 572백만(예산 대비 97%)으로 예산에 근접합니다.
+- 월 배부액은 272→300백만으로, 사옥 이전에 따른 감소는 아직 나타나지 않았습니다.</t>
+  </si>
+  <si>
+    <t>- 당월 실적 2,592백만(예산 대비 97%)으로 예산 내에서 집행했습니다.
+- 본사 1,874백만(예산 대비 94%)은 미달, 법인 718백만(예산 대비 106%)은 초과입니다.
+- MOBILITY가 101백만으로 1~2월(61·50백만) 대비 두 배 수준으로 올랐습니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 8,043백만(예산 대비 95%)으로 예산 내에서 집행 중입니다.
+- 본사 5,646백만(예산 대비 90%)은 미달, 법인 2,397백만(예산 대비 110%)은 초과로 방향이 엇갈립니다.
+- 항목별로는 HUMAX(공통) 116%, MOBILITY 143%가 예산을 넘었고, STB 72%, 건물 94%는 밑돕니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 3,770백만(국내 904백만 / 해외 2,866백만), 연간 예산의 26%로 3개월 경과 진도(25%)에 부합합니다.
+- 국내·해외 모두 26%로 진도와 나란히 갑니다.
+- 비용의 58%인 2,173백만이 인건비라 인력 운영 계획에 따라 변동됩니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 1,811백만(예산 대비 116%)으로 예산을 245백만 초과했습니다.
+- Staff부문 +240백만이 대부분이며, 특허처리비 +90백만 초과가 주원인입니다.
+- 1월 일회성(외부감사 착수금 200백만)을 빼면 월 560→467→584백만으로, 감소 추세는 확인되지 않습니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 833백만(예산 대비 94%)으로 예산에 근접합니다.
+- 월 배부액은 272→300→261백만으로, 사옥 이전에 따른 감소는 아직 나타나지 않았습니다.</t>
+  </si>
+  <si>
+    <t>- 당월 실적 2,526백만(예산 대비 96%)으로 예산 내에서 집행했습니다.
+- 본사 1,868백만(예산 대비 94%)은 미달, 법인 658백만(예산 대비 104%)은 소폭 초과입니다.
+- 건물이 135백만으로 1~3월 평균 278백만의 절반 아래로 떨어져, 사옥 이전 효과가 나타나기 시작했습니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 10,568백만(예산 대비 95%)으로 예산 내에서 집행 중입니다.
+- 본사 7,514백만(예산 대비 91%)은 미달, 법인 3,055백만(예산 대비 109%)은 초과로 방향이 엇갈립니다.
+- 항목별로는 HUMAX(공통) 115%, EVCS(국내) 107%가 예산을 넘었고, 건물 81%, STB 83%, EVCS(해외) 92%는 밑돕니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 4,972백만(국내 1,269백만 / 해외 3,703백만), 연간 예산의 34%로 4개월 경과 진도(33%)에 부합합니다.
+- 국내는 연간 예산의 36%를 써 진도를 앞서고, 월 배부액도 269→365백만으로 늘어 축소 기조와 반대입니다.
+- 해외는 33%로 진도에 맞으며, 비용의 57%인 2,817백만이 인건비라 인력 운영 계획에 따라 변동됩니다.</t>
+  </si>
+  <si>
+    <t>- 당월 실적 2,444백만(예산 대비 102%)으로 예산 수준에서 집행했습니다.
+- 본사 1,804백만(예산 대비 100%)은 계획대로이나, 법인이 640백만(예산 대비 108%)으로 초과했습니다.
+- HUMAX(공통)이 716백만으로 1~4월 평균 602백만을 웃돌았고, 건물은 121백만으로 사옥 이전 후 낮은 수준을 유지합니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 13,012백만(예산 대비 97%)으로 예산 내에서 집행 중입니다.
+- 본사 9,318백만(예산 대비 93%)은 미달, 법인 3,694백만(예산 대비 108%)은 초과로 방향이 엇갈립니다.
+- 항목별로는 HUMAX(공통) 121%, EVCS(국내) 110%가 예산을 넘었고, 건물 72%, STB 85%, EVCS(해외) 92%는 밑돕니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 6,161백만(국내 1,612백만 / 해외 4,549백만), 연간 예산의 42%로 5개월 경과 진도(42%)에 부합합니다.
+- 국내는 연간 예산의 46%를 써 진도를 앞서고, 월 배부액도 269→343백만으로 늘어 축소 기조와 반대입니다.
+- 해외는 41%로 진도에 맞으며, 비용의 56%인 3,439백만이 인건비라 인력 운영 계획에 따라 변동됩니다.</t>
+  </si>
+  <si>
+    <t>- 당월 실적 2,537백만(예산 대비 100%)으로 예산에 부합합니다.
+- 본사 1,747백만(예산 대비 91%)은 미달, 법인 790백만(예산 대비 131%)은 초과로 방향이 엇갈립니다.
+- HUMAX(공통)은 541백만으로 5월(716백만) 대비 175백만 낮아졌고, STB는 536백만으로 보정 후 1~5월 평균 476백만을 웃돌았습니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 15,549백만(예산 대비 97%)으로 예산 내에서 집행 중입니다.
+- 본사 11,065백만(예산 대비 92%)은 미달, 법인 4,484백만(예산 대비 112%)은 초과로 방향이 엇갈립니다.
+- 항목별로는 HUMAX(공통) 119%, EVCS(국내) 108%가 예산을 넘었고, 건물 67%, STB 90%, EVCS(해외) 94%는 밑돕니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 7,440백만(국내 1,973백만 / 해외 5,468백만), 연간 예산의 51%로 6개월 경과 진도(50%)에 부합합니다.
+- 국내는 연간 예산의 57%를 써 진도를 앞서고, 월 배부액도 269→361백만으로 늘어 축소 기조와 반대입니다.
+- 해외는 49%로 진도에 맞으며, 비용의 56%인 4,130백만이 인건비라 인력 운영 계획에 따라 변동됩니다.</t>
+  </si>
+  <si>
+    <t>- 1월, 5월 일회성 집행: 26년 외부감사 착수금 200백만(1월), 15차 주식선택권 취소 216백만(5월). 제외 시 HUMAX(공통) 월 배부액은 467~598백만 범위입니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 493백만(예산 대비 49%)으로 예산을 521백만 밑돕니다.
+- Media그룹 -533백만(외주개발용역비 -509)이 주원인으로, 연초 외주개발 집행이 계획보다 늦습니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 975백만(예산 대비 66%)으로 예산을 499백만 밑돕니다.
+- Media그룹 -527백만(외주개발용역비 -513)이 주원인이며, 월 배부액은 493→483백만으로 큰 변화가 없습니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 1,417백만(예산 대비 72%)으로 예산을 541백만 밑돕니다.
+- Media그룹 -522백만(외주개발용역비 -533)이 주원인이며, 월 배부액은 493→483→441백만으로 완만히 낮아집니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 1,982백만(예산 대비 83%)으로 예산을 410백만 밑돕니다.
+- Media그룹 -426백만(외주개발용역비 -533)이 주원인이며, HUK는 +79백만 초과입니다.
+- 4월 트렌드 왜곡: STB License Fee/Nagra 84백만이 4월에 기표돼 배부액이 565백만으로 부풀었습니다(5월 reverse, 선급비용 조정 시기 오류)</t>
+  </si>
+  <si>
+    <t>- 누계 실적 2,409백만(예산 대비 115%)으로 예산을 321백만 초과했습니다.
+- Staff부문 +300백만이 대부분이며, 지급수수료 +106·특허처리비 +105 초과가 주원인입니다.
+- 1월 일회성 집행으로 배부액 상승: 26년 외부감사 착수금 200백만(1월). 제외 시 월 560→467→584→598백만입니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 968백만(예산 대비 81%)으로 예산을 231백만 밑돕니다.
+- 감가상각비 -163백만, 수도광열비 -75 미달이 주원인입니다.
+- 1~3월 평균 278백만 → 4월 135백만으로 사옥 이전에 따른 감소가 시작됐습니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 2,381백만(예산 대비 85%)으로 예산을 425백만 밑돕니다.
+- Media그룹 -469백만(외주개발용역비 -525)이 주원인이며, 보정 후 월 441~493백만으로 평탄해 감소 추세는 아직 없습니다.
 - 4월, 5월 트렌드 왜곡: STB License Fee/Nagra 84백만 4월 기표 후 5월 reverse (선급비용 조정 시기 오류)</t>
   </si>
   <si>
-    <t>- 누계 실적 3,125 / 예산 2,573, 집행률 121%(+552)로 예산을 초과했습니다.
-- Staff부문 +516이 대부분이며, 급여 +208·특허처리비 +106·지급수수료 +100 초과가 주원인입니다.
+    <t>- 누계 실적 3,125백만(예산 대비 121%)으로 예산을 552백만 초과했습니다.
+- Staff부문 +516백만이 대부분이며, 급여 +208·특허처리비 +106·지급수수료 +100 초과가 주원인입니다.
 - 1월, 5월 일회성 집행으로 배부액 상승: 26년 외부감사 착수금 200백만(1월), 15차 주식선택권 취소 216백만(5월)</t>
   </si>
   <si>
-    <t>- 누계 실적 1,089 / 예산 1,505, 집행률 72%(-416)로 예산을 크게 밑돕니다.
-- 감가상각비 -326, 수도광열비 -168 미달이 주원인입니다(임차료는 +91 초과).
-- 1~3월 평균 278 → 4~5월 평균 128로 사옥 이전에 따른 계단식 감소가 확인됩니다.</t>
-  </si>
-  <si>
-    <t>- 1월, 5월 일회성 집행: 26년 외부감사 착수금 200백만(1월), 15차 주식선택권 취소 216백만(5월). 제외 시 HUMAX(공통) 월 배부액은 467~598 범위입니다.</t>
-  </si>
-  <si>
-    <t>- 누계 실적 13,012 / 예산 13,466, 집행률 97%(-454)로 예산 내 집행 중입니다.
-- 본사 9,318/10,059(93%, -741)는 미달, 법인 3,694/3,407(108%, +287)은 초과로 방향이 엇갈립니다.
-- 항목별로는 HUMAX(공통) 121%(+552)·EVCS(국내) 110%(+142)가 초과, 건물 72%·STB 85%·EVCS(해외) 92%가 미달입니다.</t>
-  </si>
-  <si>
-    <t>6월</t>
-  </si>
-  <si>
-    <t>- 당월 실적 2,537 / 예산 2,526, 집행률 100%(+11)로 예산에 부합합니다.
-- 본사 1,747/1,923(91%, -176)은 미달, 법인 790/603(131%, +187)은 초과로 방향이 엇갈립니다.
-- HUMAX(공통)은 541로 5월(716) 대비 -175 낮아졌고, STB는 536으로 보정 후 1~5월 평균 476을 웃돌았습니다.</t>
-  </si>
-  <si>
-    <t>6월 누계</t>
-  </si>
-  <si>
-    <t>- 누계 실적 15,549 / 예산 15,992, 집행률 97%(-443)로 예산 내 집행 중입니다.
-- 본사 11,065/11,982(92%, -917)는 미달, 법인 4,484/4,010(112%, +474)은 초과로 방향이 엇갈립니다.
-- 항목별로는 HUMAX(공통) 119%(+586)·EVCS(국내) 108%(+147)가 초과, 건물 67%·STB 90%·EVCS(해외) 94%가 미달입니다.</t>
-  </si>
-  <si>
-    <t>- 누계 실적 7,440(국내 1,973 / 해외 5,468), 연간 예산 14,637 대비 51% 집행으로 6개월 경과 진도(50%)에 부합합니다.
-- 국내는 57%로 진도를 앞서고 월 배부액도 269→361로 늘어, 축소 기조와는 반대 방향입니다.
-- 해외는 49%로 진도에 부합하며, 비용의 56%(4,130)가 인건비로 인력 운영 계획에 따라 변동됩니다.</t>
-  </si>
-  <si>
-    <t>- 누계 실적 2,916 / 예산 3,252, 집행률 90%(-336)로 예산에 미달합니다.
-- Media그룹 -454(외주개발용역비 -526)가 주원인이며, 왜곡 보정 후 월 441~536으로 Closing에 따른 감소 추세는 아직 확인되지 않습니다.
+    <t>- 누계 실적 1,089백만(예산 대비 72%)으로 예산을 416백만 밑돕니다.
+- 감가상각비 -326백만, 수도광열비 -168 미달이 주원인입니다(임차료 +91 초과).
+- 1~3월 평균 278백만 → 4~5월 평균 128백만으로 사옥 이전에 따른 계단식 감소가 확인됩니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 2,916백만(예산 대비 90%)으로 예산을 336백만 밑돕니다.
+- Media그룹 -454백만(외주개발용역비 -526)이 주원인이며, 보정 후 월 441~536백만으로 감소 추세는 아직 없습니다.
 - 4월, 5월 트렌드 왜곡: STB License Fee/Nagra 84백만 4월 기표 후 5월 reverse (선급비용 조정 시기 오류)</t>
   </si>
   <si>
-    <t>- 누계 실적 3,666 / 예산 3,080, 집행률 119%(+586)로 예산을 초과했습니다.
-- Staff부문 +466(급여 +217, 특허처리비 +105), HBR +124 초과가 주원인으로, 감소 추세 관리가 필요합니다.
+    <t>- 누계 실적 3,666백만(예산 대비 119%)으로 예산을 586백만 초과했습니다.
+- Staff부문 +466백만(급여 +217, 특허처리비 +105), HBR +124백만 초과가 주원인으로, 감소 추세 관리가 필요합니다.
 - 1월, 5월 일회성 집행으로 배부액 상승: 26년 외부감사 착수금 200백만(1월), 15차 주식선택권 취소 216백만(5월)</t>
   </si>
   <si>
-    <t>- 누계 실적 1,211 / 예산 1,810, 집행률 67%(-599)로 예산을 크게 밑돕니다.
-- 감가상각비 -489, 수도광열비 -254 미달이 주원인입니다(임차료는 +136 초과).
-- 1~3월 평균 278 → 4~6월 평균 126으로 사옥 이전에 따른 계단식 감소가 확인됩니다.</t>
-  </si>
-  <si>
-    <t>1월</t>
-  </si>
-  <si>
-    <t>- 당월 실적 2,818 / 예산 3,215, 집행률 88%(-397)로 예산에 미달합니다.
-- 본사 2,020/2,434(83%, -414)가 미달을 주도했고, 법인은 798/781(102%, +17)로 예산 수준입니다.
-- STB가 예산 1,014 대비 493(49%)에 그쳤고, HUMAX(공통)은 예산 622에 실적 760으로 외부감사 착수금 200이 반영됐습니다.</t>
-  </si>
-  <si>
-    <t>1월 누계</t>
-  </si>
-  <si>
-    <t>- 누계 실적 2,818 / 예산 3,215, 집행률 88%(-397)로 예산 내 집행 중입니다.
-- 본사 2,020/2,434(83%, -414)는 미달, 법인 798/781(102%, +17)은 예산 수준입니다.
-- 항목별로는 STB 49%(-521) 미달과 HUMAX(공통) 122%(+138) 초과가 차이의 대부분을 만듭니다.</t>
-  </si>
-  <si>
-    <t>- 누계 실적 1,233(국내 269 / 해외 963), 연간 예산 14,637 대비 8% 집행으로 1개월 경과 진도(8%)에 부합합니다.
-- 국내 8%·해외 9%로 아직 진도 차이는 크지 않습니다.
-- 비용의 58%(720)가 인건비로 인력 운영 계획에 따라 변동됩니다.</t>
-  </si>
-  <si>
-    <t>- 누계 실적 493 / 예산 1,014, 집행률 49%(-521)로 예산을 크게 밑돕니다.
-- Media그룹 -533(외주개발용역비 -509)이 주원인으로, 연초 외주개발 집행이 계획보다 늦습니다.</t>
-  </si>
-  <si>
-    <t>- 누계 실적 760 / 예산 622, 집행률 122%(+138)로 예산을 초과했습니다.
-- Staff부문 +138이 대부분이며, 특허처리비 +64 초과가 주원인입니다.
-- 1월 일회성 집행으로 배부액 상승: 26년 외부감사 착수금 200백만(1월)</t>
-  </si>
-  <si>
-    <t>- 누계 실적 272 / 예산 299, 집행률 91%(-27)로 예산에 소폭 미달합니다.
-- Staff부문 -26으로 차이가 작아, 사옥 이전에 따른 감소는 아직 나타나지 않았습니다.</t>
-  </si>
-  <si>
-    <t>2월</t>
-  </si>
-  <si>
-    <t>- 당월 실적 2,633 / 예산 2,566, 집행률 103%(+67)로 예산을 소폭 초과했습니다.
-- 본사 1,752/1,839(95%, -87)는 미달이나, 법인이 881/727(121%, +154)로 초과했습니다.
-- HUMAX(공통)이 467로 1월(760) 대비 -293 낮아졌습니다(1월 외부감사 착수금 200 소멸).</t>
-  </si>
-  <si>
-    <t>2월 누계</t>
-  </si>
-  <si>
-    <t>- 누계 실적 5,451 / 예산 5,781, 집행률 94%(-330)로 예산 내 집행 중입니다.
-- 본사 3,772/4,273(88%, -501)는 미달, 법인 1,679/1,508(111%, +171)은 초과로 방향이 엇갈립니다.
-- 항목별로는 HUMAX(공통) 116%(+170) 초과와 STB 66%(-499) 미달이 차이의 대부분을 만듭니다.</t>
-  </si>
-  <si>
-    <t>- 누계 실적 2,566(국내 583 / 해외 1,983), 연간 예산 14,637 대비 18% 집행으로 2개월 경과 진도(17%)에 부합합니다.
-- 국내 17%·해외 18%로 진도와 나란히 갑니다.
-- 비용의 58%(1,481)가 인건비로 인력 운영 계획에 따라 변동됩니다.</t>
-  </si>
-  <si>
-    <t>- 누계 실적 975 / 예산 1,474, 집행률 66%(-499)로 예산에 미달합니다.
-- Media그룹 -527(외주개발용역비 -513)이 주원인이며, 월 배부액은 493→483으로 큰 변화가 없습니다.</t>
-  </si>
-  <si>
-    <t>- 누계 실적 1,227 / 예산 1,057, 집행률 116%(+170)로 예산을 초과했습니다.
-- Staff부문 +180이 대부분이며, 특허처리비 +77 초과가 주원인입니다.
-- 1월 일회성(외부감사 착수금 200)을 빼면 월 560→467로 낮아지는 흐름입니다.</t>
-  </si>
-  <si>
-    <t>- 누계 실적 572 / 예산 592, 집행률 97%(-20)로 예산에 근접합니다.
-- 월 배부액은 272→300으로, 사옥 이전에 따른 감소는 아직 나타나지 않았습니다.</t>
-  </si>
-  <si>
-    <t>3월</t>
-  </si>
-  <si>
-    <t>- 당월 실적 2,592 / 예산 2,669, 집행률 97%(-77)로 예산 내에서 집행되었습니다.
-- 본사 1,874/1,993(94%, -119)는 미달, 법인 718/676(106%, +42)은 초과입니다.
-- MOBILITY가 101로 1~2월(61·50) 대비 두 배 수준으로 올랐습니다.</t>
-  </si>
-  <si>
-    <t>3월 누계</t>
-  </si>
-  <si>
-    <t>- 누계 실적 8,043 / 예산 8,450, 집행률 95%(-407)로 예산 내 집행 중입니다.
-- 본사 5,646/6,266(90%, -620)는 미달, 법인 2,397/2,184(110%, +213)은 초과로 방향이 엇갈립니다.
-- 항목별로는 HUMAX(공통) 116%(+245)·MOBILITY 143%(+64)가 초과, STB 72%(-541)·건물 94%가 미달입니다.</t>
-  </si>
-  <si>
-    <t>- 누계 실적 3,770(국내 904 / 해외 2,866), 연간 예산 14,637 대비 26% 집행으로 3개월 경과 진도(25%)에 부합합니다.
-- 국내·해외 모두 26%로 진도와 나란히 갑니다.
-- 비용의 58%(2,173)가 인건비로 인력 운영 계획에 따라 변동됩니다.</t>
-  </si>
-  <si>
-    <t>- 누계 실적 1,417 / 예산 1,958, 집행률 72%(-541)로 예산에 미달합니다.
-- Media그룹 -522(외주개발용역비 -533)가 주원인이며, 월 배부액은 493→483→441로 완만히 낮아집니다.</t>
-  </si>
-  <si>
-    <t>- 누계 실적 1,811 / 예산 1,566, 집행률 116%(+245)로 예산을 초과했습니다.
-- Staff부문 +240이 대부분이며, 특허처리비 +90 초과가 주원인입니다.
-- 1월 일회성(외부감사 착수금 200)을 빼면 월 560→467→584로, 감소 추세는 확인되지 않습니다.</t>
-  </si>
-  <si>
-    <t>- 누계 실적 833 / 예산 890, 집행률 94%(-57)로 예산에 근접합니다.
-- 월 배부액은 272→300→261로, 사옥 이전에 따른 감소는 아직 나타나지 않았습니다.</t>
-  </si>
-  <si>
-    <t>4월</t>
-  </si>
-  <si>
-    <t>- 당월 실적 2,526 / 예산 2,619, 집행률 96%(-93)로 예산 내에서 집행되었습니다.
-- 본사 1,868/1,988(94%, -120)는 미달, 법인 658/631(104%, +27)은 소폭 초과입니다.
-- 건물이 135로 1~3월 평균 278의 절반 아래로 떨어져, 사옥 이전 효과가 나타나기 시작했습니다.</t>
-  </si>
-  <si>
-    <t>4월 누계</t>
-  </si>
-  <si>
-    <t>- 누계 실적 10,568 / 예산 11,069, 집행률 95%(-501)로 예산 내 집행 중입니다.
-- 본사 7,514/8,254(91%, -740)는 미달, 법인 3,055/2,815(109%, +240)은 초과로 방향이 엇갈립니다.
-- 항목별로는 HUMAX(공통) 115%(+321)·EVCS(국내) 107%(+82)가 초과, 건물 81%·STB 83%·EVCS(해외) 92%가 미달입니다.</t>
-  </si>
-  <si>
-    <t>- 누계 실적 4,972(국내 1,269 / 해외 3,703), 연간 예산 14,637 대비 34% 집행으로 4개월 경과 진도(33%)에 부합합니다.
-- 국내는 36%로 진도를 앞서고 월 배부액도 269→365로 늘어, 축소 기조와는 반대 방향입니다.
-- 해외는 33%로 진도에 부합하며, 비용의 57%(2,817)가 인건비로 인력 운영 계획에 따라 변동됩니다.</t>
-  </si>
-  <si>
-    <t>- 누계 실적 1,982 / 예산 2,392, 집행률 83%(-410)로 예산에 미달합니다.
-- Media그룹 -426(외주개발용역비 -533)이 주원인이며, HUK는 +79 초과입니다.
-- 4월 트렌드 왜곡: STB License Fee/Nagra 84백만이 4월에 기표돼 배부액이 565로 부풀었습니다(5월 reverse, 선급비용 조정 시기 오류)</t>
-  </si>
-  <si>
-    <t>- 누계 실적 2,409 / 예산 2,088, 집행률 115%(+321)로 예산을 초과했습니다.
-- Staff부문 +300이 대부분이며, 지급수수료 +106·특허처리비 +105 초과가 주원인입니다.
-- 1월 일회성 집행으로 배부액 상승: 26년 외부감사 착수금 200백만(1월). 제외 시 월 560→467→584→598입니다.</t>
-  </si>
-  <si>
-    <t>- 누계 실적 968 / 예산 1,199, 집행률 81%(-231)로 예산을 밑돕니다.
-- 감가상각비 -163, 수도광열비 -75 미달이 주원인입니다.
-- 1~3월 평균 278 → 4월 135로 사옥 이전에 따른 감소가 시작됐습니다.</t>
+    <t>- 누계 실적 1,211백만(예산 대비 67%)으로 예산을 599백만 밑돕니다.
+- 감가상각비 -489백만, 수도광열비 -254 미달이 주원인입니다(임차료 +136 초과).
+- 1~3월 평균 278백만 → 4~6월 평균 126백만으로 사옥 이전에 따른 계단식 감소가 확인됩니다.</t>
   </si>
 </sst>
 </file>
@@ -719,11 +719,11 @@
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -731,11 +731,11 @@
         <v>4</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -743,11 +743,11 @@
         <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="5" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="33" x14ac:dyDescent="0.3">
@@ -755,13 +755,13 @@
         <v>6</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -769,13 +769,13 @@
         <v>6</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="33" x14ac:dyDescent="0.3">
@@ -783,13 +783,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -797,11 +797,11 @@
         <v>4</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="5" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -809,23 +809,23 @@
         <v>4</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="66" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="5" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="33" x14ac:dyDescent="0.3">
@@ -833,13 +833,13 @@
         <v>6</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -847,13 +847,13 @@
         <v>6</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="33" x14ac:dyDescent="0.3">
@@ -861,13 +861,13 @@
         <v>6</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -875,11 +875,11 @@
         <v>4</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="5" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -887,37 +887,37 @@
         <v>4</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="66" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="33" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -925,13 +925,13 @@
         <v>6</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="33" x14ac:dyDescent="0.3">
@@ -939,13 +939,13 @@
         <v>6</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -953,11 +953,11 @@
         <v>4</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="C20" s="4"/>
       <c r="D20" s="5" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="66" x14ac:dyDescent="0.3">
@@ -965,23 +965,23 @@
         <v>4</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="66" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="5" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="66" x14ac:dyDescent="0.3">
@@ -989,27 +989,27 @@
         <v>6</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="66" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -1017,16 +1017,16 @@
         <v>6</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="66" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>4</v>
       </c>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="5" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="66" x14ac:dyDescent="0.3">
@@ -1043,23 +1043,23 @@
         <v>4</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C27" s="4"/>
       <c r="D27" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="66" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C28" s="4"/>
       <c r="D28" s="5" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="66" x14ac:dyDescent="0.3">
@@ -1067,13 +1067,13 @@
         <v>6</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>15</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -1081,13 +1081,13 @@
         <v>6</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>16</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -1095,25 +1095,25 @@
         <v>6</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="66" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C32" s="4"/>
       <c r="D32" s="5" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="66" x14ac:dyDescent="0.3">
@@ -1121,23 +1121,23 @@
         <v>4</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C33" s="4"/>
       <c r="D33" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="66" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C34" s="4"/>
       <c r="D34" s="5" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="66" x14ac:dyDescent="0.3">
@@ -1145,27 +1145,27 @@
         <v>6</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="66" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -1173,13 +1173,13 @@
         <v>6</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="33" x14ac:dyDescent="0.3">
@@ -1191,7 +1191,7 @@
         <v>10</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E342D7C-2226-4E28-A55B-D74D9B794AFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA48AC2-63AC-4BDC-BF84-0A81EBCA7AE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
+    <workbookView xWindow="28680" yWindow="-885" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Summary!$A$1:$D$38</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -315,7 +318,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -325,6 +328,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9E1F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF2F7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -358,7 +367,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -371,10 +380,16 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -793,80 +808,80 @@
       </c>
     </row>
     <row r="8" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="5" t="s">
+      <c r="C8" s="6"/>
+      <c r="D8" s="7" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="5" t="s">
+      <c r="C9" s="6"/>
+      <c r="D9" s="7" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="5" t="s">
+      <c r="C10" s="6"/>
+      <c r="D10" s="7" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="33" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="4" t="s">
+      <c r="A11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="7" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" s="4" t="s">
+      <c r="A12" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="7" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="33" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="4" t="s">
+      <c r="A13" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="7" t="s">
         <v>32</v>
       </c>
     </row>
@@ -949,80 +964,80 @@
       </c>
     </row>
     <row r="20" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="5" t="s">
+      <c r="C20" s="6"/>
+      <c r="D20" s="7" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="66" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="4"/>
-      <c r="D21" s="5" t="s">
+      <c r="C21" s="6"/>
+      <c r="D21" s="7" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="4"/>
-      <c r="D22" s="5" t="s">
+      <c r="C22" s="6"/>
+      <c r="D22" s="7" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="66" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B23" s="4" t="s">
+      <c r="A23" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" s="7" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="66" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B24" s="4" t="s">
+      <c r="A24" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" s="7" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B25" s="4" t="s">
+      <c r="A25" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B25" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D25" s="7" t="s">
         <v>53</v>
       </c>
     </row>
@@ -1105,80 +1120,80 @@
       </c>
     </row>
     <row r="32" spans="1:4" ht="66" x14ac:dyDescent="0.3">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C32" s="4"/>
-      <c r="D32" s="5" t="s">
+      <c r="C32" s="6"/>
+      <c r="D32" s="7" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="66" x14ac:dyDescent="0.3">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="4"/>
-      <c r="D33" s="5" t="s">
+      <c r="C33" s="6"/>
+      <c r="D33" s="7" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="4"/>
-      <c r="D34" s="5" t="s">
+      <c r="C34" s="6"/>
+      <c r="D34" s="7" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="66" x14ac:dyDescent="0.3">
-      <c r="A35" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B35" s="4" t="s">
+      <c r="A35" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B35" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C35" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="D35" s="7" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="66" x14ac:dyDescent="0.3">
-      <c r="A36" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B36" s="4" t="s">
+      <c r="A36" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B36" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="D36" s="7" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A37" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B37" s="4" t="s">
+      <c r="A37" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B37" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C37" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="D37" s="7" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1195,6 +1210,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D38" xr:uid="{05630F61-30FB-4CF7-B3FF-D0B93533C1C1}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA48AC2-63AC-4BDC-BF84-0A81EBCA7AE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19C63AFE-8D03-41F5-9F9C-65BA321CDE9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-885" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -213,11 +213,6 @@
 - 해외는 41%로 진도에 맞으며, 비용의 56%인 3,439백만이 인건비라 인력 운영 계획에 따라 변동됩니다.</t>
   </si>
   <si>
-    <t>- 당월 실적 2,537백만(예산 대비 100%)으로 예산에 부합합니다.
-- 본사 1,747백만(예산 대비 91%)은 미달, 법인 790백만(예산 대비 131%)은 초과로 방향이 엇갈립니다.
-- HUMAX(공통)은 541백만으로 5월(716백만) 대비 175백만 낮아졌고, STB는 536백만으로 보정 후 1~5월 평균 476백만을 웃돌았습니다.</t>
-  </si>
-  <si>
     <t>- 누계 실적 15,549백만(예산 대비 97%)으로 예산 내에서 집행 중입니다.
 - 본사 11,065백만(예산 대비 92%)은 미달, 법인 4,484백만(예산 대비 112%)은 초과로 방향이 엇갈립니다.
 - 항목별로는 HUMAX(공통) 119%, EVCS(국내) 108%가 예산을 넘었고, 건물 67%, STB 90%, EVCS(해외) 94%는 밑돕니다.</t>
@@ -286,6 +281,11 @@
     <t>- 누계 실적 1,211백만(예산 대비 67%)으로 예산을 599백만 밑돕니다.
 - 감가상각비 -489백만, 수도광열비 -254 미달이 주원인입니다(임차료 +136 초과).
 - 1~3월 평균 278백만 → 4~6월 평균 126백만으로 사옥 이전에 따른 계단식 감소가 확인됩니다.</t>
+  </si>
+  <si>
+    <t>- 당월 실적 2,537백만(예산 대비 100%)으로 예산에 부합합니다.
+- 본사 1,747백만(예산 대비 91%)은 미달, 법인 790백만(예산 대비 131%)은 초과로 방향이 엇갈립니다.
+- HUMAX(공통)은 541백만으로 5월(716백만) 대비 175백만 낮아졌고, STB는 536백만으로 1~5월 평균 476백만을 웃돌았습니다.</t>
   </si>
 </sst>
 </file>
@@ -776,7 +776,7 @@
         <v>7</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -854,7 +854,7 @@
         <v>7</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -932,7 +932,7 @@
         <v>7</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -1010,7 +1010,7 @@
         <v>7</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="66" x14ac:dyDescent="0.3">
@@ -1024,7 +1024,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -1038,7 +1038,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="66" x14ac:dyDescent="0.3">
@@ -1088,7 +1088,7 @@
         <v>7</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -1102,7 +1102,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -1116,7 +1116,7 @@
         <v>9</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="66" x14ac:dyDescent="0.3">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="7" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="66" x14ac:dyDescent="0.3">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="C33" s="6"/>
       <c r="D33" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="66" x14ac:dyDescent="0.3">
@@ -1166,7 +1166,7 @@
         <v>7</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="66" x14ac:dyDescent="0.3">
@@ -1180,7 +1180,7 @@
         <v>8</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -1194,7 +1194,7 @@
         <v>9</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="33" x14ac:dyDescent="0.3">
@@ -1206,7 +1206,7 @@
         <v>10</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19C63AFE-8D03-41F5-9F9C-65BA321CDE9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6367479-BB67-4BF3-ADEC-7078DC9B9312}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
+    <workbookView xWindow="31335" yWindow="4860" windowWidth="11160" windowHeight="6315" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -121,20 +121,11 @@
 - 항목별로는 STB 49%의 미달과 HUMAX(공통) 122%의 초과가 차이의 대부분을 만듭니다.</t>
   </si>
   <si>
-    <t>- 누계 실적 1,233백만(국내 269백만 / 해외 963백만), 연간 예산의 8%로 1개월 경과 진도(8%)에 부합합니다.
-- 국내 8%, 해외 9%로 아직 진도 차이는 크지 않습니다.
-- 비용의 58%인 720백만이 인건비라 인력 운영 계획에 따라 변동됩니다.</t>
-  </si>
-  <si>
     <t>- 누계 실적 760백만(예산 대비 122%)으로 예산을 138백만 초과했습니다.
 - Staff부문 +138백만이 대부분이며, 특허처리비 +64백만 초과가 주원인입니다.
 - 1월 일회성 집행으로 배부액 상승: 26년 외부감사 착수금 200백만(1월)</t>
   </si>
   <si>
-    <t>- 누계 실적 272백만(예산 대비 91%)으로 예산에 소폭 미달합니다.
-- Staff부문 -26백만으로 차이가 작아, 사옥 이전에 따른 감소는 아직 나타나지 않았습니다.</t>
-  </si>
-  <si>
     <t>- 당월 실적 2,633백만(예산 대비 103%)으로 예산을 소폭 초과했습니다.
 - 본사 1,752백만(예산 대비 95%)은 미달이나, 법인이 881백만(예산 대비 121%)으로 초과했습니다.
 - HUMAX(공통)이 467백만으로 1월(760백만) 대비 293백만 낮아졌습니다(1월 외부감사 착수금 소멸).</t>
@@ -145,20 +136,11 @@
 - 항목별로는 HUMAX(공통) 116%의 초과와 STB 66%의 미달이 차이의 대부분을 만듭니다.</t>
   </si>
   <si>
-    <t>- 누계 실적 2,566백만(국내 583백만 / 해외 1,983백만), 연간 예산의 18%로 2개월 경과 진도(17%)에 부합합니다.
-- 국내 17%, 해외 18%로 진도와 나란히 갑니다.
-- 비용의 58%인 1,481백만이 인건비라 인력 운영 계획에 따라 변동됩니다.</t>
-  </si>
-  <si>
     <t>- 누계 실적 1,227백만(예산 대비 116%)으로 예산을 170백만 초과했습니다.
 - Staff부문 +180백만이 대부분이며, 특허처리비 +77백만 초과가 주원인입니다.
 - 1월 일회성(외부감사 착수금 200백만)을 빼면 월 560→467백만으로 낮아지는 흐름입니다.</t>
   </si>
   <si>
-    <t>- 누계 실적 572백만(예산 대비 97%)으로 예산에 근접합니다.
-- 월 배부액은 272→300백만으로, 사옥 이전에 따른 감소는 아직 나타나지 않았습니다.</t>
-  </si>
-  <si>
     <t>- 당월 실적 2,592백만(예산 대비 97%)으로 예산 내에서 집행했습니다.
 - 본사 1,874백만(예산 대비 94%)은 미달, 법인 718백만(예산 대비 106%)은 초과입니다.
 - MOBILITY가 101백만으로 1~2월(61·50백만) 대비 두 배 수준으로 올랐습니다.</t>
@@ -169,65 +151,27 @@
 - 항목별로는 HUMAX(공통) 116%, MOBILITY 143%가 예산을 넘었고, STB 72%, 건물 94%는 밑돕니다.</t>
   </si>
   <si>
-    <t>- 누계 실적 3,770백만(국내 904백만 / 해외 2,866백만), 연간 예산의 26%로 3개월 경과 진도(25%)에 부합합니다.
-- 국내·해외 모두 26%로 진도와 나란히 갑니다.
-- 비용의 58%인 2,173백만이 인건비라 인력 운영 계획에 따라 변동됩니다.</t>
-  </si>
-  <si>
     <t>- 누계 실적 1,811백만(예산 대비 116%)으로 예산을 245백만 초과했습니다.
 - Staff부문 +240백만이 대부분이며, 특허처리비 +90백만 초과가 주원인입니다.
 - 1월 일회성(외부감사 착수금 200백만)을 빼면 월 560→467→584백만으로, 감소 추세는 확인되지 않습니다.</t>
   </si>
   <si>
-    <t>- 누계 실적 833백만(예산 대비 94%)으로 예산에 근접합니다.
-- 월 배부액은 272→300→261백만으로, 사옥 이전에 따른 감소는 아직 나타나지 않았습니다.</t>
-  </si>
-  <si>
-    <t>- 당월 실적 2,526백만(예산 대비 96%)으로 예산 내에서 집행했습니다.
-- 본사 1,868백만(예산 대비 94%)은 미달, 법인 658백만(예산 대비 104%)은 소폭 초과입니다.
-- 건물이 135백만으로 1~3월 평균 278백만의 절반 아래로 떨어져, 사옥 이전 효과가 나타나기 시작했습니다.</t>
-  </si>
-  <si>
     <t>- 누계 실적 10,568백만(예산 대비 95%)으로 예산 내에서 집행 중입니다.
 - 본사 7,514백만(예산 대비 91%)은 미달, 법인 3,055백만(예산 대비 109%)은 초과로 방향이 엇갈립니다.
 - 항목별로는 HUMAX(공통) 115%, EVCS(국내) 107%가 예산을 넘었고, 건물 81%, STB 83%, EVCS(해외) 92%는 밑돕니다.</t>
   </si>
   <si>
-    <t>- 누계 실적 4,972백만(국내 1,269백만 / 해외 3,703백만), 연간 예산의 34%로 4개월 경과 진도(33%)에 부합합니다.
-- 국내는 연간 예산의 36%를 써 진도를 앞서고, 월 배부액도 269→365백만으로 늘어 축소 기조와 반대입니다.
-- 해외는 33%로 진도에 맞으며, 비용의 57%인 2,817백만이 인건비라 인력 운영 계획에 따라 변동됩니다.</t>
-  </si>
-  <si>
-    <t>- 당월 실적 2,444백만(예산 대비 102%)으로 예산 수준에서 집행했습니다.
-- 본사 1,804백만(예산 대비 100%)은 계획대로이나, 법인이 640백만(예산 대비 108%)으로 초과했습니다.
-- HUMAX(공통)이 716백만으로 1~4월 평균 602백만을 웃돌았고, 건물은 121백만으로 사옥 이전 후 낮은 수준을 유지합니다.</t>
-  </si>
-  <si>
     <t>- 누계 실적 13,012백만(예산 대비 97%)으로 예산 내에서 집행 중입니다.
 - 본사 9,318백만(예산 대비 93%)은 미달, 법인 3,694백만(예산 대비 108%)은 초과로 방향이 엇갈립니다.
 - 항목별로는 HUMAX(공통) 121%, EVCS(국내) 110%가 예산을 넘었고, 건물 72%, STB 85%, EVCS(해외) 92%는 밑돕니다.</t>
   </si>
   <si>
-    <t>- 누계 실적 6,161백만(국내 1,612백만 / 해외 4,549백만), 연간 예산의 42%로 5개월 경과 진도(42%)에 부합합니다.
-- 국내는 연간 예산의 46%를 써 진도를 앞서고, 월 배부액도 269→343백만으로 늘어 축소 기조와 반대입니다.
-- 해외는 41%로 진도에 맞으며, 비용의 56%인 3,439백만이 인건비라 인력 운영 계획에 따라 변동됩니다.</t>
-  </si>
-  <si>
     <t>- 누계 실적 15,549백만(예산 대비 97%)으로 예산 내에서 집행 중입니다.
 - 본사 11,065백만(예산 대비 92%)은 미달, 법인 4,484백만(예산 대비 112%)은 초과로 방향이 엇갈립니다.
 - 항목별로는 HUMAX(공통) 119%, EVCS(국내) 108%가 예산을 넘었고, 건물 67%, STB 90%, EVCS(해외) 94%는 밑돕니다.</t>
   </si>
   <si>
-    <t>- 누계 실적 7,440백만(국내 1,973백만 / 해외 5,468백만), 연간 예산의 51%로 6개월 경과 진도(50%)에 부합합니다.
-- 국내는 연간 예산의 57%를 써 진도를 앞서고, 월 배부액도 269→361백만으로 늘어 축소 기조와 반대입니다.
-- 해외는 49%로 진도에 맞으며, 비용의 56%인 4,130백만이 인건비라 인력 운영 계획에 따라 변동됩니다.</t>
-  </si>
-  <si>
     <t>- 1월, 5월 일회성 집행: 26년 외부감사 착수금 200백만(1월), 15차 주식선택권 취소 216백만(5월). 제외 시 HUMAX(공통) 월 배부액은 467~598백만 범위입니다.</t>
-  </si>
-  <si>
-    <t>- 누계 실적 493백만(예산 대비 49%)으로 예산을 521백만 밑돕니다.
-- Media그룹 -533백만(외주개발용역비 -509)이 주원인으로, 연초 외주개발 집행이 계획보다 늦습니다.</t>
   </si>
   <si>
     <t>- 누계 실적 975백만(예산 대비 66%)으로 예산을 499백만 밑돕니다.
@@ -248,11 +192,6 @@
 - 1월 일회성 집행으로 배부액 상승: 26년 외부감사 착수금 200백만(1월). 제외 시 월 560→467→584→598백만입니다.</t>
   </si>
   <si>
-    <t>- 누계 실적 968백만(예산 대비 81%)으로 예산을 231백만 밑돕니다.
-- 감가상각비 -163백만, 수도광열비 -75 미달이 주원인입니다.
-- 1~3월 평균 278백만 → 4월 135백만으로 사옥 이전에 따른 감소가 시작됐습니다.</t>
-  </si>
-  <si>
     <t>- 누계 실적 2,381백만(예산 대비 85%)으로 예산을 425백만 밑돕니다.
 - Media그룹 -469백만(외주개발용역비 -525)이 주원인이며, 보정 후 월 441~493백만으로 평탄해 감소 추세는 아직 없습니다.
 - 4월, 5월 트렌드 왜곡: STB License Fee/Nagra 84백만 4월 기표 후 5월 reverse (선급비용 조정 시기 오류)</t>
@@ -263,29 +202,90 @@
 - 1월, 5월 일회성 집행으로 배부액 상승: 26년 외부감사 착수금 200백만(1월), 15차 주식선택권 취소 216백만(5월)</t>
   </si>
   <si>
-    <t>- 누계 실적 1,089백만(예산 대비 72%)으로 예산을 416백만 밑돕니다.
-- 감가상각비 -326백만, 수도광열비 -168 미달이 주원인입니다(임차료 +91 초과).
-- 1~3월 평균 278백만 → 4~5월 평균 128백만으로 사옥 이전에 따른 계단식 감소가 확인됩니다.</t>
-  </si>
-  <si>
     <t>- 누계 실적 2,916백만(예산 대비 90%)으로 예산을 336백만 밑돕니다.
 - Media그룹 -454백만(외주개발용역비 -526)이 주원인이며, 보정 후 월 441~536백만으로 감소 추세는 아직 없습니다.
 - 4월, 5월 트렌드 왜곡: STB License Fee/Nagra 84백만 4월 기표 후 5월 reverse (선급비용 조정 시기 오류)</t>
   </si>
   <si>
+    <t>- 누계 실적 1,233백만(예산 대비 100%)은 연간 예산의 8%로 1개월 경과 진도(8%)에 부합합니다.
+- 국내 269백만은 연간 예산의 8%이며, 첫 달이라 아직 추이는 판단할 수 없습니다.
+- 해외 963백만은 연간 예산의 9%이며, 비용의 58%인 720백만이 인건비입니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 493백만(예산 대비 49%)으로 예산을 521백만 밑돕니다.
+- Media그룹 -533백만(외주개발용역비 -509)이 미달의 대부분입니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 272백만(예산 대비 91%)으로 예산에 소폭 미달합니다.
+- Staff부문 -26백만으로 차이가 작습니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 2,566백만(예산 대비 100%)은 연간 예산의 18%로 2개월 경과 진도(17%)에 부합합니다.
+- 국내 583백만은 연간 예산의 17%이고, 월 배부액도 269→314백만으로 증가 추세입니다.
+- 해외 1,983백만은 연간 예산의 18%이며, 비용의 58%인 1,481백만이 인건비입니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 572백만(예산 대비 97%)으로 예산에 근접합니다.
+- 월 배부액은 272→300백만으로 아직 줄지 않았습니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 3,770백만(예산 대비 97%)은 연간 예산의 26%로 3개월 경과 진도(25%)에 부합합니다.
+- 국내 904백만은 연간 예산의 26%로 진도를 앞서고, 월 배부액도 269→321백만으로 증가 추세입니다.
+- 해외 2,866백만은 연간 예산의 26%이며, 비용의 58%인 2,173백만이 인건비입니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 833백만(예산 대비 94%)으로 예산에 근접합니다.
+- 월 배부액은 272→300→261백만으로 큰 변화가 없습니다.</t>
+  </si>
+  <si>
+    <t>- 당월 실적 2,526백만(예산 대비 96%)으로 예산 내에서 집행했습니다.
+- 본사 1,868백만(예산 대비 94%)은 미달, 법인 658백만(예산 대비 104%)은 소폭 초과입니다.
+- 건물이 135백만으로 1~3월 평균 278백만의 절반 아래로 떨어졌습니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 4,972백만(예산 대비 95%)은 연간 예산의 34%로 4개월 경과 진도(33%)에 부합합니다.
+- 국내 1,269백만은 연간 예산의 36%로 진도를 앞서고, 월 배부액도 269→365백만으로 증가 추세입니다.
+- 해외 3,703백만은 연간 예산의 33%이며, 비용의 57%인 2,817백만이 인건비입니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 968백만(예산 대비 81%)으로 예산을 231백만 밑돕니다.
+- 감가상각비 -163백만, 수도광열비 -75 미달이 주원인입니다.
+- 1~3월 평균 278백만 → 4월 135백만으로 절반 아래로 떨어졌습니다.</t>
+  </si>
+  <si>
+    <t>- 당월 실적 2,444백만(예산 대비 102%)으로 예산 수준에서 집행했습니다.
+- 본사 1,804백만(예산 대비 100%), 법인 640백만(예산 대비 108%)으로 법인이 초과했습니다.
+- HUMAX(공통)이 716백만으로 1~4월 평균 602백만을 웃돌았고, 건물은 121백만으로 4월(135백만)에 이어 낮은 수준입니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 6,161백만(예산 대비 96%)은 연간 예산의 42%로 5개월 경과 진도(42%)에 부합합니다.
+- 국내 1,612백만은 연간 예산의 46%로 진도를 앞서고, 월 배부액도 269→343백만으로 증가 추세입니다.
+- 해외 4,549백만은 연간 예산의 41%이며, 비용의 56%인 3,439백만이 인건비입니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 1,089백만(예산 대비 72%)으로 예산을 416백만 밑돕니다.
+- 감가상각비 -326백만, 수도광열비 -168 미달이 주원인입니다(임차료 +91 초과).
+- 1~3월 평균 278백만 → 4~5월 평균 128백만으로 4월부터 계단식으로 낮아졌습니다.</t>
+  </si>
+  <si>
+    <t>- 당월 실적 2,537백만(예산 대비 100%)으로 예산에 부합합니다.
+- 본사 1,747백만(예산 대비 91%)은 미달, 법인 790백만(예산 대비 131%)은 초과로 방향이 엇갈립니다.
+- HUMAX(공통)은 541백만으로 5월(716백만) 대비 175백만 줄었고, STB는 536백만으로 1~5월 평균(476백만)을 60백만 웃돌았습니다.</t>
+  </si>
+  <si>
+    <t>- 누계 실적 7,440백만(예산 대비 97%)은 연간 예산의 51%로 6개월 경과 진도(50%)에 부합합니다.
+- 국내 1,973백만은 연간 예산의 57%로 진도를 앞서고, 월 배부액도 269→361백만으로 증가 추세입니다.
+- 해외 5,468백만은 연간 예산의 49%이며, 비용의 56%인 4,130백만이 인건비입니다.</t>
+  </si>
+  <si>
     <t>- 누계 실적 3,666백만(예산 대비 119%)으로 예산을 586백만 초과했습니다.
-- Staff부문 +466백만(급여 +217, 특허처리비 +105), HBR +124백만 초과가 주원인으로, 감소 추세 관리가 필요합니다.
+- Staff부문 +466백만(급여 +217, 특허처리비 +105), HBR +124백만이 초과의 대부분입니다.
 - 1월, 5월 일회성 집행으로 배부액 상승: 26년 외부감사 착수금 200백만(1월), 15차 주식선택권 취소 216백만(5월)</t>
   </si>
   <si>
     <t>- 누계 실적 1,211백만(예산 대비 67%)으로 예산을 599백만 밑돕니다.
 - 감가상각비 -489백만, 수도광열비 -254 미달이 주원인입니다(임차료 +136 초과).
-- 1~3월 평균 278백만 → 4~6월 평균 126백만으로 사옥 이전에 따른 계단식 감소가 확인됩니다.</t>
-  </si>
-  <si>
-    <t>- 당월 실적 2,537백만(예산 대비 100%)으로 예산에 부합합니다.
-- 본사 1,747백만(예산 대비 91%)은 미달, 법인 790백만(예산 대비 131%)은 초과로 방향이 엇갈립니다.
-- HUMAX(공통)은 541백만으로 5월(716백만) 대비 175백만 낮아졌고, STB는 536백만으로 1~5월 평균 476백만을 웃돌았습니다.</t>
+- 1~3월 평균 278백만 → 4~6월 평균 126백만으로 4월부터 계단식으로 낮아졌습니다.</t>
   </si>
 </sst>
 </file>
@@ -762,7 +762,7 @@
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="5" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="33" x14ac:dyDescent="0.3">
@@ -776,7 +776,7 @@
         <v>7</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -790,7 +790,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="33" x14ac:dyDescent="0.3">
@@ -804,7 +804,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -816,7 +816,7 @@
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -828,7 +828,7 @@
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -840,7 +840,7 @@
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="7" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="33" x14ac:dyDescent="0.3">
@@ -854,7 +854,7 @@
         <v>7</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -868,7 +868,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="33" x14ac:dyDescent="0.3">
@@ -882,7 +882,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -894,7 +894,7 @@
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -906,7 +906,7 @@
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="5" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -918,7 +918,7 @@
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="5" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -932,7 +932,7 @@
         <v>7</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -946,7 +946,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="33" x14ac:dyDescent="0.3">
@@ -960,7 +960,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -972,7 +972,7 @@
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="7" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="66" x14ac:dyDescent="0.3">
@@ -984,7 +984,7 @@
       </c>
       <c r="C21" s="6"/>
       <c r="D21" s="7" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -996,7 +996,7 @@
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="7" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="66" x14ac:dyDescent="0.3">
@@ -1010,7 +1010,7 @@
         <v>7</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="66" x14ac:dyDescent="0.3">
@@ -1024,7 +1024,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="5" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="66" x14ac:dyDescent="0.3">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="C27" s="4"/>
       <c r="D27" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="C28" s="4"/>
       <c r="D28" s="5" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="66" x14ac:dyDescent="0.3">
@@ -1088,7 +1088,7 @@
         <v>7</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -1102,7 +1102,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="66" x14ac:dyDescent="0.3">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="C33" s="6"/>
       <c r="D33" s="7" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="7" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="66" x14ac:dyDescent="0.3">
@@ -1166,10 +1166,10 @@
         <v>7</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="66" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>6</v>
       </c>
@@ -1180,7 +1180,7 @@
         <v>8</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -1194,7 +1194,7 @@
         <v>9</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="33" x14ac:dyDescent="0.3">
@@ -1206,7 +1206,7 @@
         <v>10</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6367479-BB67-4BF3-ADEC-7078DC9B9312}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31C0AD84-E584-4747-A895-133007EFBB64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31335" yWindow="4860" windowWidth="11160" windowHeight="6315" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
+    <workbookView xWindow="28680" yWindow="-885" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -111,181 +111,217 @@
     <t>4월 누계</t>
   </si>
   <si>
-    <t>- 당월 실적 2,818백만(예산 대비 88%)으로 예산에 미달합니다.
-- 본사 2,020백만(예산 대비 83%)이 미달을 주도했고, 법인은 798백만(예산 대비 102%)으로 예산 수준입니다.
-- STB는 예산 대비 49%(493백만)에 그친 반면, HUMAX(공통)은 760백만으로 외부감사 착수금 200백만이 반영됐습니다.</t>
-  </si>
-  <si>
-    <t>- 누계 실적 2,818백만(예산 대비 88%)으로 예산 내에서 집행 중입니다.
-- 본사 2,020백만(예산 대비 83%)은 미달, 법인 798백만(예산 대비 102%)은 예산 수준입니다.
-- 항목별로는 STB 49%의 미달과 HUMAX(공통) 122%의 초과가 차이의 대부분을 만듭니다.</t>
-  </si>
-  <si>
-    <t>- 누계 실적 760백만(예산 대비 122%)으로 예산을 138백만 초과했습니다.
-- Staff부문 +138백만이 대부분이며, 특허처리비 +64백만 초과가 주원인입니다.
-- 1월 일회성 집행으로 배부액 상승: 26년 외부감사 착수금 200백만(1월)</t>
-  </si>
-  <si>
-    <t>- 당월 실적 2,633백만(예산 대비 103%)으로 예산을 소폭 초과했습니다.
-- 본사 1,752백만(예산 대비 95%)은 미달이나, 법인이 881백만(예산 대비 121%)으로 초과했습니다.
-- HUMAX(공통)이 467백만으로 1월(760백만) 대비 293백만 낮아졌습니다(1월 외부감사 착수금 소멸).</t>
-  </si>
-  <si>
-    <t>- 누계 실적 5,451백만(예산 대비 94%)으로 예산 내에서 집행 중입니다.
-- 본사 3,772백만(예산 대비 88%)은 미달, 법인 1,679백만(예산 대비 111%)은 초과로 방향이 엇갈립니다.
-- 항목별로는 HUMAX(공통) 116%의 초과와 STB 66%의 미달이 차이의 대부분을 만듭니다.</t>
-  </si>
-  <si>
-    <t>- 누계 실적 1,227백만(예산 대비 116%)으로 예산을 170백만 초과했습니다.
-- Staff부문 +180백만이 대부분이며, 특허처리비 +77백만 초과가 주원인입니다.
-- 1월 일회성(외부감사 착수금 200백만)을 빼면 월 560→467백만으로 낮아지는 흐름입니다.</t>
-  </si>
-  <si>
-    <t>- 당월 실적 2,592백만(예산 대비 97%)으로 예산 내에서 집행했습니다.
-- 본사 1,874백만(예산 대비 94%)은 미달, 법인 718백만(예산 대비 106%)은 초과입니다.
-- MOBILITY가 101백만으로 1~2월(61·50백만) 대비 두 배 수준으로 올랐습니다.</t>
-  </si>
-  <si>
-    <t>- 누계 실적 8,043백만(예산 대비 95%)으로 예산 내에서 집행 중입니다.
-- 본사 5,646백만(예산 대비 90%)은 미달, 법인 2,397백만(예산 대비 110%)은 초과로 방향이 엇갈립니다.
-- 항목별로는 HUMAX(공통) 116%, MOBILITY 143%가 예산을 넘었고, STB 72%, 건물 94%는 밑돕니다.</t>
-  </si>
-  <si>
-    <t>- 누계 실적 1,811백만(예산 대비 116%)으로 예산을 245백만 초과했습니다.
-- Staff부문 +240백만이 대부분이며, 특허처리비 +90백만 초과가 주원인입니다.
-- 1월 일회성(외부감사 착수금 200백만)을 빼면 월 560→467→584백만으로, 감소 추세는 확인되지 않습니다.</t>
-  </si>
-  <si>
-    <t>- 누계 실적 10,568백만(예산 대비 95%)으로 예산 내에서 집행 중입니다.
-- 본사 7,514백만(예산 대비 91%)은 미달, 법인 3,055백만(예산 대비 109%)은 초과로 방향이 엇갈립니다.
-- 항목별로는 HUMAX(공통) 115%, EVCS(국내) 107%가 예산을 넘었고, 건물 81%, STB 83%, EVCS(해외) 92%는 밑돕니다.</t>
-  </si>
-  <si>
-    <t>- 누계 실적 13,012백만(예산 대비 97%)으로 예산 내에서 집행 중입니다.
-- 본사 9,318백만(예산 대비 93%)은 미달, 법인 3,694백만(예산 대비 108%)은 초과로 방향이 엇갈립니다.
-- 항목별로는 HUMAX(공통) 121%, EVCS(국내) 110%가 예산을 넘었고, 건물 72%, STB 85%, EVCS(해외) 92%는 밑돕니다.</t>
-  </si>
-  <si>
-    <t>- 누계 실적 15,549백만(예산 대비 97%)으로 예산 내에서 집행 중입니다.
-- 본사 11,065백만(예산 대비 92%)은 미달, 법인 4,484백만(예산 대비 112%)은 초과로 방향이 엇갈립니다.
-- 항목별로는 HUMAX(공통) 119%, EVCS(국내) 108%가 예산을 넘었고, 건물 67%, STB 90%, EVCS(해외) 94%는 밑돕니다.</t>
-  </si>
-  <si>
     <t>- 1월, 5월 일회성 집행: 26년 외부감사 착수금 200백만(1월), 15차 주식선택권 취소 216백만(5월). 제외 시 HUMAX(공통) 월 배부액은 467~598백만 범위입니다.</t>
   </si>
   <si>
-    <t>- 누계 실적 975백만(예산 대비 66%)으로 예산을 499백만 밑돕니다.
-- Media그룹 -527백만(외주개발용역비 -513)이 주원인이며, 월 배부액은 493→483백만으로 큰 변화가 없습니다.</t>
-  </si>
-  <si>
-    <t>- 누계 실적 1,417백만(예산 대비 72%)으로 예산을 541백만 밑돕니다.
-- Media그룹 -522백만(외주개발용역비 -533)이 주원인이며, 월 배부액은 493→483→441백만으로 완만히 낮아집니다.</t>
-  </si>
-  <si>
-    <t>- 누계 실적 1,982백만(예산 대비 83%)으로 예산을 410백만 밑돕니다.
-- Media그룹 -426백만(외주개발용역비 -533)이 주원인이며, HUK는 +79백만 초과입니다.
-- 4월 트렌드 왜곡: STB License Fee/Nagra 84백만이 4월에 기표돼 배부액이 565백만으로 부풀었습니다(5월 reverse, 선급비용 조정 시기 오류)</t>
-  </si>
-  <si>
-    <t>- 누계 실적 2,409백만(예산 대비 115%)으로 예산을 321백만 초과했습니다.
-- Staff부문 +300백만이 대부분이며, 지급수수료 +106·특허처리비 +105 초과가 주원인입니다.
-- 1월 일회성 집행으로 배부액 상승: 26년 외부감사 착수금 200백만(1월). 제외 시 월 560→467→584→598백만입니다.</t>
-  </si>
-  <si>
-    <t>- 누계 실적 2,381백만(예산 대비 85%)으로 예산을 425백만 밑돕니다.
-- Media그룹 -469백만(외주개발용역비 -525)이 주원인이며, 보정 후 월 441~493백만으로 평탄해 감소 추세는 아직 없습니다.
-- 4월, 5월 트렌드 왜곡: STB License Fee/Nagra 84백만 4월 기표 후 5월 reverse (선급비용 조정 시기 오류)</t>
-  </si>
-  <si>
-    <t>- 누계 실적 3,125백만(예산 대비 121%)으로 예산을 552백만 초과했습니다.
-- Staff부문 +516백만이 대부분이며, 급여 +208·특허처리비 +106·지급수수료 +100 초과가 주원인입니다.
-- 1월, 5월 일회성 집행으로 배부액 상승: 26년 외부감사 착수금 200백만(1월), 15차 주식선택권 취소 216백만(5월)</t>
-  </si>
-  <si>
-    <t>- 누계 실적 2,916백만(예산 대비 90%)으로 예산을 336백만 밑돕니다.
-- Media그룹 -454백만(외주개발용역비 -526)이 주원인이며, 보정 후 월 441~536백만으로 감소 추세는 아직 없습니다.
-- 4월, 5월 트렌드 왜곡: STB License Fee/Nagra 84백만 4월 기표 후 5월 reverse (선급비용 조정 시기 오류)</t>
-  </si>
-  <si>
-    <t>- 누계 실적 1,233백만(예산 대비 100%)은 연간 예산의 8%로 1개월 경과 진도(8%)에 부합합니다.
+    <t>- 당월 실적 2,818백만(집행률 88%)으로 예산에 미달합니다.
+- 본사 2,020백만(집행률 83%)이 예산 대비 미달을 주도했고, 법인은 798백만(집행률 102%)으로 예산 수준입니다.
+- STB는 집행률 49%(493백만)에 그친 반면, HUMAX(공통)은 760백만으로 외부감사 착수금 200백만이 반영됐습니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 2,818백만(집행률 88%)으로 예산 내에서 집행 중입니다.
+- 본사 2,020백만(집행률 83%)은 예산 대비 미달, 법인 798백만(집행률 102%)은 예산 수준입니다.
+- 항목별 집행률에서는 HUMAX(공통) 122%로 예산을 초과하였고, STB 49%는 예산을 밑돌아 차이의 대부분을 만듭니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 1,233백만(집행률 100%)은 연간 예산의 8%로 1개월 경과 진도(8%)에 부합합니다.
 - 국내 269백만은 연간 예산의 8%이며, 첫 달이라 아직 추이는 판단할 수 없습니다.
 - 해외 963백만은 연간 예산의 9%이며, 비용의 58%인 720백만이 인건비입니다.</t>
-  </si>
-  <si>
-    <t>- 누계 실적 493백만(예산 대비 49%)으로 예산을 521백만 밑돕니다.
-- Media그룹 -533백만(외주개발용역비 -509)이 미달의 대부분입니다.</t>
-  </si>
-  <si>
-    <t>- 누계 실적 272백만(예산 대비 91%)으로 예산에 소폭 미달합니다.
-- Staff부문 -26백만으로 차이가 작습니다.</t>
-  </si>
-  <si>
-    <t>- 누계 실적 2,566백만(예산 대비 100%)은 연간 예산의 18%로 2개월 경과 진도(17%)에 부합합니다.
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 493백만(집행률 49%)으로 예산을 521백만 밑돕니다.
+- 예산 대비 Media그룹 -533백만(외주개발용역비 -509)이 미달의 대부분입니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 760백만(집행률 122%)으로 예산을 138백만 초과했습니다.
+- 예산 대비 Staff부문 +138백만이 대부분이며, 특허처리비 +64백만 초과가 주원인입니다.
+- 1월 일회성 집행으로 배부액 상승: 26년 외부감사 착수금 200백만(1월)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 272백만(집행률 91%)으로 예산에 소폭 미달합니다.
+- 예산 대비 Staff부문 -26백만으로 차이가 작습니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 당월 실적 2,633백만(집행률 103%)으로 예산을 소폭 초과했습니다.
+- 본사 1,752백만(집행률 95%)은 예산 대비 미달이나, 법인이 881백만(집행률 121%)으로 예산을 초과했습니다.
+- HUMAX(공통)이 467백만으로 1월(760백만) 대비 293백만 낮아졌습니다(1월 외부감사 착수금 소멸).</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 5,451백만(집행률 94%)으로 예산 내에서 집행 중입니다.
+- 본사 3,772백만(집행률 88%)은 예산 대비 미달, 법인 1,679백만(집행률 111%)은 초과로 방향이 엇갈립니다.
+- 항목별 집행률에서는 HUMAX(공통) 116%로 예산을 초과하였고, STB 66%는 예산을 밑돌아 차이의 대부분을 만듭니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 2,566백만(집행률 100%)은 연간 예산의 18%로 2개월 경과 진도(17%)에 부합합니다.
 - 국내 583백만은 연간 예산의 17%이고, 월 배부액도 269→314백만으로 증가 추세입니다.
 - 해외 1,983백만은 연간 예산의 18%이며, 비용의 58%인 1,481백만이 인건비입니다.</t>
-  </si>
-  <si>
-    <t>- 누계 실적 572백만(예산 대비 97%)으로 예산에 근접합니다.
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 975백만(집행률 66%)으로 예산을 499백만 밑돕니다.
+- 예산 대비 Media그룹 -527백만(외주개발용역비 -513)이 주원인이며, 월 배부액은 493→483백만으로 큰 변화가 없습니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 1,227백만(집행률 116%)으로 예산을 170백만 초과했습니다.
+- 예산 대비 Staff부문 +180백만이 대부분이며, 특허처리비 +77백만 초과가 주원인입니다.
+- 1월 일회성(외부감사 착수금 200백만)을 빼면 월 560→467백만으로 낮아지는 흐름입니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 572백만(집행률 97%)으로 예산에 근접합니다.
 - 월 배부액은 272→300백만으로 아직 줄지 않았습니다.</t>
-  </si>
-  <si>
-    <t>- 누계 실적 3,770백만(예산 대비 97%)은 연간 예산의 26%로 3개월 경과 진도(25%)에 부합합니다.
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 당월 실적 2,592백만(집행률 97%)으로 예산 내에서 집행했습니다.
+- 본사 1,874백만(집행률 94%)은 예산 대비 미달, 법인 718백만(집행률 106%)은 초과입니다.
+- MOBILITY가 101백만으로 1~2월(61·50백만) 대비 두 배 수준으로 올랐습니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 8,043백만(집행률 95%)으로 예산 내에서 집행 중입니다.
+- 본사 5,646백만(집행률 90%)은 예산 대비 미달, 법인 2,397백만(집행률 110%)은 초과로 방향이 엇갈립니다.
+- 항목별 집행률에서는 HUMAX(공통) 116%, MOBILITY 143%로 예산을 초과하였고, STB 72%, 건물 94%는 예산을 밑돕니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 3,770백만(집행률 97%)은 연간 예산의 26%로 3개월 경과 진도(25%)에 부합합니다.
 - 국내 904백만은 연간 예산의 26%로 진도를 앞서고, 월 배부액도 269→321백만으로 증가 추세입니다.
 - 해외 2,866백만은 연간 예산의 26%이며, 비용의 58%인 2,173백만이 인건비입니다.</t>
-  </si>
-  <si>
-    <t>- 누계 실적 833백만(예산 대비 94%)으로 예산에 근접합니다.
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 1,417백만(집행률 72%)으로 예산을 541백만 밑돕니다.
+- 예산 대비 Media그룹 -522백만(외주개발용역비 -533)이 주원인이며, 월 배부액은 493→483→441백만으로 완만히 낮아집니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 1,811백만(집행률 116%)으로 예산을 245백만 초과했습니다.
+- 예산 대비 Staff부문 +240백만이 대부분이며, 특허처리비 +90백만 초과가 주원인입니다.
+- 1월 일회성(외부감사 착수금 200백만)을 빼면 월 560→467→584백만으로, 감소 추세는 확인되지 않습니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 833백만(집행률 94%)으로 예산에 근접합니다.
 - 월 배부액은 272→300→261백만으로 큰 변화가 없습니다.</t>
-  </si>
-  <si>
-    <t>- 당월 실적 2,526백만(예산 대비 96%)으로 예산 내에서 집행했습니다.
-- 본사 1,868백만(예산 대비 94%)은 미달, 법인 658백만(예산 대비 104%)은 소폭 초과입니다.
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 당월 실적 2,526백만(집행률 96%)으로 예산 내에서 집행했습니다.
+- 본사 1,868백만(집행률 94%)은 예산 대비 미달, 법인 658백만(집행률 104%)은 소폭 초과입니다.
 - 건물이 135백만으로 1~3월 평균 278백만의 절반 아래로 떨어졌습니다.</t>
-  </si>
-  <si>
-    <t>- 누계 실적 4,972백만(예산 대비 95%)은 연간 예산의 34%로 4개월 경과 진도(33%)에 부합합니다.
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 10,568백만(집행률 95%)으로 예산 내에서 집행 중입니다.
+- 본사 7,514백만(집행률 91%)은 예산 대비 미달, 법인 3,055백만(집행률 109%)은 초과로 방향이 엇갈립니다.
+- 항목별 집행률에서는 HUMAX(공통) 115%, EVCS(국내) 107%로 예산을 초과하였고, 건물 81%, STB 83%, EVCS(해외) 92%는 예산을 밑돕니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 4,972백만(집행률 95%)은 연간 예산의 34%로 4개월 경과 진도(33%)에 부합합니다.
 - 국내 1,269백만은 연간 예산의 36%로 진도를 앞서고, 월 배부액도 269→365백만으로 증가 추세입니다.
 - 해외 3,703백만은 연간 예산의 33%이며, 비용의 57%인 2,817백만이 인건비입니다.</t>
-  </si>
-  <si>
-    <t>- 누계 실적 968백만(예산 대비 81%)으로 예산을 231백만 밑돕니다.
-- 감가상각비 -163백만, 수도광열비 -75 미달이 주원인입니다.
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 1,982백만(집행률 83%)으로 예산을 410백만 밑돕니다.
+- 예산 대비 Media그룹 -426백만(외주개발용역비 -533)이 주원인이며, HUK는 +79백만 초과입니다.
+- 4월 트렌드 왜곡: STB License Fee/Nagra 84백만이 4월에 기표돼 배부액이 565백만으로 부풀었습니다(5월 reverse, 선급비용 조정 시기 오류)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 2,409백만(집행률 115%)으로 예산을 321백만 초과했습니다.
+- 예산 대비 Staff부문 +300백만이 대부분이며, 지급수수료 +106·특허처리비 +105 초과가 주원인입니다.
+- 1월 일회성 집행으로 배부액 상승: 26년 외부감사 착수금 200백만(1월). 제외 시 월 560→467→584→598백만입니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 968백만(집행률 81%)으로 예산을 231백만 밑돕니다.
+- 예산 대비 감가상각비 -163백만, 수도광열비 -75 미달이 주원인입니다.
 - 1~3월 평균 278백만 → 4월 135백만으로 절반 아래로 떨어졌습니다.</t>
-  </si>
-  <si>
-    <t>- 당월 실적 2,444백만(예산 대비 102%)으로 예산 수준에서 집행했습니다.
-- 본사 1,804백만(예산 대비 100%), 법인 640백만(예산 대비 108%)으로 법인이 초과했습니다.
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 당월 실적 2,444백만(집행률 102%)으로 예산 수준에서 집행했습니다.
+- 본사 1,804백만(집행률 100%), 법인 640백만(집행률 108%)으로 법인이 예산을 초과했습니다.
 - HUMAX(공통)이 716백만으로 1~4월 평균 602백만을 웃돌았고, 건물은 121백만으로 4월(135백만)에 이어 낮은 수준입니다.</t>
-  </si>
-  <si>
-    <t>- 누계 실적 6,161백만(예산 대비 96%)은 연간 예산의 42%로 5개월 경과 진도(42%)에 부합합니다.
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 13,012백만(집행률 97%)으로 예산 내에서 집행 중입니다.
+- 본사 9,318백만(집행률 93%)은 예산 대비 미달, 법인 3,694백만(집행률 108%)은 초과로 방향이 엇갈립니다.
+- 항목별 집행률에서는 HUMAX(공통) 121%, EVCS(국내) 110%로 예산을 초과하였고, 건물 72%, STB 85%, EVCS(해외) 92%는 예산을 밑돕니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 6,161백만(집행률 96%)은 연간 예산의 42%로 5개월 경과 진도(42%)에 부합합니다.
 - 국내 1,612백만은 연간 예산의 46%로 진도를 앞서고, 월 배부액도 269→343백만으로 증가 추세입니다.
 - 해외 4,549백만은 연간 예산의 41%이며, 비용의 56%인 3,439백만이 인건비입니다.</t>
-  </si>
-  <si>
-    <t>- 누계 실적 1,089백만(예산 대비 72%)으로 예산을 416백만 밑돕니다.
-- 감가상각비 -326백만, 수도광열비 -168 미달이 주원인입니다(임차료 +91 초과).
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 2,381백만(집행률 85%)으로 예산을 425백만 밑돕니다.
+- 예산 대비 Media그룹 -469백만(외주개발용역비 -525)이 주원인이며, 보정 후 월 441~493백만으로 평탄해 감소 추세는 아직 없습니다.
+- 4월, 5월 트렌드 왜곡: STB License Fee/Nagra 84백만 4월 기표 후 5월 reverse (선급비용 조정 시기 오류)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 3,125백만(집행률 121%)으로 예산을 552백만 초과했습니다.
+- 예산 대비 Staff부문 +516백만이 대부분이며, 급여 +208·특허처리비 +106·지급수수료 +100 초과가 주원인입니다.
+- 1월, 5월 일회성 집행으로 배부액 상승: 26년 외부감사 착수금 200백만(1월), 15차 주식선택권 취소 216백만(5월)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 1,089백만(집행률 72%)으로 예산을 416백만 밑돕니다.
+- 예산 대비 감가상각비 -326백만, 수도광열비 -168 미달이 주원인입니다(임차료 +91 초과).
 - 1~3월 평균 278백만 → 4~5월 평균 128백만으로 4월부터 계단식으로 낮아졌습니다.</t>
-  </si>
-  <si>
-    <t>- 당월 실적 2,537백만(예산 대비 100%)으로 예산에 부합합니다.
-- 본사 1,747백만(예산 대비 91%)은 미달, 법인 790백만(예산 대비 131%)은 초과로 방향이 엇갈립니다.
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 당월 실적 2,537백만(집행률 100%)으로 예산에 부합합니다.
+- 본사 1,747백만(집행률 91%)은 예산 대비 미달, 법인 790백만(집행률 131%)은 초과로 방향이 엇갈립니다.
 - HUMAX(공통)은 541백만으로 5월(716백만) 대비 175백만 줄었고, STB는 536백만으로 1~5월 평균(476백만)을 60백만 웃돌았습니다.</t>
-  </si>
-  <si>
-    <t>- 누계 실적 7,440백만(예산 대비 97%)은 연간 예산의 51%로 6개월 경과 진도(50%)에 부합합니다.
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 15,549백만(집행률 97%)으로 예산 내에서 집행 중입니다.
+- 본사 11,065백만(집행률 92%)은 예산 대비 미달, 법인 4,484백만(집행률 112%)은 초과로 방향이 엇갈립니다.
+- 항목별 집행률에서는 HUMAX(공통) 119%, EVCS(국내) 108%로 예산을 초과하였고, 건물 67%, STB 90%, EVCS(해외) 94%는 예산을 밑돕니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 7,440백만(집행률 97%)은 연간 예산의 51%로 6개월 경과 진도(50%)에 부합합니다.
 - 국내 1,973백만은 연간 예산의 57%로 진도를 앞서고, 월 배부액도 269→361백만으로 증가 추세입니다.
 - 해외 5,468백만은 연간 예산의 49%이며, 비용의 56%인 4,130백만이 인건비입니다.</t>
-  </si>
-  <si>
-    <t>- 누계 실적 3,666백만(예산 대비 119%)으로 예산을 586백만 초과했습니다.
-- Staff부문 +466백만(급여 +217, 특허처리비 +105), HBR +124백만이 초과의 대부분입니다.
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 2,916백만(집행률 90%)으로 예산을 336백만 밑돕니다.
+- 예산 대비 Media그룹 -454백만(외주개발용역비 -526)이 주원인이며, 보정 후 월 441~536백만으로 감소 추세는 아직 없습니다.
+- 4월, 5월 트렌드 왜곡: STB License Fee/Nagra 84백만 4월 기표 후 5월 reverse (선급비용 조정 시기 오류)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 3,666백만(집행률 119%)으로 예산을 586백만 초과했습니다.
+- 예산 대비 Staff부문 +466백만(급여 +217, 특허처리비 +105), HBR +124백만이 초과의 대부분입니다.
 - 1월, 5월 일회성 집행으로 배부액 상승: 26년 외부감사 착수금 200백만(1월), 15차 주식선택권 취소 216백만(5월)</t>
-  </si>
-  <si>
-    <t>- 누계 실적 1,211백만(예산 대비 67%)으로 예산을 599백만 밑돕니다.
-- 감가상각비 -489백만, 수도광열비 -254 미달이 주원인입니다(임차료 +136 초과).
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 1,211백만(집행률 67%)으로 예산을 599백만 밑돕니다.
+- 예산 대비 감가상각비 -489백만, 수도광열비 -254 미달이 주원인입니다(임차료 +136 초과).
 - 1~3월 평균 278백만 → 4~6월 평균 126백만으로 4월부터 계단식으로 낮아졌습니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -738,10 +774,10 @@
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="66" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
@@ -750,7 +786,7 @@
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -762,7 +798,7 @@
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="5" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="33" x14ac:dyDescent="0.3">
@@ -776,7 +812,7 @@
         <v>7</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -790,7 +826,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="33" x14ac:dyDescent="0.3">
@@ -804,7 +840,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -816,10 +852,10 @@
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="66" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>4</v>
       </c>
@@ -828,7 +864,7 @@
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="7" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -840,10 +876,10 @@
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="33" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>6</v>
       </c>
@@ -854,7 +890,7 @@
         <v>7</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -868,7 +904,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="33" x14ac:dyDescent="0.3">
@@ -882,7 +918,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -894,10 +930,10 @@
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="66" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>4</v>
       </c>
@@ -906,7 +942,7 @@
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="5" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -918,7 +954,7 @@
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="5" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -932,7 +968,7 @@
         <v>7</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -946,7 +982,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="33" x14ac:dyDescent="0.3">
@@ -960,7 +996,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -972,7 +1008,7 @@
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="7" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="66" x14ac:dyDescent="0.3">
@@ -984,7 +1020,7 @@
       </c>
       <c r="C21" s="6"/>
       <c r="D21" s="7" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -996,7 +1032,7 @@
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="7" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="66" x14ac:dyDescent="0.3">
@@ -1010,7 +1046,7 @@
         <v>7</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="66" x14ac:dyDescent="0.3">
@@ -1024,7 +1060,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -1038,7 +1074,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="66" x14ac:dyDescent="0.3">
@@ -1050,7 +1086,7 @@
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="66" x14ac:dyDescent="0.3">
@@ -1062,7 +1098,7 @@
       </c>
       <c r="C27" s="4"/>
       <c r="D27" s="5" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -1074,7 +1110,7 @@
       </c>
       <c r="C28" s="4"/>
       <c r="D28" s="5" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="66" x14ac:dyDescent="0.3">
@@ -1088,10 +1124,10 @@
         <v>7</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="66" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>6</v>
       </c>
@@ -1102,7 +1138,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -1116,7 +1152,7 @@
         <v>9</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="66" x14ac:dyDescent="0.3">
@@ -1128,7 +1164,7 @@
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="66" x14ac:dyDescent="0.3">
@@ -1140,7 +1176,7 @@
       </c>
       <c r="C33" s="6"/>
       <c r="D33" s="7" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -1152,7 +1188,7 @@
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="66" x14ac:dyDescent="0.3">
@@ -1166,7 +1202,7 @@
         <v>7</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -1206,7 +1242,7 @@
         <v>10</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31C0AD84-E584-4747-A895-133007EFBB64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADA7D752-4141-4978-818B-81CD427F29FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-885" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Summary!$A$1:$D$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Summary!$A$1:$D$37</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="60">
   <si>
     <t>탭</t>
   </si>
@@ -72,9 +72,6 @@
     <t>건물</t>
   </si>
   <si>
-    <t>월별 배부액 추이</t>
-  </si>
-  <si>
     <t>5월</t>
   </si>
   <si>
@@ -111,216 +108,221 @@
     <t>4월 누계</t>
   </si>
   <si>
-    <t>- 1월, 5월 일회성 집행: 26년 외부감사 착수금 200백만(1월), 15차 주식선택권 취소 216백만(5월). 제외 시 HUMAX(공통) 월 배부액은 467~598백만 범위입니다.</t>
-  </si>
-  <si>
-    <t>- 당월 실적 2,818백만(집행률 88%)으로 예산에 미달합니다.
-- 본사 2,020백만(집행률 83%)이 예산 대비 미달을 주도했고, 법인은 798백만(집행률 102%)으로 예산 수준입니다.
-- STB는 집행률 49%(493백만)에 그친 반면, HUMAX(공통)은 760백만으로 외부감사 착수금 200백만이 반영됐습니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 2,818백만(집행률 88%)으로 예산 내에서 집행 중입니다.
-- 본사 2,020백만(집행률 83%)은 예산 대비 미달, 법인 798백만(집행률 102%)은 예산 수준입니다.
-- 항목별 집행률에서는 HUMAX(공통) 122%로 예산을 초과하였고, STB 49%는 예산을 밑돌아 차이의 대부분을 만듭니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 1,233백만(집행률 100%)은 연간 예산의 8%로 1개월 경과 진도(8%)에 부합합니다.
-- 국내 269백만은 연간 예산의 8%이며, 첫 달이라 아직 추이는 판단할 수 없습니다.
-- 해외 963백만은 연간 예산의 9%이며, 비용의 58%인 720백만이 인건비입니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 493백만(집행률 49%)으로 예산을 521백만 밑돕니다.
-- 예산 대비 Media그룹 -533백만(외주개발용역비 -509)이 미달의 대부분입니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 760백만(집행률 122%)으로 예산을 138백만 초과했습니다.
-- 예산 대비 Staff부문 +138백만이 대부분이며, 특허처리비 +64백만 초과가 주원인입니다.
-- 1월 일회성 집행으로 배부액 상승: 26년 외부감사 착수금 200백만(1월)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 272백만(집행률 91%)으로 예산에 소폭 미달합니다.
-- 예산 대비 Staff부문 -26백만으로 차이가 작습니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 당월 실적 2,633백만(집행률 103%)으로 예산을 소폭 초과했습니다.
-- 본사 1,752백만(집행률 95%)은 예산 대비 미달이나, 법인이 881백만(집행률 121%)으로 예산을 초과했습니다.
-- HUMAX(공통)이 467백만으로 1월(760백만) 대비 293백만 낮아졌습니다(1월 외부감사 착수금 소멸).</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 5,451백만(집행률 94%)으로 예산 내에서 집행 중입니다.
-- 본사 3,772백만(집행률 88%)은 예산 대비 미달, 법인 1,679백만(집행률 111%)은 초과로 방향이 엇갈립니다.
-- 항목별 집행률에서는 HUMAX(공통) 116%로 예산을 초과하였고, STB 66%는 예산을 밑돌아 차이의 대부분을 만듭니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 2,566백만(집행률 100%)은 연간 예산의 18%로 2개월 경과 진도(17%)에 부합합니다.
-- 국내 583백만은 연간 예산의 17%이고, 월 배부액도 269→314백만으로 증가 추세입니다.
-- 해외 1,983백만은 연간 예산의 18%이며, 비용의 58%인 1,481백만이 인건비입니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 975백만(집행률 66%)으로 예산을 499백만 밑돕니다.
-- 예산 대비 Media그룹 -527백만(외주개발용역비 -513)이 주원인이며, 월 배부액은 493→483백만으로 큰 변화가 없습니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 1,227백만(집행률 116%)으로 예산을 170백만 초과했습니다.
-- 예산 대비 Staff부문 +180백만이 대부분이며, 특허처리비 +77백만 초과가 주원인입니다.
-- 1월 일회성(외부감사 착수금 200백만)을 빼면 월 560→467백만으로 낮아지는 흐름입니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 572백만(집행률 97%)으로 예산에 근접합니다.
-- 월 배부액은 272→300백만으로 아직 줄지 않았습니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 당월 실적 2,592백만(집행률 97%)으로 예산 내에서 집행했습니다.
-- 본사 1,874백만(집행률 94%)은 예산 대비 미달, 법인 718백만(집행률 106%)은 초과입니다.
-- MOBILITY가 101백만으로 1~2월(61·50백만) 대비 두 배 수준으로 올랐습니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 8,043백만(집행률 95%)으로 예산 내에서 집행 중입니다.
-- 본사 5,646백만(집행률 90%)은 예산 대비 미달, 법인 2,397백만(집행률 110%)은 초과로 방향이 엇갈립니다.
-- 항목별 집행률에서는 HUMAX(공통) 116%, MOBILITY 143%로 예산을 초과하였고, STB 72%, 건물 94%는 예산을 밑돕니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 3,770백만(집행률 97%)은 연간 예산의 26%로 3개월 경과 진도(25%)에 부합합니다.
-- 국내 904백만은 연간 예산의 26%로 진도를 앞서고, 월 배부액도 269→321백만으로 증가 추세입니다.
-- 해외 2,866백만은 연간 예산의 26%이며, 비용의 58%인 2,173백만이 인건비입니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 1,417백만(집행률 72%)으로 예산을 541백만 밑돕니다.
-- 예산 대비 Media그룹 -522백만(외주개발용역비 -533)이 주원인이며, 월 배부액은 493→483→441백만으로 완만히 낮아집니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 1,811백만(집행률 116%)으로 예산을 245백만 초과했습니다.
-- 예산 대비 Staff부문 +240백만이 대부분이며, 특허처리비 +90백만 초과가 주원인입니다.
-- 1월 일회성(외부감사 착수금 200백만)을 빼면 월 560→467→584백만으로, 감소 추세는 확인되지 않습니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 833백만(집행률 94%)으로 예산에 근접합니다.
-- 월 배부액은 272→300→261백만으로 큰 변화가 없습니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 당월 실적 2,526백만(집행률 96%)으로 예산 내에서 집행했습니다.
-- 본사 1,868백만(집행률 94%)은 예산 대비 미달, 법인 658백만(집행률 104%)은 소폭 초과입니다.
-- 건물이 135백만으로 1~3월 평균 278백만의 절반 아래로 떨어졌습니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 10,568백만(집행률 95%)으로 예산 내에서 집행 중입니다.
-- 본사 7,514백만(집행률 91%)은 예산 대비 미달, 법인 3,055백만(집행률 109%)은 초과로 방향이 엇갈립니다.
-- 항목별 집행률에서는 HUMAX(공통) 115%, EVCS(국내) 107%로 예산을 초과하였고, 건물 81%, STB 83%, EVCS(해외) 92%는 예산을 밑돕니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 4,972백만(집행률 95%)은 연간 예산의 34%로 4개월 경과 진도(33%)에 부합합니다.
-- 국내 1,269백만은 연간 예산의 36%로 진도를 앞서고, 월 배부액도 269→365백만으로 증가 추세입니다.
-- 해외 3,703백만은 연간 예산의 33%이며, 비용의 57%인 2,817백만이 인건비입니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 1,982백만(집행률 83%)으로 예산을 410백만 밑돕니다.
-- 예산 대비 Media그룹 -426백만(외주개발용역비 -533)이 주원인이며, HUK는 +79백만 초과입니다.
-- 4월 트렌드 왜곡: STB License Fee/Nagra 84백만이 4월에 기표돼 배부액이 565백만으로 부풀었습니다(5월 reverse, 선급비용 조정 시기 오류)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 2,409백만(집행률 115%)으로 예산을 321백만 초과했습니다.
-- 예산 대비 Staff부문 +300백만이 대부분이며, 지급수수료 +106·특허처리비 +105 초과가 주원인입니다.
-- 1월 일회성 집행으로 배부액 상승: 26년 외부감사 착수금 200백만(1월). 제외 시 월 560→467→584→598백만입니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 968백만(집행률 81%)으로 예산을 231백만 밑돕니다.
-- 예산 대비 감가상각비 -163백만, 수도광열비 -75 미달이 주원인입니다.
-- 1~3월 평균 278백만 → 4월 135백만으로 절반 아래로 떨어졌습니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 당월 실적 2,444백만(집행률 102%)으로 예산 수준에서 집행했습니다.
-- 본사 1,804백만(집행률 100%), 법인 640백만(집행률 108%)으로 법인이 예산을 초과했습니다.
-- HUMAX(공통)이 716백만으로 1~4월 평균 602백만을 웃돌았고, 건물은 121백만으로 4월(135백만)에 이어 낮은 수준입니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 13,012백만(집행률 97%)으로 예산 내에서 집행 중입니다.
-- 본사 9,318백만(집행률 93%)은 예산 대비 미달, 법인 3,694백만(집행률 108%)은 초과로 방향이 엇갈립니다.
-- 항목별 집행률에서는 HUMAX(공통) 121%, EVCS(국내) 110%로 예산을 초과하였고, 건물 72%, STB 85%, EVCS(해외) 92%는 예산을 밑돕니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 6,161백만(집행률 96%)은 연간 예산의 42%로 5개월 경과 진도(42%)에 부합합니다.
-- 국내 1,612백만은 연간 예산의 46%로 진도를 앞서고, 월 배부액도 269→343백만으로 증가 추세입니다.
-- 해외 4,549백만은 연간 예산의 41%이며, 비용의 56%인 3,439백만이 인건비입니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 2,381백만(집행률 85%)으로 예산을 425백만 밑돕니다.
-- 예산 대비 Media그룹 -469백만(외주개발용역비 -525)이 주원인이며, 보정 후 월 441~493백만으로 평탄해 감소 추세는 아직 없습니다.
-- 4월, 5월 트렌드 왜곡: STB License Fee/Nagra 84백만 4월 기표 후 5월 reverse (선급비용 조정 시기 오류)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 3,125백만(집행률 121%)으로 예산을 552백만 초과했습니다.
-- 예산 대비 Staff부문 +516백만이 대부분이며, 급여 +208·특허처리비 +106·지급수수료 +100 초과가 주원인입니다.
-- 1월, 5월 일회성 집행으로 배부액 상승: 26년 외부감사 착수금 200백만(1월), 15차 주식선택권 취소 216백만(5월)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 1,089백만(집행률 72%)으로 예산을 416백만 밑돕니다.
-- 예산 대비 감가상각비 -326백만, 수도광열비 -168 미달이 주원인입니다(임차료 +91 초과).
-- 1~3월 평균 278백만 → 4~5월 평균 128백만으로 4월부터 계단식으로 낮아졌습니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 당월 실적 2,537백만(집행률 100%)으로 예산에 부합합니다.
-- 본사 1,747백만(집행률 91%)은 예산 대비 미달, 법인 790백만(집행률 131%)은 초과로 방향이 엇갈립니다.
-- HUMAX(공통)은 541백만으로 5월(716백만) 대비 175백만 줄었고, STB는 536백만으로 1~5월 평균(476백만)을 60백만 웃돌았습니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 15,549백만(집행률 97%)으로 예산 내에서 집행 중입니다.
-- 본사 11,065백만(집행률 92%)은 예산 대비 미달, 법인 4,484백만(집행률 112%)은 초과로 방향이 엇갈립니다.
-- 항목별 집행률에서는 HUMAX(공통) 119%, EVCS(국내) 108%로 예산을 초과하였고, 건물 67%, STB 90%, EVCS(해외) 94%는 예산을 밑돕니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 7,440백만(집행률 97%)은 연간 예산의 51%로 6개월 경과 진도(50%)에 부합합니다.
-- 국내 1,973백만은 연간 예산의 57%로 진도를 앞서고, 월 배부액도 269→361백만으로 증가 추세입니다.
-- 해외 5,468백만은 연간 예산의 49%이며, 비용의 56%인 4,130백만이 인건비입니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 2,916백만(집행률 90%)으로 예산을 336백만 밑돕니다.
-- 예산 대비 Media그룹 -454백만(외주개발용역비 -526)이 주원인이며, 보정 후 월 441~536백만으로 감소 추세는 아직 없습니다.
-- 4월, 5월 트렌드 왜곡: STB License Fee/Nagra 84백만 4월 기표 후 5월 reverse (선급비용 조정 시기 오류)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 3,666백만(집행률 119%)으로 예산을 586백만 초과했습니다.
-- 예산 대비 Staff부문 +466백만(급여 +217, 특허처리비 +105), HBR +124백만이 초과의 대부분입니다.
-- 1월, 5월 일회성 집행으로 배부액 상승: 26년 외부감사 착수금 200백만(1월), 15차 주식선택권 취소 216백만(5월)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 1,211백만(집행률 67%)으로 예산을 599백만 밑돕니다.
-- 예산 대비 감가상각비 -489백만, 수도광열비 -254 미달이 주원인입니다(임차료 +136 초과).
-- 1~3월 평균 278백만 → 4~6월 평균 126백만으로 4월부터 계단식으로 낮아졌습니다.</t>
+    <t>수정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>월별 배부액 추이 (왜곡 수정ver)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 당월 실적 2,818백만(집행률 88%) — 예산 대비 미달
+- 본사 2,020백만(집행률 83%) 미달 주도 · 법인 798백만(집행률 102%) 예산 수준
+- STB 493백만(집행률 49%) 최저 · HUMAX(공통) 760백만 — 외부감사 착수금 200백만 반영</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 1,233백만(집행률 100%) · 연간 예산의 8% — 1개월 경과 진도(8%) 부합
+- 국내 269백만 · 연간 예산의 8% — 첫 달, 추이 판단 불가
+- 해외 963백만 · 연간 예산의 9% — 인건비 720백만(58%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 493백만(집행률 49%) — 예산 대비 521백만 미달
+- 예산 대비 Media그룹 -533백만(외주개발용역비 -509) — 미달의 대부분</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 760백만(집행률 122%) — 예산 대비 138백만 초과
+- 예산 대비 Staff부문 +138백만 — 특허처리비 +64백만 주원인
+- 1월 일회성 증가: 26년 외부감사 착수금 200백만</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 272백만(집행률 91%) — 예산 대비 소폭 미달
+- 예산 대비 Staff부문 -26백만 — 차이 작음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 당월 실적 2,633백만(집행률 103%) — 예산 대비 소폭 초과
+- 본사 1,752백만(집행률 95%) 예산 대비 미달 · 법인 881백만(집행률 121%) 예산 초과
+- HUMAX(공통) 467백만 — 1월(760백만) 대비 293백만 감소(외부감사 착수금 소멸)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 2,566백만(집행률 100%) · 연간 예산의 18% — 2개월 경과 진도(17%) 부합
+- 국내 583백만 · 연간 예산의 17% — 월 배부액 269→314백만 증가
+- 해외 1,983백만 · 연간 예산의 18% — 인건비 1,481백만(58%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 975백만(집행률 66%) — 예산 대비 499백만 미달
+- 예산 대비 Media그룹 -527백만(외주개발용역비 -513) 주원인 · 월 배부액 493→483백만 변화 없음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 1,227백만(집행률 116%) — 예산 대비 170백만 초과
+- 예산 대비 Staff부문 +180백만 — 특허처리비 +77백만 주원인
+- 1월 일회성 증가: 26년 외부감사 착수금 200백만 — 제외 시 월 560→467백만</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 572백만(집행률 97%) — 예산 근접
+- 월 배부액 272→300백만 — 아직 감소 없음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 3,770백만(집행률 97%) · 연간 예산의 26% — 3개월 경과 진도(25%) 부합
+- 국내 904백만 · 연간 예산의 26% 진도 상회 — 월 배부액 269→321백만 증가
+- 해외 2,866백만 · 연간 예산의 26% — 인건비 2,173백만(58%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 1,417백만(집행률 72%) — 예산 대비 541백만 미달
+- 예산 대비 Media그룹 -522백만(외주개발용역비 -533) 주원인 · 월 배부액 493→483→441백만 완만한 감소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 1,811백만(집행률 116%) — 예산 대비 245백만 초과
+- 예산 대비 Staff부문 +240백만 — 특허처리비 +90백만 주원인
+- 1월 일회성 증가: 26년 외부감사 착수금 200백만 — 제외 시 월 560→467→584백만, 감소 추세 없음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 833백만(집행률 94%) — 예산 근접
+- 월 배부액 272→300→261백만 — 큰 변화 없음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 당월 실적 2,526백만(집행률 96%) — 예산 내 집행
+- 본사 1,868백만(집행률 94%) 예산 대비 미달 · 법인 658백만(집행률 104%) 소폭 초과
+- 건물 135백만 — 1~3월 평균 278백만의 절반 이하</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 4,972백만(집행률 95%) · 연간 예산의 34% — 4개월 경과 진도(33%) 부합
+- 국내 1,269백만 · 연간 예산의 36% 진도 상회 — 월 배부액 269→365백만 증가
+- 해외 3,703백만 · 연간 예산의 33% — 인건비 2,817백만(57%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 1,982백만(집행률 83%) — 예산 대비 410백만 미달
+- 예산 대비 Media그룹 -426백만(외주개발용역비 -533) 주원인 · HUK +79백만 초과
+- 4월 트렌드 왜곡: STB License Fee/Nagra 4월 -84백만 (선급비용 결산 조정 지연)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 당월 실적 2,444백만(집행률 102%) — 예산 수준
+- 본사 1,804백만(집행률 100%) · 법인 640백만(집행률 108%) 예산 초과
+- HUMAX(공통) 716백만 — 1~4월 평균 602백만 상회 · 건물 121백만 — 4월(135백만)에 이어 낮은 수준</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 6,161백만(집행률 96%) · 연간 예산의 42% — 5개월 경과 진도(42%) 부합
+- 국내 1,612백만 · 연간 예산의 46% 진도 상회 — 월 배부액 269→343백만 증가
+- 해외 4,549백만 · 연간 예산의 41% — 인건비 3,439백만(56%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 2,381백만(집행률 85%) — 예산 대비 425백만 미달
+- 예산 대비 Media그룹 -469백만(외주개발용역비 -525) 주원인 · 보정 후 월 441~493백만 — 감소 추세 없음
+- 4월, 5월 트렌드 왜곡: STB License Fee/Nagra 4월 -84백만, 5월 +84백만 (선급비용 결산 조정 지연)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 당월 실적 2,537백만(집행률 100%) — 예산 부합
+- 본사 1,747백만(집행률 91%) 예산 대비 미달 · 법인 790백만(집행률 131%) 초과 — 방향 엇갈림
+- HUMAX(공통) 541백만 — 5월(716백만) 대비 175백만 감소 · STB 536백만 — 1~5월 평균(476백만) 60백만 상회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 7,440백만(집행률 97%) · 연간 예산의 51% — 6개월 경과 진도(50%) 부합
+- 국내 1,973백만 · 연간 예산의 57% 진도 상회 — 월 배부액 269→361백만 증가
+- 해외 5,468백만 · 연간 예산의 49% — 인건비 4,130백만(56%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 2,916백만(집행률 90%) — 예산 대비 336백만 미달
+- 예산 대비 Media그룹 -454백만(외주개발용역비 -526) 주원인 · 보정 후 월 441~536백만 — 감소 추세 없음
+- 4월, 5월 트렌드 왜곡: STB License Fee/Nagra 4월 -84백만, 5월 +84백만 (선급비용 결산 조정 지연)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 2,818백만(집행률 88%) — 예산 내 집행
+- 본사 2,020백만(집행률 83%) 예산 대비 미달 · 법인 798백만(집행률 102%) 예산 수준
+- 항목별 집행률: 예산 초과 HUMAX(공통) 122% / 예산 미달 STB 49% — 차이의 대부분</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 5,451백만(집행률 94%) — 예산 내 집행
+- 본사 3,772백만(집행률 88%) 예산 대비 미달 · 법인 1,679백만(집행률 111%) 초과 — 방향 엇갈림
+- 항목별 집행률: 예산 초과 HUMAX(공통) 116% / 예산 미달 STB 66% — 차이의 대부분</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 당월 실적 2,592백만(집행률 97%) — 예산 내 집행
+- 본사 1,874백만(집행률 94%) 예산 대비 미달 · 법인 718백만(집행률 106%) 초과
+- MOBILITY 101백만 — 1~2월(61, 50백만) 대비 2배</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 8,043백만(집행률 95%) — 예산 내 집행
+- 본사 5,646백만(집행률 90%) 예산 대비 미달 · 법인 2,397백만(집행률 110%) 초과 — 방향 엇갈림
+- 항목별 집행률: 예산 초과 HUMAX(공통) 116%, MOBILITY 143% / 예산 미달 STB 72%, 건물 94%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 10,568백만(집행률 95%) — 예산 내 집행
+- 본사 7,514백만(집행률 91%) 예산 대비 미달 · 법인 3,055백만(집행률 109%) 초과 — 방향 엇갈림
+- 항목별 집행률: 예산 초과 HUMAX(공통) 115%, EVCS(국내) 107% / 예산 미달 건물 81%, STB 83%, EVCS(해외) 92%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 2,409백만(집행률 115%) — 예산 대비 321백만 초과
+- 예산 대비 Staff부문 +300백만 — 지급수수료 +106, 특허처리비 +105 주원인
+- 1월 일회성 증가: 26년 외부감사 착수금 200백만 — 제외 시 월 560→467→584→598백만</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 968백만(집행률 81%) — 예산 대비 231백만 미달
+- 예산 대비 감가상각비 -163백만, 수도광열비 -75 — 미달 주원인
+- 1~3월 평균 278백만 → 4월 135백만 — 절반 이하</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 13,012백만(집행률 97%) — 예산 내 집행
+- 본사 9,318백만(집행률 93%) 예산 대비 미달 · 법인 3,694백만(집행률 108%) 초과 — 방향 엇갈림
+- 항목별 집행률: 예산 초과 HUMAX(공통) 121%, EVCS(국내) 110% / 예산 미달 건물 72%, STB 85%, EVCS(해외) 92%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 3,125백만(집행률 121%) — 예산 대비 552백만 초과
+- 예산 대비 Staff부문 +516백만 — 급여 +208, 특허처리비 +106, 지급수수료 +100 주원인
+- 1월, 5월 일회성 증가: 26년 외부감사 착수금 200백만(1월), 15차 주식선택권 취소 216백만(5월)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 1,089백만(집행률 72%) — 예산 대비 416백만 미달
+- 예산 대비 감가상각비 -326백만, 수도광열비 -168 미달 주원인(임차료 +91 초과)
+- 1~3월 평균 278백만 → 4~5월 평균 128백만 — 4월부터 계단식 감소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 15,549백만(집행률 97%) — 예산 내 집행
+- 본사 11,065백만(집행률 92%) 예산 대비 미달 · 법인 4,484백만(집행률 112%) 초과 — 방향 엇갈림
+- 항목별 집행률: 예산 초과 HUMAX(공통) 119%, EVCS(국내) 108% / 예산 미달 건물 67%, STB 90%, EVCS(해외) 94%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 3,666백만(집행률 119%) — 예산 대비 586백만 초과
+- 예산 대비 Staff부문 +466백만(급여 +217, 특허처리비 +105) · HBR +124백만 — 초과의 대부분
+- 1월, 5월 일회성 증가: 26년 외부감사 착수금 200백만(1월), 15차 주식선택권 취소 216백만(5월)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 1,211백만(집행률 67%) — 예산 대비 599백만 미달
+- 예산 대비 감가상각비 -489백만, 수도광열비 -254 미달 주원인(임차료 +136 초과)
+- 1~3월 평균 278백만 → 4~6월 평균 126백만 — 4월부터 계단식 감소</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -328,7 +330,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -350,6 +352,22 @@
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
@@ -403,7 +421,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -419,13 +437,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -742,7 +769,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05630F61-30FB-4CF7-B3FF-D0B93533C1C1}">
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.625" customWidth="1"/>
@@ -765,28 +792,28 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="66" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" s="4"/>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="8" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="66" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" s="4"/>
-      <c r="D3" s="5" t="s">
-        <v>25</v>
+      <c r="D3" s="8" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -794,11 +821,11 @@
         <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" s="4"/>
-      <c r="D4" s="5" t="s">
-        <v>26</v>
+      <c r="D4" s="8" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="33" x14ac:dyDescent="0.3">
@@ -806,13 +833,13 @@
         <v>6</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>27</v>
+      <c r="D5" s="8" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -820,13 +847,13 @@
         <v>6</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>28</v>
+      <c r="D6" s="8" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="33" x14ac:dyDescent="0.3">
@@ -834,91 +861,91 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="5"/>
+      <c r="D8" s="9" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
+    <row r="9" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="7" t="s">
+      <c r="C9" s="5"/>
+      <c r="D9" s="9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="5"/>
+      <c r="D10" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="66" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="7" t="s">
+    <row r="11" spans="1:4" ht="33" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="9" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="7" t="s">
+    <row r="12" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="7" t="s">
+    <row r="13" spans="1:4" ht="33" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="9" t="s">
         <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="33" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -926,23 +953,23 @@
         <v>4</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C14" s="4"/>
-      <c r="D14" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="66" x14ac:dyDescent="0.3">
+      <c r="D14" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C15" s="4"/>
-      <c r="D15" s="5" t="s">
-        <v>37</v>
+      <c r="D15" s="8" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -950,25 +977,25 @@
         <v>5</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C16" s="4"/>
-      <c r="D16" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="D16" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="33" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>39</v>
+      <c r="D17" s="8" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -976,13 +1003,13 @@
         <v>6</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D18" s="5" t="s">
-        <v>40</v>
+      <c r="D18" s="8" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="33" x14ac:dyDescent="0.3">
@@ -990,103 +1017,103 @@
         <v>6</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D19" s="5" t="s">
-        <v>41</v>
+      <c r="D19" s="8" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="5"/>
+      <c r="D20" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="66" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="6"/>
-      <c r="D20" s="7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="66" x14ac:dyDescent="0.3">
-      <c r="A21" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" s="6"/>
-      <c r="D21" s="7" t="s">
-        <v>43</v>
+      <c r="C21" s="5"/>
+      <c r="D21" s="9" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22" s="6"/>
-      <c r="D22" s="7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="66" x14ac:dyDescent="0.3">
-      <c r="A23" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C23" s="6" t="s">
+      <c r="B22" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="5"/>
+      <c r="D22" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D23" s="7" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="66" x14ac:dyDescent="0.3">
-      <c r="A24" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C24" s="6" t="s">
+      <c r="D23" s="9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D24" s="7" t="s">
-        <v>46</v>
+      <c r="D24" s="9" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A25" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C25" s="6" t="s">
+      <c r="A25" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D25" s="7" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="66" x14ac:dyDescent="0.3">
+      <c r="D25" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C26" s="4"/>
-      <c r="D26" s="5" t="s">
-        <v>48</v>
+      <c r="D26" s="8" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="66" x14ac:dyDescent="0.3">
@@ -1094,11 +1121,11 @@
         <v>4</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C27" s="4"/>
-      <c r="D27" s="5" t="s">
-        <v>49</v>
+      <c r="D27" s="8" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -1106,39 +1133,39 @@
         <v>5</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C28" s="4"/>
-      <c r="D28" s="5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="66" x14ac:dyDescent="0.3">
+      <c r="D28" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D29" s="5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="66" x14ac:dyDescent="0.3">
+      <c r="D29" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D30" s="5" t="s">
-        <v>52</v>
+      <c r="D30" s="8" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -1146,107 +1173,112 @@
         <v>6</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D31" s="5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="66" x14ac:dyDescent="0.3">
-      <c r="A32" s="6" t="s">
+      <c r="D31" s="8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A32" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32" s="5"/>
+      <c r="D32" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="66" x14ac:dyDescent="0.3">
+      <c r="A33" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B33" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C32" s="6"/>
-      <c r="D32" s="7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="66" x14ac:dyDescent="0.3">
-      <c r="A33" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C33" s="6"/>
-      <c r="D33" s="7" t="s">
-        <v>55</v>
+      <c r="C33" s="5"/>
+      <c r="D33" s="9" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C34" s="6"/>
-      <c r="D34" s="7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="66" x14ac:dyDescent="0.3">
-      <c r="A35" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C35" s="6" t="s">
+      <c r="B34" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C34" s="5"/>
+      <c r="D34" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A35" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C35" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D35" s="7" t="s">
-        <v>57</v>
+      <c r="D35" s="10" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A36" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C36" s="6" t="s">
+      <c r="A36" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C36" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D36" s="7" t="s">
+      <c r="D36" s="10" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A37" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C37" s="6" t="s">
+      <c r="A37" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D37" s="7" t="s">
+      <c r="D37" s="9" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="33" x14ac:dyDescent="0.3">
-      <c r="A38" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D38" s="5" t="s">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" s="5" t="s">
         <v>23</v>
       </c>
+      <c r="D38" s="7"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D40" s="6" t="s">
+        <v>22</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D38" xr:uid="{05630F61-30FB-4CF7-B3FF-D0B93533C1C1}"/>
+  <autoFilter ref="A1:D37" xr:uid="{05630F61-30FB-4CF7-B3FF-D0B93533C1C1}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADA7D752-4141-4978-818B-81CD427F29FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CC97D91-4717-4E6B-B02D-A4225B98C481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-885" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
@@ -108,10 +108,6 @@
     <t>4월 누계</t>
   </si>
   <si>
-    <t>수정</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>월별 배부액 추이 (왜곡 수정ver)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -230,24 +226,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>- 당월 실적 2,537백만(집행률 100%) — 예산 부합
-- 본사 1,747백만(집행률 91%) 예산 대비 미달 · 법인 790백만(집행률 131%) 초과 — 방향 엇갈림
-- HUMAX(공통) 541백만 — 5월(716백만) 대비 175백만 감소 · STB 536백만 — 1~5월 평균(476백만) 60백만 상회</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 7,440백만(집행률 97%) · 연간 예산의 51% — 6개월 경과 진도(50%) 부합
-- 국내 1,973백만 · 연간 예산의 57% 진도 상회 — 월 배부액 269→361백만 증가
-- 해외 5,468백만 · 연간 예산의 49% — 인건비 4,130백만(56%)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 2,916백만(집행률 90%) — 예산 대비 336백만 미달
-- 예산 대비 Media그룹 -454백만(외주개발용역비 -526) 주원인 · 보정 후 월 441~536백만 — 감소 추세 없음
-- 4월, 5월 트렌드 왜곡: STB License Fee/Nagra 4월 -84백만, 5월 +84백만 (선급비용 결산 조정 지연)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>- 누계 실적 2,818백만(집행률 88%) — 예산 내 집행
 - 본사 2,020백만(집행률 83%) 예산 대비 미달 · 법인 798백만(집행률 102%) 예산 수준
 - 항목별 집행률: 예산 초과 HUMAX(공통) 122% / 예산 미달 STB 49% — 차이의 대부분</t>
@@ -308,21 +286,79 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>- 누계 실적 15,549백만(집행률 97%) — 예산 내 집행
-- 본사 11,065백만(집행률 92%) 예산 대비 미달 · 법인 4,484백만(집행률 112%) 초과 — 방향 엇갈림
-- 항목별 집행률: 예산 초과 HUMAX(공통) 119%, EVCS(국내) 108% / 예산 미달 건물 67%, STB 90%, EVCS(해외) 94%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 3,666백만(집행률 119%) — 예산 대비 586백만 초과
-- 예산 대비 Staff부문 +466백만(급여 +217, 특허처리비 +105) · HBR +124백만 — 초과의 대부분
-- 1월, 5월 일회성 증가: 26년 외부감사 착수금 200백만(1월), 15차 주식선택권 취소 216백만(5월)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 1,211백만(집행률 67%) — 예산 대비 599백만 미달
-- 예산 대비 감가상각비 -489백만, 수도광열비 -254 미달 주원인(임차료 +136 초과)
+    <t xml:space="preserve"> - STB · STB License Fee/Nagra 4월 -84백만, 5월 +84백만 (선급비용 결산 조정 지연)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 당월 실적 2,537백만(집행률 100%): 본사 1,747백만(집행률 91%), 법인 790백만(집행률 131%)
+- HUMAX(공통) 541백만으로 전월 대비 175백만 감소
+- STB 536백만으로 1~5월 평균 대비 60백만 초과</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 15,549백만(집행률 97%): 본사 11,065백만(집행률 92%), 법인 4,484백만(집행률 112%)
+- 집행률 초과: HUMAX(공통) 119%, EVCS(국내) 108%
+- 집행률 미달: 건물 67%, STB 90%, EVCS(해외) 94%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 1,211백만(집행률 67%)
+- 미달 사유: 예산 대비 감가상각비 -489백만, 수도광열비 -254 미달 주원인(임차료 +136 초과)
 - 1~3월 평균 278백만 → 4~6월 평균 126백만 — 4월부터 계단식 감소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">- 누계 실적 3,666백만(집행률 119%)
+- 초과 사유: 예산 대비 Staff부문 +466백만(급여 +217, 특허처리비 +105)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">   *CEO주식보상비용 6월 누계 2.5억원(예산 외), VVC 특허처리비 초과 집행</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- 1월, 5월 일회성 증가: 26년 외부감사 착수금 200백만(1월), 15차 주식선택권 취소 216백만(5월)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 7,440백만(집행률 97%): 연간 예산의 51% 수준, 6개월 경과 진도(50%)에 부합
+- 누계 실적_국내 1,973백만(집행률 108%): 예산 대비 147백만 초과, 연간 예산의 57% 수준, 월 배부액 269→361백만 증가
+- 누계 실적_해외 5,468백만(집행률 94%): 예산 대비 353백만 미달, 연간 예산의 49% 수준, 인건비 3,141백만(해외의 57% 차지)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 2,916백만(집행률 90%)
+- 미달 사유: Media그룹 New Aura/iWedia 외주개발용역비 6월 누계 5.18억원 미집행 (SW이슈로 집행 지연)
+- 4월, 5월 트렌드 왜곡: STB License Fee/Nagra 4월 -84백만, 5월 +84백만 (선급비용 결산 조정 지연)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -330,7 +366,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -368,6 +404,14 @@
       <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
@@ -443,9 +487,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -453,6 +494,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -470,6 +514,1319 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>409575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{523023D9-85E9-479C-A4E0-221935FF4431}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11620500" y="14725650"/>
+          <a:ext cx="4391025" cy="17659350"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFE5"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000"/>
+            <a:t>1. Humax</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000"/>
+            <a:t>합계</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000"/>
+            <a:t>.sheet</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000"/>
+            <a:t>당월</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000"/>
+            <a:t>당월 누계</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000"/>
+            <a:t>2. EVCS</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000"/>
+            <a:t>사업부</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000"/>
+            <a:t>.sheet</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000"/>
+            <a:t>- </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="1"/>
+            <a:t>3. Humax</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="1"/>
+            <a:t>합계</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="1"/>
+            <a:t>_</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="1"/>
+            <a:t>상세</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="1"/>
+            <a:t>.sheet</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000"/>
+            <a:t>-</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
+            <a:t>예산 대비 큰 폭으로 초과</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+            <a:t>, </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
+            <a:t>미달 인 경우 → </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+            <a:t>Appendix D</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+            <a:t>- </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
+            <a:t>전월 대비 큰 폭으로 증가</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+            <a:t>, </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
+            <a:t>감소 한 경우 → 클로드 명령</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="1"/>
+            <a:t>▶ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="1"/>
+            <a:t>STB</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="1"/>
+            <a:t>[Staff]</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Charter Legal fee/B&amp;M</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="0" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> 6</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="0" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>월 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="0" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>71</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="0" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>백만 집행 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="0" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="0" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>예산 외</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="0" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+            <a:t>- 26</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
+            <a:t>년 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+            <a:t>3</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
+            <a:t>월 소송 제기로 올해 비용 지속 예상</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="1" baseline="0"/>
+            <a:t>[Media]</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000" b="1"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>New</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> Aura/iWedia </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>외주개발용역비 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>6</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>월 누계 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>5.18</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>억원 미집행</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> - SW</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>이슈로 용역비 집행 지연</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>, 2H </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>비용 협상 시도 예정</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+            <a:t>STB License Fee/Nagra </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
+            <a:t>조정 시기 오류로 인한 트렌드 왜곡</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+            <a:t>- 4</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
+            <a:t>월 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+            <a:t>84</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
+            <a:t>백만</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+            <a:t>, 5</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
+            <a:t>월 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+            <a:t>-84</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
+            <a:t>백만</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+            <a:t>(4</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
+            <a:t>월에 기표되었어야함</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+            <a:t>)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="1" baseline="0"/>
+            <a:t>[SCM]</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000"/>
+            <a:t>삼계리 편성 오류</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000"/>
+            <a:t>:</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
+            <a:t>매월 감가상각비 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+            <a:t>+6.8</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
+            <a:t>백만</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+            <a:t>, </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
+            <a:t>임차료 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+            <a:t>-18</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
+            <a:t>백만</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+            <a:t>- </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
+            <a:t>임차료 제외 후 감가상각비 사용권 자산 반영중 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
+            <a:t>월 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+            <a:t>-11</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
+            <a:t>백만</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+            <a:t>)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="1" baseline="0"/>
+            <a:t>[HUK]</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Bonus  +1.5</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>억</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(2</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>억 집행</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>/</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>예산 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>0.5</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>억</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>): STB</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>  +0.2</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>억</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>, EVCS +1.3</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>억</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
+            <a:t>리소스 투입률 변동 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+            <a:t>STB</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
+            <a:t>↑</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+            <a:t>(New Aura </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
+            <a:t>품질이슈</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+            <a:t>) EVCS</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
+            <a:t>↓ 으로 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+            <a:t>2Q STB </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
+            <a:t>비용 부담 증가</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000"/>
+            <a:t>Victor </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000"/>
+            <a:t>용역비</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000"/>
+            <a:t>/TSG 6</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000"/>
+            <a:t>월 누계 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000"/>
+            <a:t>+71</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000"/>
+            <a:t>백만</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000"/>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000"/>
+            <a:t>월 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000"/>
+            <a:t>11.8</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000"/>
+            <a:t>백만</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000"/>
+            <a:t>/</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000"/>
+            <a:t>예산 사업그룹</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000"/>
+            <a:t>): STB +16</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000"/>
+            <a:t>백만</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000"/>
+            <a:t>, EVCS +55</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000"/>
+            <a:t>백만</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="1"/>
+            <a:t>[HJP]</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>인건비 외 경비 집행률 저조</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>:</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>광고선전비</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>, </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>여비교통비</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>, </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>회의비</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>, </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>접대비 등</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+            <a:t>5</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
+            <a:t>월 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+            <a:t>1</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
+            <a:t>명 퇴사로 인건비 예산 대비 감소 지속</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="1" baseline="0"/>
+            <a:t>[HUG]</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="0" baseline="0"/>
+            <a:t>5</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="0" baseline="0"/>
+            <a:t>월 부터 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="0" baseline="0"/>
+            <a:t>Fleetup </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="0" baseline="0"/>
+            <a:t>비용 부담</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000" b="0" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>지급수수료 초과로 예산 대비 초과 집행</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+            <a:t>- Marie </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
+            <a:t>용역비 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
+            <a:t>예산 외</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+            <a:t>): 2Q 15</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
+            <a:t>백만</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+            <a:t> </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+            <a:t>- KWS </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
+            <a:t>용역비 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
+            <a:t>예산 외</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+            <a:t>): 1</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
+            <a:t>월 성과급 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+            <a:t>18</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
+            <a:t>백만</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+            <a:t>, 2Q </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
+            <a:t>용역비 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+            <a:t>12</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
+            <a:t>백만</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+            <a:t>- </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
+            <a:t>멕시코 장비반송료 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+            <a:t>1</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
+            <a:t>월 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+            <a:t>9</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
+            <a:t>백만 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" baseline="0"/>
+            <a:t>예산 외</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" baseline="0"/>
+            <a:t>)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="1"/>
+            <a:t>▶ [Humax(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="1"/>
+            <a:t>공통</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="1"/>
+            <a:t>)]</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="1"/>
+            <a:t>[Staff]</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>특허처리비 초과 집행 지속 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>6</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>월 누계 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>+105</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>백만 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(VVC</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="0" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="0" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>예산 누락</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="0" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="0"/>
+            <a:t>CEO </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="0"/>
+            <a:t>주식보상비 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="0"/>
+            <a:t>6</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="0"/>
+            <a:t>월 누계 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="0"/>
+            <a:t>2.5</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="0"/>
+            <a:t>억원 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="0"/>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="0"/>
+            <a:t>예산 외</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="0"/>
+            <a:t>)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="1"/>
+            <a:t>[HBR]</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000"/>
+            <a:t>인원수 변동 없음</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000"/>
+            <a:t>, </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000"/>
+            <a:t>회계수수료 및 복리후생비 초과집행중</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000"/>
+            <a:t>회계수수료 예산 외 집행</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000"/>
+            <a:t> 6</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000"/>
+            <a:t>월 누계 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000"/>
+            <a:t>+50</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000"/>
+            <a:t>백만</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000"/>
+            <a:t>복리후생비 초과 집행중 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000"/>
+            <a:t>6</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000"/>
+            <a:t>월 누계 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000"/>
+            <a:t>+9</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000"/>
+            <a:t>백만</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="1"/>
+            <a:t>[</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="1"/>
+            <a:t>건물</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="1"/>
+            <a:t>]</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>1~3</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>월 평균 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>278 → 4~6</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>월 평균 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>126</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>으로 사옥 이전에 따른 계단식 감소</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="0" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> 확인</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000" b="0">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1000" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -800,8 +2157,8 @@
         <v>14</v>
       </c>
       <c r="C2" s="4"/>
-      <c r="D2" s="8" t="s">
-        <v>24</v>
+      <c r="D2" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -812,8 +2169,8 @@
         <v>15</v>
       </c>
       <c r="C3" s="4"/>
-      <c r="D3" s="8" t="s">
-        <v>47</v>
+      <c r="D3" s="7" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -824,8 +2181,8 @@
         <v>15</v>
       </c>
       <c r="C4" s="4"/>
-      <c r="D4" s="8" t="s">
-        <v>25</v>
+      <c r="D4" s="7" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="33" x14ac:dyDescent="0.3">
@@ -838,8 +2195,8 @@
       <c r="C5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="8" t="s">
-        <v>26</v>
+      <c r="D5" s="7" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -852,8 +2209,8 @@
       <c r="C6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="8" t="s">
-        <v>27</v>
+      <c r="D6" s="7" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="33" x14ac:dyDescent="0.3">
@@ -866,8 +2223,8 @@
       <c r="C7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="8" t="s">
-        <v>28</v>
+      <c r="D7" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -878,8 +2235,8 @@
         <v>16</v>
       </c>
       <c r="C8" s="5"/>
-      <c r="D8" s="9" t="s">
-        <v>29</v>
+      <c r="D8" s="8" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -890,8 +2247,8 @@
         <v>17</v>
       </c>
       <c r="C9" s="5"/>
-      <c r="D9" s="9" t="s">
-        <v>48</v>
+      <c r="D9" s="8" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -902,8 +2259,8 @@
         <v>17</v>
       </c>
       <c r="C10" s="5"/>
-      <c r="D10" s="9" t="s">
-        <v>30</v>
+      <c r="D10" s="8" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="33" x14ac:dyDescent="0.3">
@@ -916,8 +2273,8 @@
       <c r="C11" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="9" t="s">
-        <v>31</v>
+      <c r="D11" s="8" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -930,8 +2287,8 @@
       <c r="C12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="9" t="s">
-        <v>32</v>
+      <c r="D12" s="8" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="33" x14ac:dyDescent="0.3">
@@ -944,8 +2301,8 @@
       <c r="C13" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="9" t="s">
-        <v>33</v>
+      <c r="D13" s="8" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -956,8 +2313,8 @@
         <v>18</v>
       </c>
       <c r="C14" s="4"/>
-      <c r="D14" s="8" t="s">
-        <v>49</v>
+      <c r="D14" s="7" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -968,8 +2325,8 @@
         <v>19</v>
       </c>
       <c r="C15" s="4"/>
-      <c r="D15" s="8" t="s">
-        <v>50</v>
+      <c r="D15" s="7" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -980,8 +2337,8 @@
         <v>19</v>
       </c>
       <c r="C16" s="4"/>
-      <c r="D16" s="8" t="s">
-        <v>34</v>
+      <c r="D16" s="7" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="33" x14ac:dyDescent="0.3">
@@ -994,8 +2351,8 @@
       <c r="C17" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="8" t="s">
-        <v>35</v>
+      <c r="D17" s="7" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -1008,8 +2365,8 @@
       <c r="C18" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D18" s="8" t="s">
-        <v>36</v>
+      <c r="D18" s="7" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="33" x14ac:dyDescent="0.3">
@@ -1022,8 +2379,8 @@
       <c r="C19" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D19" s="8" t="s">
-        <v>37</v>
+      <c r="D19" s="7" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -1034,8 +2391,8 @@
         <v>20</v>
       </c>
       <c r="C20" s="5"/>
-      <c r="D20" s="9" t="s">
-        <v>38</v>
+      <c r="D20" s="8" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="66" x14ac:dyDescent="0.3">
@@ -1046,8 +2403,8 @@
         <v>21</v>
       </c>
       <c r="C21" s="5"/>
-      <c r="D21" s="9" t="s">
-        <v>51</v>
+      <c r="D21" s="8" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -1058,8 +2415,8 @@
         <v>21</v>
       </c>
       <c r="C22" s="5"/>
-      <c r="D22" s="9" t="s">
-        <v>39</v>
+      <c r="D22" s="8" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -1072,8 +2429,8 @@
       <c r="C23" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D23" s="9" t="s">
-        <v>40</v>
+      <c r="D23" s="8" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -1086,8 +2443,8 @@
       <c r="C24" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D24" s="9" t="s">
-        <v>52</v>
+      <c r="D24" s="8" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -1100,8 +2457,8 @@
       <c r="C25" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D25" s="9" t="s">
-        <v>53</v>
+      <c r="D25" s="8" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -1112,8 +2469,8 @@
         <v>10</v>
       </c>
       <c r="C26" s="4"/>
-      <c r="D26" s="8" t="s">
-        <v>41</v>
+      <c r="D26" s="7" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="66" x14ac:dyDescent="0.3">
@@ -1124,8 +2481,8 @@
         <v>11</v>
       </c>
       <c r="C27" s="4"/>
-      <c r="D27" s="8" t="s">
-        <v>54</v>
+      <c r="D27" s="7" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -1136,8 +2493,8 @@
         <v>11</v>
       </c>
       <c r="C28" s="4"/>
-      <c r="D28" s="8" t="s">
-        <v>42</v>
+      <c r="D28" s="7" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -1150,8 +2507,8 @@
       <c r="C29" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D29" s="8" t="s">
-        <v>43</v>
+      <c r="D29" s="7" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -1164,8 +2521,8 @@
       <c r="C30" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D30" s="8" t="s">
-        <v>55</v>
+      <c r="D30" s="7" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -1178,8 +2535,8 @@
       <c r="C31" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D31" s="8" t="s">
-        <v>56</v>
+      <c r="D31" s="7" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -1191,10 +2548,10 @@
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="66" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>4</v>
       </c>
@@ -1203,10 +2560,10 @@
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>5</v>
       </c>
@@ -1215,7 +2572,7 @@
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="9" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -1228,11 +2585,11 @@
       <c r="C35" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D35" s="10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="D35" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="66" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
         <v>6</v>
       </c>
@@ -1242,8 +2599,8 @@
       <c r="C36" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D36" s="10" t="s">
-        <v>58</v>
+      <c r="D36" s="9" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
@@ -1257,7 +2614,7 @@
         <v>9</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
@@ -1268,19 +2625,20 @@
         <v>13</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D38" s="7"/>
+        <v>22</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D40" s="6" t="s">
-        <v>22</v>
-      </c>
+      <c r="D40" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D37" xr:uid="{05630F61-30FB-4CF7-B3FF-D0B93533C1C1}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CC97D91-4717-4E6B-B02D-A4225B98C481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCDF45F0-351C-4F4F-BA09-C52D19A0EDF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-885" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="62">
   <si>
     <t>탭</t>
   </si>
@@ -286,10 +286,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> - STB · STB License Fee/Nagra 4월 -84백만, 5월 +84백만 (선급비용 결산 조정 지연)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>- 당월 실적 2,537백만(집행률 100%): 본사 1,747백만(집행률 91%), 법인 790백만(집행률 131%)
 - HUMAX(공통) 541백만으로 전월 대비 175백만 감소
 - STB 536백만으로 1~5월 평균 대비 60백만 초과</t>
@@ -302,63 +298,124 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>- 누계 실적 1,211백만(집행률 67%)
-- 미달 사유: 예산 대비 감가상각비 -489백만, 수도광열비 -254 미달 주원인(임차료 +136 초과)
-- 1~3월 평균 278백만 → 4~6월 평균 126백만 — 4월부터 계단식 감소</t>
+    <t>- 누계 실적 2,916백만(집행률 90%)
+- 미달 사유: Media그룹 New Aura/iWedia 외주개발용역비 6월 누계 5.18억원 미집행 (SW이슈로 집행 지연)
+- 4월, 5월 트렌드 왜곡: STB License Fee/Nagra 4월 -84백만, 5월 +84백만 (선급비용 결산 조정 지연)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 3,666백만(집행률 119%)
+- 초과 사유: 예산 대비 Staff부문 +466백만(급여 +217, 특허처리비 +105)
+   *CEO주식보상비용 2.5억원, VVC 특허처리비 예산 누락
+- 1월, 5월 일회성 증가: 26년 외부감사 착수금 200백만(1월), 15차 주식선택권 취소 216백만(5월)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
-      <t xml:space="preserve">- 누계 실적 3,666백만(집행률 119%)
-- 초과 사유: 예산 대비 Staff부문 +466백만(급여 +217, 특허처리비 +105)
-</t>
+      <t xml:space="preserve">(*) 자가사용 비율(사업부에 배부되는 건물비용): (BP/1Q) 분당/용인 </t>
     </r>
     <r>
       <rPr>
+        <b/>
+        <i/>
         <sz val="11"/>
-        <color rgb="FFFF0000"/>
+        <color theme="1"/>
         <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">   *CEO주식보상비용 6월 누계 2.5억원(예산 외), VVC 특허처리비 초과 집행</t>
+      <t>10%</t>
     </r>
     <r>
       <rPr>
+        <i/>
         <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
+        <color theme="1"/>
         <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>- 1월, 5월 일회성 증가: 26년 외부감사 착수금 200백만(1월), 15차 주식선택권 취소 216백만(5월)</t>
+      <t xml:space="preserve"> → (2Q) 분당</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 7,440백만(집행률 97%): 연간 예산의 51% 수준, 6개월 경과 진도(50%)에 부합
-- 누계 실적_국내 1,973백만(집행률 108%): 예산 대비 147백만 초과, 연간 예산의 57% 수준, 월 배부액 269→361백만 증가
-- 누계 실적_해외 5,468백만(집행률 94%): 예산 대비 353백만 미달, 연간 예산의 49% 수준, 인건비 3,141백만(해외의 57% 차지)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 2,916백만(집행률 90%)
-- 미달 사유: Media그룹 New Aura/iWedia 외주개발용역비 6월 누계 5.18억원 미집행 (SW이슈로 집행 지연)
-- 4월, 5월 트렌드 왜곡: STB License Fee/Nagra 4월 -84백만, 5월 +84백만 (선급비용 결산 조정 지연)</t>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 70%</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 용인 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>10%</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(*) []: 줄바꿈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 7,440백만(집행률 97%): 연간 예산의 51% 수준,[] 6개월 경과 진도(50%)에 부합
+- 누계 실적_국내 1,973백만(집행률 108%): 예산 대비 147백만 초과,[]연간 예산의 57% 수준
+- 누계 실적_해외 5,468백만(집행률 94%): 예산 대비 353백만 미달,[]연간 예산의 49% 수준, 인건비 비중 57%
+- 개발 그룹 리소스 투입률: 국내↑해외↓</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">- 누계 실적 1,211백만(집행률 67%)
+- 미달 사유: 예산 대비 감가상각비 -489백만, 수도광열비 -254 미달 주원인(임차료 +136 초과)
+- 계단식 감소: 1Q 월평균 278백만 → 2Q 월평균 126백만 (분당 감가상각비 월1.6억 → 분당 임차료 월 0.45억)
+- 6월 1.2억 구성: 용인 0.8억(64%), 분당 0.4억(36%)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*용인 0.8억(총 0.9억): 감가상각비 0.4억(총 0.45억), 건물관리수수료 0.27억(총 0.32억), []수도광열비 0.04억(총 0.07억), 보험료 0.06억
+*분당 0.4억(총 1.9억): 임차료 0.45억(총 1.44억), 수광비 0.01억(총 0.05억: 챔버, 카페), []건물관리수수료 0.01억(총 0.4억: 관리비 0.6억 중 건물배부 0.2억 - 실비수입 0.2억), 보험료 -0.03억(환급)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*수정한 부분에 커서를 갖다대면 메모 형태로 표기
+[STB] 4월, 5월: STB License Fee/Nagra 4월 -84백만, 5월 +84백만 (선급비용 결산 조정 지연)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -366,7 +423,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -409,7 +466,34 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
@@ -465,7 +549,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -496,8 +580,14 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2127,7 +2217,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05630F61-30FB-4CF7-B3FF-D0B93533C1C1}">
   <dimension ref="A1:D40"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="18.625" customWidth="1"/>
     <col min="2" max="2" width="12.625" customWidth="1"/>
@@ -2135,7 +2225,7 @@
     <col min="4" max="4" width="95.625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2149,7 +2239,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="49.5">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -2161,7 +2251,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="49.5">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
@@ -2173,7 +2263,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="49.5">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -2185,7 +2275,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="33" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="33">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -2199,7 +2289,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="49.5">
       <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
@@ -2213,7 +2303,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="33" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="33">
       <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
@@ -2227,7 +2317,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="49.5">
       <c r="A8" s="5" t="s">
         <v>4</v>
       </c>
@@ -2239,7 +2329,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="49.5">
       <c r="A9" s="5" t="s">
         <v>4</v>
       </c>
@@ -2251,7 +2341,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="49.5">
       <c r="A10" s="5" t="s">
         <v>5</v>
       </c>
@@ -2263,7 +2353,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="33" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="33">
       <c r="A11" s="5" t="s">
         <v>6</v>
       </c>
@@ -2277,7 +2367,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="49.5">
       <c r="A12" s="5" t="s">
         <v>6</v>
       </c>
@@ -2291,7 +2381,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="33" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" ht="33">
       <c r="A13" s="5" t="s">
         <v>6</v>
       </c>
@@ -2305,7 +2395,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" ht="49.5">
       <c r="A14" s="4" t="s">
         <v>4</v>
       </c>
@@ -2317,7 +2407,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" ht="49.5">
       <c r="A15" s="4" t="s">
         <v>4</v>
       </c>
@@ -2329,7 +2419,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" ht="49.5">
       <c r="A16" s="4" t="s">
         <v>5</v>
       </c>
@@ -2341,7 +2431,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="33" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="33">
       <c r="A17" s="4" t="s">
         <v>6</v>
       </c>
@@ -2355,7 +2445,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" ht="49.5">
       <c r="A18" s="4" t="s">
         <v>6</v>
       </c>
@@ -2369,7 +2459,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="33" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" ht="33">
       <c r="A19" s="4" t="s">
         <v>6</v>
       </c>
@@ -2383,7 +2473,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" ht="49.5">
       <c r="A20" s="5" t="s">
         <v>4</v>
       </c>
@@ -2395,7 +2485,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="66" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" ht="66">
       <c r="A21" s="5" t="s">
         <v>4</v>
       </c>
@@ -2407,7 +2497,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" ht="49.5">
       <c r="A22" s="5" t="s">
         <v>5</v>
       </c>
@@ -2419,7 +2509,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" ht="49.5">
       <c r="A23" s="5" t="s">
         <v>6</v>
       </c>
@@ -2433,7 +2523,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" ht="49.5">
       <c r="A24" s="5" t="s">
         <v>6</v>
       </c>
@@ -2447,7 +2537,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" ht="49.5">
       <c r="A25" s="5" t="s">
         <v>6</v>
       </c>
@@ -2461,7 +2551,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" ht="49.5">
       <c r="A26" s="4" t="s">
         <v>4</v>
       </c>
@@ -2473,7 +2563,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="66" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" ht="66">
       <c r="A27" s="4" t="s">
         <v>4</v>
       </c>
@@ -2485,7 +2575,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" ht="49.5">
       <c r="A28" s="4" t="s">
         <v>5</v>
       </c>
@@ -2497,7 +2587,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" ht="49.5">
       <c r="A29" s="4" t="s">
         <v>6</v>
       </c>
@@ -2511,7 +2601,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" ht="49.5">
       <c r="A30" s="4" t="s">
         <v>6</v>
       </c>
@@ -2525,7 +2615,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" ht="49.5">
       <c r="A31" s="4" t="s">
         <v>6</v>
       </c>
@@ -2539,7 +2629,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" ht="49.5">
       <c r="A32" s="5" t="s">
         <v>4</v>
       </c>
@@ -2548,10 +2638,10 @@
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="9" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="49.5">
       <c r="A33" s="5" t="s">
         <v>4</v>
       </c>
@@ -2560,10 +2650,10 @@
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="82.5" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="66">
       <c r="A34" s="5" t="s">
         <v>5</v>
       </c>
@@ -2572,10 +2662,10 @@
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="49.5">
       <c r="A35" s="5" t="s">
         <v>6</v>
       </c>
@@ -2586,10 +2676,10 @@
         <v>7</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="66" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="66">
       <c r="A36" s="5" t="s">
         <v>6</v>
       </c>
@@ -2599,11 +2689,11 @@
       <c r="C36" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D36" s="9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="D36" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="132">
       <c r="A37" s="5" t="s">
         <v>6</v>
       </c>
@@ -2614,10 +2704,10 @@
         <v>9</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="33">
       <c r="A38" s="5" t="s">
         <v>6</v>
       </c>
@@ -2627,11 +2717,19 @@
       <c r="C38" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D38" s="10" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D38" s="11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="12" t="s">
+        <v>57</v>
+      </c>
       <c r="D40" s="6"/>
     </row>
   </sheetData>

--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCDF45F0-351C-4F4F-BA09-C52D19A0EDF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CDF1514-295A-4240-979B-CB9ADD98F4D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-885" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -384,13 +384,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>- 누계 실적 7,440백만(집행률 97%): 연간 예산의 51% 수준,[] 6개월 경과 진도(50%)에 부합
-- 누계 실적_국내 1,973백만(집행률 108%): 예산 대비 147백만 초과,[]연간 예산의 57% 수준
-- 누계 실적_해외 5,468백만(집행률 94%): 예산 대비 353백만 미달,[]연간 예산의 49% 수준, 인건비 비중 57%
-- 개발 그룹 리소스 투입률: 국내↑해외↓</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">- 누계 실적 1,211백만(집행률 67%)
 - 미달 사유: 예산 대비 감가상각비 -489백만, 수도광열비 -254 미달 주원인(임차료 +136 초과)
@@ -416,6 +409,13 @@
   <si>
     <t>*수정한 부분에 커서를 갖다대면 메모 형태로 표기
 [STB] 4월, 5월: STB License Fee/Nagra 4월 -84백만, 5월 +84백만 (선급비용 결산 조정 지연)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 7,440백만(집행률 97%): 연간 예산의 51% 수준, 6개월 경과 진도(50%)에 부합
+- 누계 실적_국내 1,973백만(집행률 108%): 예산 대비 147백만 초과, 연간 예산의 57% 수준
+- 누계 실적_해외 5,468백만(집행률 94%): 예산 대비 353백만 미달, 연간 예산의 49% 수준, 인건비 비중 57%
+- 개발 그룹 리소스 투입률: 국내↑해외↓</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="49.5">
@@ -2704,7 +2704,7 @@
         <v>9</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="33">
@@ -2718,7 +2718,7 @@
         <v>22</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="39" spans="1:4">

--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CDF1514-295A-4240-979B-CB9ADD98F4D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9659ED10-89FF-4A19-81B0-91DAF92E3795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
+    <workbookView xWindow="28680" yWindow="-885" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -286,12 +286,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>- 당월 실적 2,537백만(집행률 100%): 본사 1,747백만(집행률 91%), 법인 790백만(집행률 131%)
-- HUMAX(공통) 541백만으로 전월 대비 175백만 감소
-- STB 536백만으로 1~5월 평균 대비 60백만 초과</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>- 누계 실적 15,549백만(집행률 97%): 본사 11,065백만(집행률 92%), 법인 4,484백만(집행률 112%)
 - 집행률 초과: HUMAX(공통) 119%, EVCS(국내) 108%
 - 집행률 미달: 건물 67%, STB 90%, EVCS(해외) 94%</t>
@@ -301,13 +295,6 @@
     <t>- 누계 실적 2,916백만(집행률 90%)
 - 미달 사유: Media그룹 New Aura/iWedia 외주개발용역비 6월 누계 5.18억원 미집행 (SW이슈로 집행 지연)
 - 4월, 5월 트렌드 왜곡: STB License Fee/Nagra 4월 -84백만, 5월 +84백만 (선급비용 결산 조정 지연)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 3,666백만(집행률 119%)
-- 초과 사유: 예산 대비 Staff부문 +466백만(급여 +217, 특허처리비 +105)
-   *CEO주식보상비용 2.5억원, VVC 특허처리비 예산 누락
-- 1월, 5월 일회성 증가: 26년 외부감사 착수금 200백만(1월), 15차 주식선택권 취소 216백만(5월)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -416,6 +403,19 @@
 - 누계 실적_국내 1,973백만(집행률 108%): 예산 대비 147백만 초과, 연간 예산의 57% 수준
 - 누계 실적_해외 5,468백만(집행률 94%): 예산 대비 353백만 미달, 연간 예산의 49% 수준, 인건비 비중 57%
 - 개발 그룹 리소스 투입률: 국내↑해외↓</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 당월 실적 2,537백만(집행률 100%): 본사 1,747백만(집행률 91%), 법인 790백만(집행률 131%)
+- HUMAX(공통) 541백만으로 전월 대비 175백만 감소 (전월 주식보상비용 2.2억 집행 영향)
+- STB 536백만으로 1~5월 평균 대비 60백만 초과</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 3,666백만(집행률 119%)
+- 초과 사유: 예산 대비 Staff부문 +466백만(급여 +217, 특허처리비 +105)
+   *CEO주식보상비용 6월 누계 2.5억원, VVC 특허처리비 예산 누락
+- 1월, 5월 일회성 증가: 26년 외부감사 착수금 200백만(1월), 15차 주식선택권 취소 216백만(5월)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="9" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="49.5">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="66">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="49.5">
@@ -2676,7 +2676,7 @@
         <v>7</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="66">
@@ -2690,7 +2690,7 @@
         <v>8</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="132">
@@ -2704,7 +2704,7 @@
         <v>9</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="33">
@@ -2718,17 +2718,17 @@
         <v>22</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D40" s="6"/>
     </row>

--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9659ED10-89FF-4A19-81B0-91DAF92E3795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A053871A-4F4C-4D0E-8504-18534FBDDD75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-885" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Summary!$A$1:$D$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Summary!$A$1:$D$40</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -283,18 +283,6 @@
     <t>- 누계 실적 1,089백만(집행률 72%) — 예산 대비 416백만 미달
 - 예산 대비 감가상각비 -326백만, 수도광열비 -168 미달 주원인(임차료 +91 초과)
 - 1~3월 평균 278백만 → 4~5월 평균 128백만 — 4월부터 계단식 감소</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 15,549백만(집행률 97%): 본사 11,065백만(집행률 92%), 법인 4,484백만(집행률 112%)
-- 집행률 초과: HUMAX(공통) 119%, EVCS(국내) 108%
-- 집행률 미달: 건물 67%, STB 90%, EVCS(해외) 94%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 2,916백만(집행률 90%)
-- 미달 사유: Media그룹 New Aura/iWedia 외주개발용역비 6월 누계 5.18억원 미집행 (SW이슈로 집행 지연)
-- 4월, 5월 트렌드 왜곡: STB License Fee/Nagra 4월 -84백만, 5월 +84백만 (선급비용 결산 조정 지연)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -371,10 +359,46 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>*수정한 부분에 커서를 갖다대면 메모 형태로 표기
+[STB] 4월, 5월: STB License Fee/Nagra 4월 -84백만, 5월 +84백만 (선급비용 결산 조정 지연)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 7,440백만(집행률 97%): 연간 예산의 51% 수준, 6개월 경과 진도(50%)에 부합
+- 누계 실적_국내 1,973백만(집행률 108%): 예산 대비 147백만 초과, 연간 예산의 57% 수준
+- 누계 실적_해외 5,468백만(집행률 94%): 예산 대비 353백만 미달, 연간 예산의 49% 수준, 인건비 비중 57%
+- 개발 그룹 리소스 투입률: 국내↑해외↓</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 당월 실적 2,537백만(집행률 100%): 본사 1,747백만(집행률 91%), 법인 790백만(집행률 131%)
+- HUMAX(공통) 541백만으로 전월 대비 175백만 감소 (전월 주식보상비용 216백만 일회성 집행)
+- STB 536백만으로 1~5월 평균 대비 60백만 초과 (Charter B&amp;M Legal fee 71백만 집행)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 15,549백만(집행률 97%): 본사 11,065백만(집행률 92%), 법인 4,484백만(집행률 112%)
+- 집행률 초과: HUMAX(공통) 119%(주식보상 비용, VVC특허처리비 등) EVCS(국내) 108%
+- 집행률 미달: 건물 67%(1Q 94%, 2Q 41%), STB 90%, EVCS(해외) 94%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 2,916백만(집행률 90%)
+- Media그룹 New Aura/iWedia 외주개발용역비 6월 누계 5.18억원 미집행 (SW이슈로 집행 지연)
+- 4월, 5월 트렌드 왜곡: STB License Fee/Nagra 4월 -84백만, 5월 +84백만 (선급비용 결산 조정 지연)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 누계 실적 3,666백만(집행률 119%)
+- 예산 대비 Staff부문 +466백만: 급여 +217백만(주식보상비용), 특허처리비 +105백만(VVC)
+- 1월, 5월 일회성 증가: 26년 외부감사 착수금 200백만(1월), 주식보상비용 216백만(5월)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">- 누계 실적 1,211백만(집행률 67%)
-- 미달 사유: 예산 대비 감가상각비 -489백만, 수도광열비 -254 미달 주원인(임차료 +136 초과)
-- 계단식 감소: 1Q 월평균 278백만 → 2Q 월평균 126백만 (분당 감가상각비 월1.6억 → 분당 임차료 월 0.45억)
+- 예산 대비 감가상각비 -489백만, 임차료 +136백만, 수도광열비 -254백만 
+- 계단식 감소: 1Q 월평균 278백만 → 2Q 월평균 126백만 (분당 감가상각비 163백만 → 분당 임차료 월 45백만)
 - 6월 1.2억 구성: 용인 0.8억(64%), 분당 0.4억(36%)
 </t>
     </r>
@@ -388,34 +412,9 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>*용인 0.8억(총 0.9억): 감가상각비 0.4억(총 0.45억), 건물관리수수료 0.27억(총 0.32억), []수도광열비 0.04억(총 0.07억), 보험료 0.06억
-*분당 0.4억(총 1.9억): 임차료 0.45억(총 1.44억), 수광비 0.01억(총 0.05억: 챔버, 카페), []건물관리수수료 0.01억(총 0.4억: 관리비 0.6억 중 건물배부 0.2억 - 실비수입 0.2억), 보험료 -0.03억(환급)</t>
+      <t>*용인 0.8억(총 0.9억): 감가상각비 0.4억(총 0.45억), 건물관리수수료 0.27억(총 0.32억), 수도광열비 0.04억(총 0.07억), 보험료 0.06억
+*분당 0.4억(총 1.9억): 임차료 0.45억(총 1.44억), 수광비 0.01억(총 0.05억: 챔버, 카페), 건물관리수수료 0.01억(총 0.4억: 관리비 0.6억 중 건물배부 0.2억 - 실비수입 0.2억), 보험료 -0.03억(환급)</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>*수정한 부분에 커서를 갖다대면 메모 형태로 표기
-[STB] 4월, 5월: STB License Fee/Nagra 4월 -84백만, 5월 +84백만 (선급비용 결산 조정 지연)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 7,440백만(집행률 97%): 연간 예산의 51% 수준, 6개월 경과 진도(50%)에 부합
-- 누계 실적_국내 1,973백만(집행률 108%): 예산 대비 147백만 초과, 연간 예산의 57% 수준
-- 누계 실적_해외 5,468백만(집행률 94%): 예산 대비 353백만 미달, 연간 예산의 49% 수준, 인건비 비중 57%
-- 개발 그룹 리소스 투입률: 국내↑해외↓</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 당월 실적 2,537백만(집행률 100%): 본사 1,747백만(집행률 91%), 법인 790백만(집행률 131%)
-- HUMAX(공통) 541백만으로 전월 대비 175백만 감소 (전월 주식보상비용 2.2억 집행 영향)
-- STB 536백만으로 1~5월 평균 대비 60백만 초과</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 3,666백만(집행률 119%)
-- 초과 사유: 예산 대비 Staff부문 +466백만(급여 +217, 특허처리비 +105)
-   *CEO주식보상비용 6월 누계 2.5억원, VVC 특허처리비 예산 누락
-- 1월, 5월 일회성 증가: 26년 외부감사 착수금 200백만(1월), 15차 주식선택권 취소 216백만(5월)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2216,6 +2215,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05630F61-30FB-4CF7-B3FF-D0B93533C1C1}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:D40"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -2239,7 +2239,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="49.5">
+    <row r="2" spans="1:4" ht="49.5" hidden="1">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -2251,7 +2251,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="49.5">
+    <row r="3" spans="1:4" ht="49.5" hidden="1">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
@@ -2263,7 +2263,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="49.5">
+    <row r="4" spans="1:4" ht="49.5" hidden="1">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -2275,7 +2275,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="33">
+    <row r="5" spans="1:4" ht="33" hidden="1">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -2289,7 +2289,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="49.5">
+    <row r="6" spans="1:4" ht="49.5" hidden="1">
       <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
@@ -2303,7 +2303,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="33">
+    <row r="7" spans="1:4" ht="33" hidden="1">
       <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
@@ -2317,7 +2317,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="49.5">
+    <row r="8" spans="1:4" ht="49.5" hidden="1">
       <c r="A8" s="5" t="s">
         <v>4</v>
       </c>
@@ -2329,7 +2329,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="49.5">
+    <row r="9" spans="1:4" ht="49.5" hidden="1">
       <c r="A9" s="5" t="s">
         <v>4</v>
       </c>
@@ -2341,7 +2341,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="49.5">
+    <row r="10" spans="1:4" ht="49.5" hidden="1">
       <c r="A10" s="5" t="s">
         <v>5</v>
       </c>
@@ -2353,7 +2353,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="33">
+    <row r="11" spans="1:4" ht="33" hidden="1">
       <c r="A11" s="5" t="s">
         <v>6</v>
       </c>
@@ -2367,7 +2367,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="49.5">
+    <row r="12" spans="1:4" ht="49.5" hidden="1">
       <c r="A12" s="5" t="s">
         <v>6</v>
       </c>
@@ -2381,7 +2381,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="33">
+    <row r="13" spans="1:4" ht="33" hidden="1">
       <c r="A13" s="5" t="s">
         <v>6</v>
       </c>
@@ -2395,7 +2395,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="49.5">
+    <row r="14" spans="1:4" ht="49.5" hidden="1">
       <c r="A14" s="4" t="s">
         <v>4</v>
       </c>
@@ -2407,7 +2407,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="49.5">
+    <row r="15" spans="1:4" ht="49.5" hidden="1">
       <c r="A15" s="4" t="s">
         <v>4</v>
       </c>
@@ -2419,7 +2419,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="49.5">
+    <row r="16" spans="1:4" ht="49.5" hidden="1">
       <c r="A16" s="4" t="s">
         <v>5</v>
       </c>
@@ -2431,7 +2431,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="33">
+    <row r="17" spans="1:4" ht="33" hidden="1">
       <c r="A17" s="4" t="s">
         <v>6</v>
       </c>
@@ -2445,7 +2445,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="49.5">
+    <row r="18" spans="1:4" ht="49.5" hidden="1">
       <c r="A18" s="4" t="s">
         <v>6</v>
       </c>
@@ -2459,7 +2459,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="33">
+    <row r="19" spans="1:4" ht="33" hidden="1">
       <c r="A19" s="4" t="s">
         <v>6</v>
       </c>
@@ -2473,7 +2473,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="49.5">
+    <row r="20" spans="1:4" ht="49.5" hidden="1">
       <c r="A20" s="5" t="s">
         <v>4</v>
       </c>
@@ -2485,7 +2485,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="66">
+    <row r="21" spans="1:4" ht="66" hidden="1">
       <c r="A21" s="5" t="s">
         <v>4</v>
       </c>
@@ -2497,7 +2497,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="49.5">
+    <row r="22" spans="1:4" ht="49.5" hidden="1">
       <c r="A22" s="5" t="s">
         <v>5</v>
       </c>
@@ -2509,7 +2509,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="49.5">
+    <row r="23" spans="1:4" ht="49.5" hidden="1">
       <c r="A23" s="5" t="s">
         <v>6</v>
       </c>
@@ -2523,7 +2523,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="49.5">
+    <row r="24" spans="1:4" ht="49.5" hidden="1">
       <c r="A24" s="5" t="s">
         <v>6</v>
       </c>
@@ -2537,7 +2537,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="49.5">
+    <row r="25" spans="1:4" ht="49.5" hidden="1">
       <c r="A25" s="5" t="s">
         <v>6</v>
       </c>
@@ -2551,7 +2551,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="49.5">
+    <row r="26" spans="1:4" ht="49.5" hidden="1">
       <c r="A26" s="4" t="s">
         <v>4</v>
       </c>
@@ -2563,7 +2563,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="66">
+    <row r="27" spans="1:4" ht="66" hidden="1">
       <c r="A27" s="4" t="s">
         <v>4</v>
       </c>
@@ -2575,7 +2575,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="49.5">
+    <row r="28" spans="1:4" ht="49.5" hidden="1">
       <c r="A28" s="4" t="s">
         <v>5</v>
       </c>
@@ -2587,7 +2587,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="49.5">
+    <row r="29" spans="1:4" ht="49.5" hidden="1">
       <c r="A29" s="4" t="s">
         <v>6</v>
       </c>
@@ -2601,7 +2601,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="49.5">
+    <row r="30" spans="1:4" ht="49.5" hidden="1">
       <c r="A30" s="4" t="s">
         <v>6</v>
       </c>
@@ -2615,7 +2615,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="49.5">
+    <row r="31" spans="1:4" ht="49.5" hidden="1">
       <c r="A31" s="4" t="s">
         <v>6</v>
       </c>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="9" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="49.5">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="9" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="66">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="9" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="49.5">
@@ -2676,10 +2676,10 @@
         <v>7</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="66">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="49.5">
       <c r="A36" s="5" t="s">
         <v>6</v>
       </c>
@@ -2690,7 +2690,7 @@
         <v>8</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="132">
@@ -2704,7 +2704,7 @@
         <v>9</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="33">
@@ -2718,22 +2718,29 @@
         <v>22</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" hidden="1">
       <c r="A39" s="12" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" hidden="1">
       <c r="A40" s="12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D40" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D37" xr:uid="{05630F61-30FB-4CF7-B3FF-D0B93533C1C1}"/>
+  <autoFilter ref="A1:D40" xr:uid="{05630F61-30FB-4CF7-B3FF-D0B93533C1C1}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="6월"/>
+        <filter val="6월 누계"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A053871A-4F4C-4D0E-8504-18534FBDDD75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{494B0312-0B7D-467F-A162-BCDB3658FFA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-885" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
@@ -364,43 +364,43 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>- 누계 실적 7,440백만(집행률 97%): 연간 예산의 51% 수준, 6개월 경과 진도(50%)에 부합
-- 누계 실적_국내 1,973백만(집행률 108%): 예산 대비 147백만 초과, 연간 예산의 57% 수준
-- 누계 실적_해외 5,468백만(집행률 94%): 예산 대비 353백만 미달, 연간 예산의 49% 수준, 인건비 비중 57%
-- 개발 그룹 리소스 투입률: 국내↑해외↓</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 당월 실적 2,537백만(집행률 100%): 본사 1,747백만(집행률 91%), 법인 790백만(집행률 131%)
-- HUMAX(공통) 541백만으로 전월 대비 175백만 감소 (전월 주식보상비용 216백만 일회성 집행)
-- STB 536백만으로 1~5월 평균 대비 60백만 초과 (Charter B&amp;M Legal fee 71백만 집행)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 15,549백만(집행률 97%): 본사 11,065백만(집행률 92%), 법인 4,484백만(집행률 112%)
-- 집행률 초과: HUMAX(공통) 119%(주식보상 비용, VVC특허처리비 등) EVCS(국내) 108%
-- 집행률 미달: 건물 67%(1Q 94%, 2Q 41%), STB 90%, EVCS(해외) 94%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 2,916백만(집행률 90%)
-- Media그룹 New Aura/iWedia 외주개발용역비 6월 누계 5.18억원 미집행 (SW이슈로 집행 지연)
-- 4월, 5월 트렌드 왜곡: STB License Fee/Nagra 4월 -84백만, 5월 +84백만 (선급비용 결산 조정 지연)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 누계 실적 3,666백만(집행률 119%)
-- 예산 대비 Staff부문 +466백만: 급여 +217백만(주식보상비용), 특허처리비 +105백만(VVC)
-- 1월, 5월 일회성 증가: 26년 외부감사 착수금 200백만(1월), 주식보상비용 216백만(5월)</t>
+    <t>누계 실적 2,916백만(집행률 90%)
+Media그룹 New Aura/iWedia 외주개발용역비 6월 누계 5.18억원 미집행 (SW이슈로 집행 지연)
+4월, 5월 트렌드 왜곡: STB License Fee/Nagra 4월 -84백만, 5월 +84백만 (선급비용 결산 조정 지연)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>당월 실적 2,537백만(집행률 100%): 본사 1,747백만(집행률 91%), 법인 790백만(집행률 131%)
+ - HUMAX(공통) 541백만으로 전월 대비 175백만 감소 (전월 주식보상비용 216백만 일회성 집행)
+STB 536백만으로 1~5월 평균 대비 60백만 초과 (Charter B&amp;M Legal fee 71백만 집행)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>누계 실적 15,549백만(집행률 97%): 본사 11,065백만(집행률 92%), 법인 4,484백만(집행률 112%)
+ - 집행률 초과: HUMAX(공통) 119%(주식보상 비용, VVC특허처리비 등) EVCS(국내) 108%
+ - 집행률 미달: 건물 67%(1Q 94%, 2Q 41%), STB 90%, EVCS(해외) 94%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>누계 실적 7,440백만(집행률 97%): 연간 예산의 51% 수준, 6개월 경과 진도(50%)에 부합
+  - 누계 실적_국내 1,973백만(집행률 108%): 예산 대비 147백만 초과, 연간 예산의 57% 수준
+  - 누계 실적_해외 5,468백만(집행률 94%): 예산 대비 353백만 미달, 연간 예산의 49% 수준, 인건비 비중 57%
+개발 그룹 리소스 투입률: 국내↑해외↓</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>누계 실적 3,666백만(집행률 119%)
+ - 예산 대비 Staff부문 +466백만: 급여 +217백만(주식보상비용), 특허처리비 +105백만(VVC)
+1월, 5월 일회성 증가: 26년 외부감사 착수금 200백만(1월), 주식보상비용 216백만(5월)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
-      <t xml:space="preserve">- 누계 실적 1,211백만(집행률 67%)
-- 예산 대비 감가상각비 -489백만, 임차료 +136백만, 수도광열비 -254백만 
-- 계단식 감소: 1Q 월평균 278백만 → 2Q 월평균 126백만 (분당 감가상각비 163백만 → 분당 임차료 월 45백만)
-- 6월 1.2억 구성: 용인 0.8억(64%), 분당 0.4억(36%)
-</t>
+      <t xml:space="preserve">누계 실적 1,211백만(집행률 67%)
+ - 예산 대비 감가상각비 -489백만, 임차료 +136백만, 수도광열비 -254백만 
+계단식 감소: 1Q 월평균 278백만 → 2Q 월평균 126백만 (분당 감가상각비 163백만 → 분당 임차료 월 45백만)
+6월 1.2억 구성: 용인 0.8억(64%), 분당 0.4억(36%)
+ - </t>
     </r>
     <r>
       <rPr>
@@ -412,8 +412,8 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>*용인 0.8억(총 0.9억): 감가상각비 0.4억(총 0.45억), 건물관리수수료 0.27억(총 0.32억), 수도광열비 0.04억(총 0.07억), 보험료 0.06억
-*분당 0.4억(총 1.9억): 임차료 0.45억(총 1.44억), 수광비 0.01억(총 0.05억: 챔버, 카페), 건물관리수수료 0.01억(총 0.4억: 관리비 0.6억 중 건물배부 0.2억 - 실비수입 0.2억), 보험료 -0.03억(환급)</t>
+      <t>용인 0.8억(총 0.9억): 감가상각비 0.4억(총 0.45억), 건물관리수수료 0.27억(총 0.32억), 수도광열비 0.04억(총 0.07억), 보험료 0.06억
+ - 분당 0.4억(총 1.9억): 임차료 0.45억(총 1.44억), 수광비 0.01억(총 0.05억: 챔버, 카페), 건물관리수수료 0.01억(총 0.4억: 관리비 0.6억 중 건물배부 0.2억 - 실비수입 0.2억), 보험료 -0.03억(환급)</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="9" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="49.5">
@@ -2676,7 +2676,7 @@
         <v>7</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="49.5">

--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{494B0312-0B7D-467F-A162-BCDB3658FFA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5954C42B-9EB2-438F-9AB5-A611ADE25132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-885" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Summary!$A$1:$D$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Summary!$A$1:$D$43</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="72">
   <si>
     <t>탭</t>
   </si>
@@ -106,10 +106,6 @@
   </si>
   <si>
     <t>4월 누계</t>
-  </si>
-  <si>
-    <t>월별 배부액 추이 (왜곡 수정ver)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>- 당월 실적 2,818백만(집행률 88%) — 예산 대비 미달
@@ -364,42 +360,53 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>누계 실적 2,916백만(집행률 90%)
-Media그룹 New Aura/iWedia 외주개발용역비 6월 누계 5.18억원 미집행 (SW이슈로 집행 지연)
-4월, 5월 트렌드 왜곡: STB License Fee/Nagra 4월 -84백만, 5월 +84백만 (선급비용 결산 조정 지연)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>당월 실적 2,537백만(집행률 100%): 본사 1,747백만(집행률 91%), 법인 790백만(집행률 131%)
- - HUMAX(공통) 541백만으로 전월 대비 175백만 감소 (전월 주식보상비용 216백만 일회성 집행)
-STB 536백만으로 1~5월 평균 대비 60백만 초과 (Charter B&amp;M Legal fee 71백만 집행)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>누계 실적 15,549백만(집행률 97%): 본사 11,065백만(집행률 92%), 법인 4,484백만(집행률 112%)
- - 집행률 초과: HUMAX(공통) 119%(주식보상 비용, VVC특허처리비 등) EVCS(국내) 108%
- - 집행률 미달: 건물 67%(1Q 94%, 2Q 41%), STB 90%, EVCS(해외) 94%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>누계 실적 7,440백만(집행률 97%): 연간 예산의 51% 수준, 6개월 경과 진도(50%)에 부합
-  - 누계 실적_국내 1,973백만(집행률 108%): 예산 대비 147백만 초과, 연간 예산의 57% 수준
-  - 누계 실적_해외 5,468백만(집행률 94%): 예산 대비 353백만 미달, 연간 예산의 49% 수준, 인건비 비중 57%
-개발 그룹 리소스 투입률: 국내↑해외↓</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>누계 실적 3,666백만(집행률 119%)
- - 예산 대비 Staff부문 +466백만: 급여 +217백만(주식보상비용), 특허처리비 +105백만(VVC)
-1월, 5월 일회성 증가: 26년 외부감사 착수금 200백만(1월), 주식보상비용 216백만(5월)</t>
+    <t>월별 배부액 추이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1월, 5월 일회성 증가
+ - 26년 외부감사 착수금 200백만(1월), 주식보상비용 34백만(3월) 216백만(5월)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>계단식 감소: 1Q 월평균 278백만 → 2Q 월평균 126백만
+ - 분당 감가상각비 163백만 → 분당 임차료 월 45백만)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4월, 5월 트렌드 왜곡
+ - STB License Fee/Nagra 4월 -84백만, 5월 +84백만 (선급비용 결산 조정 지연)
+1~5월 평균 대비 6월 60백만 초과
+ - Charter B&amp;M Legal fee 71백만 집행 (추가 비용 집행 예상)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예산 대비 실적 집행률: 합계 2,537백만(100%), 본사 1,747백만(91%), 법인 790백만(131%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예산 대비 실적 집행률: 합계 15,549백만(97%), 본사 11,065백만(92%), 법인 4,484백만(112%)
+ - 예산 초과: HUMAX(공통) 119%(주식보상 비용, VVC특허처리비 등) EVCS(국내) 108%
+ - 예산 미달: 건물 67%(1Q 94%, 2Q 41%), STB 90%, EVCS(해외) 94%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[지급수수료]
+New Aura/iWedia 외주개발용역비 518백만 추가 집행 가능성 있음 (SW이슈로 지연)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[인건비]
+주식보상비용 250백만 (예산 외, 일회성)
+[지급수수료]
+특허처리비 105백만 초과 집행 (VVC 예산 누락 영향)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
-      <t xml:space="preserve">누계 실적 1,211백만(집행률 67%)
- - 예산 대비 감가상각비 -489백만, 임차료 +136백만, 수도광열비 -254백만 
-계단식 감소: 1Q 월평균 278백만 → 2Q 월평균 126백만 (분당 감가상각비 163백만 → 분당 임차료 월 45백만)
-6월 1.2억 구성: 용인 0.8억(64%), 분당 0.4억(36%)
+      <t xml:space="preserve">1Q 월평균 278백만 → 2Q 월평균 126백만로 감소 확인 (4월 임대차 계약 영향)
+10월 사옥 이전 전까지 아래 비용 구조로 예상
+ - Ex 6월 1.2억: 용인 0.8억(64%), 분당 0.4억(36%)
  - </t>
     </r>
     <r>
@@ -415,6 +422,40 @@
       <t>용인 0.8억(총 0.9억): 감가상각비 0.4억(총 0.45억), 건물관리수수료 0.27억(총 0.32억), 수도광열비 0.04억(총 0.07억), 보험료 0.06억
  - 분당 0.4억(총 1.9억): 임차료 0.45억(총 1.44억), 수광비 0.01억(총 0.05억: 챔버, 카페), 건물관리수수료 0.01억(총 0.4억: 관리비 0.6억 중 건물배부 0.2억 - 실비수입 0.2억), 보험료 -0.03억(환급)</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>배부액 추이</t>
+  </si>
+  <si>
+    <t>배부액 추이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예산 대비 실적 집행률 체크</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예산 대비 실적 집행률 체크
+, 국내/해외 비중 체크</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>실적 특이사항 기재</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>건물 비용 구성 및 예측, 실적 특이사항 기재</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>추이 상 특이점 기재 (증가)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예산 대비 실적 집행률: 합계 7,440백만(97%), 본사 5,487백만(95%), 법인 1,953백만(104%)
+국내/해외 비중: 1Q 국내실적 24%/해외실적 76%, 2Q 국내실적 29%/해외실적 71%
+ - 개발 그룹 리소스 투입 변화: 해외→국내</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -519,7 +560,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -542,13 +583,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -588,6 +640,12 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -609,16 +667,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>409575</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>447675</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -633,8 +691,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11620500" y="14725650"/>
-          <a:ext cx="4391025" cy="17659350"/>
+          <a:off x="15373350" y="447675"/>
+          <a:ext cx="4391025" cy="16182975"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2215,14 +2273,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05630F61-30FB-4CF7-B3FF-D0B93533C1C1}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="18.625" customWidth="1"/>
     <col min="2" max="2" width="12.625" customWidth="1"/>
     <col min="3" max="3" width="18.625" customWidth="1"/>
     <col min="4" max="4" width="95.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9" style="13"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="21.95" customHeight="1">
@@ -2248,7 +2306,7 @@
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="49.5" hidden="1">
@@ -2260,7 +2318,7 @@
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="49.5" hidden="1">
@@ -2272,7 +2330,7 @@
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="33" hidden="1">
@@ -2286,7 +2344,7 @@
         <v>7</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="49.5" hidden="1">
@@ -2300,7 +2358,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="33" hidden="1">
@@ -2314,7 +2372,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="49.5" hidden="1">
@@ -2326,7 +2384,7 @@
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="49.5" hidden="1">
@@ -2338,7 +2396,7 @@
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="49.5" hidden="1">
@@ -2350,7 +2408,7 @@
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="33" hidden="1">
@@ -2364,7 +2422,7 @@
         <v>7</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="49.5" hidden="1">
@@ -2378,7 +2436,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="33" hidden="1">
@@ -2392,7 +2450,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="49.5" hidden="1">
@@ -2404,7 +2462,7 @@
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="49.5" hidden="1">
@@ -2416,7 +2474,7 @@
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="49.5" hidden="1">
@@ -2428,10 +2486,10 @@
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="33" hidden="1">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="33" hidden="1">
       <c r="A17" s="4" t="s">
         <v>6</v>
       </c>
@@ -2442,10 +2500,10 @@
         <v>7</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="49.5" hidden="1">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="49.5" hidden="1">
       <c r="A18" s="4" t="s">
         <v>6</v>
       </c>
@@ -2456,10 +2514,10 @@
         <v>8</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="33" hidden="1">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="33" hidden="1">
       <c r="A19" s="4" t="s">
         <v>6</v>
       </c>
@@ -2470,10 +2528,10 @@
         <v>9</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="49.5" hidden="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="49.5" hidden="1">
       <c r="A20" s="5" t="s">
         <v>4</v>
       </c>
@@ -2482,10 +2540,10 @@
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="66" hidden="1">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="66" hidden="1">
       <c r="A21" s="5" t="s">
         <v>4</v>
       </c>
@@ -2494,10 +2552,10 @@
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="49.5" hidden="1">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="49.5" hidden="1">
       <c r="A22" s="5" t="s">
         <v>5</v>
       </c>
@@ -2506,10 +2564,10 @@
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="49.5" hidden="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="49.5" hidden="1">
       <c r="A23" s="5" t="s">
         <v>6</v>
       </c>
@@ -2520,10 +2578,10 @@
         <v>7</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="49.5" hidden="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="49.5" hidden="1">
       <c r="A24" s="5" t="s">
         <v>6</v>
       </c>
@@ -2534,10 +2592,10 @@
         <v>8</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="49.5" hidden="1">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="49.5" hidden="1">
       <c r="A25" s="5" t="s">
         <v>6</v>
       </c>
@@ -2548,10 +2606,10 @@
         <v>9</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="49.5" hidden="1">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="49.5" hidden="1">
       <c r="A26" s="4" t="s">
         <v>4</v>
       </c>
@@ -2560,10 +2618,10 @@
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="66" hidden="1">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="66" hidden="1">
       <c r="A27" s="4" t="s">
         <v>4</v>
       </c>
@@ -2572,10 +2630,10 @@
       </c>
       <c r="C27" s="4"/>
       <c r="D27" s="7" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="49.5" hidden="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="49.5" hidden="1">
       <c r="A28" s="4" t="s">
         <v>5</v>
       </c>
@@ -2584,10 +2642,10 @@
       </c>
       <c r="C28" s="4"/>
       <c r="D28" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="49.5" hidden="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="49.5" hidden="1">
       <c r="A29" s="4" t="s">
         <v>6</v>
       </c>
@@ -2598,10 +2656,10 @@
         <v>7</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="49.5" hidden="1">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="49.5" hidden="1">
       <c r="A30" s="4" t="s">
         <v>6</v>
       </c>
@@ -2612,10 +2670,10 @@
         <v>8</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="49.5" hidden="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="49.5" hidden="1">
       <c r="A31" s="4" t="s">
         <v>6</v>
       </c>
@@ -2626,10 +2684,10 @@
         <v>9</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="49.5">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
         <v>4</v>
       </c>
@@ -2638,10 +2696,13 @@
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="49.5">
+        <v>59</v>
+      </c>
+      <c r="E32" s="14" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="49.5">
       <c r="A33" s="5" t="s">
         <v>4</v>
       </c>
@@ -2650,10 +2711,13 @@
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="66">
+        <v>60</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="49.5">
       <c r="A34" s="5" t="s">
         <v>5</v>
       </c>
@@ -2662,10 +2726,13 @@
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="49.5">
+        <v>71</v>
+      </c>
+      <c r="E34" s="14" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="33">
       <c r="A35" s="5" t="s">
         <v>6</v>
       </c>
@@ -2676,10 +2743,13 @@
         <v>7</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="49.5">
+        <v>61</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="66">
       <c r="A36" s="5" t="s">
         <v>6</v>
       </c>
@@ -2690,10 +2760,13 @@
         <v>8</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="132">
+        <v>62</v>
+      </c>
+      <c r="E36" s="14" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="115.5">
       <c r="A37" s="5" t="s">
         <v>6</v>
       </c>
@@ -2704,43 +2777,93 @@
         <v>9</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="33">
+        <v>63</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="33">
       <c r="A38" s="5" t="s">
-        <v>6</v>
+        <v>65</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" hidden="1">
-      <c r="A39" s="12" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" hidden="1">
-      <c r="A40" s="12" t="s">
+      <c r="E38" s="14" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="66">
+      <c r="A39" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E39" s="14" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="33">
+      <c r="A40" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E40" s="14" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="33">
+      <c r="A41" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E41" s="14" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="D40" s="6"/>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D43" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D40" xr:uid="{05630F61-30FB-4CF7-B3FF-D0B93533C1C1}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="6월"/>
-        <filter val="6월 누계"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:D43" xr:uid="{05630F61-30FB-4CF7-B3FF-D0B93533C1C1}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5954C42B-9EB2-438F-9AB5-A611ADE25132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78864755-86C6-4053-98E6-9587137293E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-885" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
@@ -369,11 +369,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>계단식 감소: 1Q 월평균 278백만 → 2Q 월평균 126백만
- - 분당 감가상각비 163백만 → 분당 임차료 월 45백만)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>4월, 5월 트렌드 왜곡
  - STB License Fee/Nagra 4월 -84백만, 5월 +84백만 (선급비용 결산 조정 지연)
 1~5월 평균 대비 6월 60백만 초과
@@ -400,6 +395,39 @@
 주식보상비용 250백만 (예산 외, 일회성)
 [지급수수료]
 특허처리비 105백만 초과 집행 (VVC 예산 누락 영향)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>배부액 추이</t>
+  </si>
+  <si>
+    <t>배부액 추이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예산 대비 실적 집행률 체크</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예산 대비 실적 집행률 체크
+, 국내/해외 비중 체크</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>실적 특이사항 기재</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>건물 비용 구성 및 예측, 실적 특이사항 기재</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>추이 상 특이점 기재 (증가)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>계단식 감소: 1Q 월평균 278백만 → 2Q 월평균 126백만
+ - 분당 감가상각비 163백만 → 분당 임차료 월 45백만</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -420,41 +448,13 @@
         <scheme val="minor"/>
       </rPr>
       <t>용인 0.8억(총 0.9억): 감가상각비 0.4억(총 0.45억), 건물관리수수료 0.27억(총 0.32억), 수도광열비 0.04억(총 0.07억), 보험료 0.06억
- - 분당 0.4억(총 1.9억): 임차료 0.45억(총 1.44억), 수광비 0.01억(총 0.05억: 챔버, 카페), 건물관리수수료 0.01억(총 0.4억: 관리비 0.6억 중 건물배부 0.2억 - 실비수입 0.2억), 보험료 -0.03억(환급)</t>
+ - 분당 0.4억(총 1.9억): 임차료 0.45억(총 1.44억), 수광비 0.01억(총 0.05억: 챔버, 카페), 건물관리수수료 0.01억(총 0.4억: 관리비 0.6억 - 실비수입 0.2억), 보험료 -0.03억(환급)</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>배부액 추이</t>
-  </si>
-  <si>
-    <t>배부액 추이</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>예산 대비 실적 집행률 체크</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>예산 대비 실적 집행률 체크
-, 국내/해외 비중 체크</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>실적 특이사항 기재</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>건물 비용 구성 및 예측, 실적 특이사항 기재</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>추이 상 특이점 기재 (증가)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>예산 대비 실적 집행률: 합계 7,440백만(97%), 본사 5,487백만(95%), 법인 1,953백만(104%)
-국내/해외 비중: 1Q 국내실적 24%/해외실적 76%, 2Q 국내실적 29%/해외실적 71%
+국내/해외 비중: 1Q 국내 24%/해외 76%, 2Q 국내 29%/해외 71%
  - 개발 그룹 리소스 투입 변화: 해외→국내</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2696,10 +2696,10 @@
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="49.5">
@@ -2711,10 +2711,10 @@
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="49.5">
@@ -2729,7 +2729,7 @@
         <v>71</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="33">
@@ -2743,10 +2743,10 @@
         <v>7</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="66">
@@ -2760,10 +2760,10 @@
         <v>8</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="115.5">
@@ -2777,15 +2777,15 @@
         <v>9</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="33">
       <c r="A38" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>13</v>
@@ -2797,12 +2797,12 @@
         <v>54</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="66">
       <c r="A39" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>13</v>
@@ -2811,15 +2811,15 @@
         <v>7</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E39" s="14" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="33">
       <c r="A40" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>13</v>
@@ -2831,12 +2831,12 @@
         <v>56</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="33">
       <c r="A41" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>13</v>
@@ -2845,10 +2845,10 @@
         <v>9</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="42" spans="1:5">

--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78864755-86C6-4053-98E6-9587137293E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED345FBC-68FB-4B17-B456-E6C695C67CE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-885" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Summary!$A$1:$D$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Summary!$A$1:$D$52</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="88">
   <si>
     <t>탭</t>
   </si>
@@ -457,6 +457,79 @@
 국내/해외 비중: 1Q 국내 24%/해외 76%, 2Q 국내 29%/해외 71%
  - 개발 그룹 리소스 투입 변화: 해외→국내</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7월</t>
+  </si>
+  <si>
+    <t>예산 대비 실적 집행률: 합계 2,661백만(102%), 본사 2,032백만(101%), 법인 628백만(107%)</t>
+  </si>
+  <si>
+    <t>예산 대비 실적 집행률 체크</t>
+  </si>
+  <si>
+    <t>7월 누계</t>
+  </si>
+  <si>
+    <t>예산 대비 실적 집행률: 합계 18,210백만(98%), 본사 13,097백만(94%), 법인 5,112백만(111%)
+ - 예산 초과: HUMAX(공통) 127%(합병 자문·평가 수수료, 주식보상 비용, VVC특허처리비 등) EVCS(국내) 108%
+ - 예산 미달: 건물 64%(1Q 94%, 2Q 41%, 7월 50%), STB 94%, EVCS(해외) 91%</t>
+  </si>
+  <si>
+    <t>예산 대비 실적 집행률: 합계 8,524백만(95%), 본사 6,335백만(92%), 법인 2,189백만(102%)
+국내/해외 비중: 1Q 국내 24%/해외 76%, 2Q 국내 29%/해외 71%, 7월 국내 28%/해외 72%
+ - 개발 그룹 리소스 투입 변화: 해외→국내</t>
+  </si>
+  <si>
+    <t>예산 대비 실적 집행률 체크
+, 국내/해외 비중 체크</t>
+  </si>
+  <si>
+    <t>[지급수수료]
+외주개발용역비 누계 200백만(집행률 28%) — 예산 대비 524백만 미달 (New Aura/iWedia SW이슈로 지연)
+Charter B&amp;M Legal fee 7월 55백만 추가 집행 (누계 127백만)</t>
+  </si>
+  <si>
+    <t>실적 특이사항 기재</t>
+  </si>
+  <si>
+    <t>[인건비]
+주식보상비용 250백만 (예산 외, 일회성)
+[지급수수료]
+7월 합병 자문·평가 수수료 350백만 (예산 외, 일회성)
+ - KB증권 200백만, 이촌회계법인 150백만
+특허처리비 105백만 초과 집행 (VVC 예산 누락 영향)</t>
+  </si>
+  <si>
+    <t>1Q 월평균 278백만 → 2Q 월평균 126백만로 감소 확인 (4월 임대차 계약 영향)
+7월 154백만 — 2Q 월평균 대비 29백만 증가 (티맥스수내타워 7월 임대차 관리비 신규 반영)
+10월 사옥 이전 전까지 아래 비용 구조로 예상
+ - Ex 6월 1.2억: 용인 0.8억(64%), 분당 0.4억(36%)
+ - 용인 0.8억(총 0.9억): 감가상각비 0.4억(총 0.45억), 건물관리수수료 0.27억(총 0.32억), 수도광열비 0.04억(총 0.07억), 보험료 0.06억
+ - 분당 0.4억(총 1.9억): 임차료 0.45억(총 1.44억), 수광비 0.01억(총 0.05억: 챔버, 카페), 건물관리수수료 0.01억(총 0.4억: 관리비 0.6억 - 실비수입 0.2억), 보험료 -0.03억(환급)</t>
+  </si>
+  <si>
+    <t>건물 비용 구성 및 예측, 실적 특이사항 기재</t>
+  </si>
+  <si>
+    <t>4월, 5월 트렌드 왜곡
+ - STB License Fee/Nagra 4월 -84백만, 5월 +84백만 (선급비용 결산 조정 지연)
+1~5월 평균 대비 6월 60백만, 7월 45백만 초과
+ - Charter B&amp;M Legal fee 7월 55백만 추가 집행 (누계 127백만)</t>
+  </si>
+  <si>
+    <t>추이 상 특이점 기재 (증가)</t>
+  </si>
+  <si>
+    <t>1월, 5월, 7월 일회성 증가
+ - 26년 외부감사 착수금 200백만(1월), 주식보상비용 34백만(3월) 216백만(5월)
+7월 880백만 — 1~6월 평균 611백만 대비 269백만 초과
+ - 합병 자문·평가 수수료 350백만 집행</t>
+  </si>
+  <si>
+    <t>계단식 감소: 1Q 월평균 278백만 → 2Q 월평균 126백만 · 7월 154백만
+ - 분당 감가상각비 163백만 → 분당 임차료 월 45백만
+ - 7월 티맥스수내타워 임대차 관리비 29백만 신규 반영</t>
   </si>
 </sst>
 </file>
@@ -600,7 +673,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -618,9 +691,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -645,6 +715,30 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -675,7 +769,7 @@
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>447675</xdr:colOff>
-      <xdr:row>89</xdr:row>
+      <xdr:row>98</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2273,14 +2367,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05630F61-30FB-4CF7-B3FF-D0B93533C1C1}">
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="18.625" customWidth="1"/>
     <col min="2" max="2" width="12.625" customWidth="1"/>
     <col min="3" max="3" width="18.625" customWidth="1"/>
     <col min="4" max="4" width="95.625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9" style="13"/>
+    <col min="5" max="5" width="9" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="21.95" customHeight="1">
@@ -2305,7 +2399,7 @@
         <v>14</v>
       </c>
       <c r="C2" s="4"/>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2317,7 +2411,7 @@
         <v>15</v>
       </c>
       <c r="C3" s="4"/>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>42</v>
       </c>
     </row>
@@ -2329,7 +2423,7 @@
         <v>15</v>
       </c>
       <c r="C4" s="4"/>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="6" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2343,7 +2437,7 @@
       <c r="C5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="6" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2357,7 +2451,7 @@
       <c r="C6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -2371,7 +2465,7 @@
       <c r="C7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="6" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2383,7 +2477,7 @@
         <v>16</v>
       </c>
       <c r="C8" s="5"/>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="7" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2395,7 +2489,7 @@
         <v>17</v>
       </c>
       <c r="C9" s="5"/>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="7" t="s">
         <v>43</v>
       </c>
     </row>
@@ -2407,7 +2501,7 @@
         <v>17</v>
       </c>
       <c r="C10" s="5"/>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="7" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2421,7 +2515,7 @@
       <c r="C11" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="7" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2435,7 +2529,7 @@
       <c r="C12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="7" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2449,7 +2543,7 @@
       <c r="C13" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="7" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2461,7 +2555,7 @@
         <v>18</v>
       </c>
       <c r="C14" s="4"/>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="6" t="s">
         <v>44</v>
       </c>
     </row>
@@ -2473,7 +2567,7 @@
         <v>19</v>
       </c>
       <c r="C15" s="4"/>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="6" t="s">
         <v>45</v>
       </c>
     </row>
@@ -2485,7 +2579,7 @@
         <v>19</v>
       </c>
       <c r="C16" s="4"/>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="6" t="s">
         <v>32</v>
       </c>
     </row>
@@ -2499,7 +2593,7 @@
       <c r="C17" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="6" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2513,7 +2607,7 @@
       <c r="C18" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="6" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2527,7 +2621,7 @@
       <c r="C19" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="6" t="s">
         <v>35</v>
       </c>
     </row>
@@ -2539,7 +2633,7 @@
         <v>20</v>
       </c>
       <c r="C20" s="5"/>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="7" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2551,7 +2645,7 @@
         <v>21</v>
       </c>
       <c r="C21" s="5"/>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="7" t="s">
         <v>46</v>
       </c>
     </row>
@@ -2563,7 +2657,7 @@
         <v>21</v>
       </c>
       <c r="C22" s="5"/>
-      <c r="D22" s="8" t="s">
+      <c r="D22" s="7" t="s">
         <v>37</v>
       </c>
     </row>
@@ -2577,7 +2671,7 @@
       <c r="C23" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2591,7 +2685,7 @@
       <c r="C24" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="7" t="s">
         <v>47</v>
       </c>
     </row>
@@ -2605,7 +2699,7 @@
       <c r="C25" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="D25" s="7" t="s">
         <v>48</v>
       </c>
     </row>
@@ -2617,7 +2711,7 @@
         <v>10</v>
       </c>
       <c r="C26" s="4"/>
-      <c r="D26" s="7" t="s">
+      <c r="D26" s="6" t="s">
         <v>39</v>
       </c>
     </row>
@@ -2629,7 +2723,7 @@
         <v>11</v>
       </c>
       <c r="C27" s="4"/>
-      <c r="D27" s="7" t="s">
+      <c r="D27" s="6" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2641,7 +2735,7 @@
         <v>11</v>
       </c>
       <c r="C28" s="4"/>
-      <c r="D28" s="7" t="s">
+      <c r="D28" s="6" t="s">
         <v>40</v>
       </c>
     </row>
@@ -2655,7 +2749,7 @@
       <c r="C29" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2669,7 +2763,7 @@
       <c r="C30" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="D30" s="6" t="s">
         <v>50</v>
       </c>
     </row>
@@ -2683,7 +2777,7 @@
       <c r="C31" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="D31" s="6" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2695,10 +2789,10 @@
         <v>12</v>
       </c>
       <c r="C32" s="5"/>
-      <c r="D32" s="9" t="s">
+      <c r="D32" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="E32" s="14" t="s">
+      <c r="E32" s="13" t="s">
         <v>64</v>
       </c>
     </row>
@@ -2710,10 +2804,10 @@
         <v>13</v>
       </c>
       <c r="C33" s="5"/>
-      <c r="D33" s="9" t="s">
+      <c r="D33" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="E33" s="14" t="s">
+      <c r="E33" s="13" t="s">
         <v>64</v>
       </c>
     </row>
@@ -2725,10 +2819,10 @@
         <v>13</v>
       </c>
       <c r="C34" s="5"/>
-      <c r="D34" s="9" t="s">
+      <c r="D34" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E34" s="14" t="s">
+      <c r="E34" s="13" t="s">
         <v>65</v>
       </c>
     </row>
@@ -2742,10 +2836,10 @@
       <c r="C35" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D35" s="9" t="s">
+      <c r="D35" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="E35" s="14" t="s">
+      <c r="E35" s="13" t="s">
         <v>66</v>
       </c>
     </row>
@@ -2759,10 +2853,10 @@
       <c r="C36" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D36" s="10" t="s">
+      <c r="D36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="E36" s="14" t="s">
+      <c r="E36" s="13" t="s">
         <v>66</v>
       </c>
     </row>
@@ -2776,10 +2870,10 @@
       <c r="C37" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D37" s="9" t="s">
+      <c r="D37" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="E37" s="14" t="s">
+      <c r="E37" s="13" t="s">
         <v>67</v>
       </c>
     </row>
@@ -2793,10 +2887,10 @@
       <c r="C38" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D38" s="11" t="s">
+      <c r="D38" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="E38" s="14" t="s">
+      <c r="E38" s="13" t="s">
         <v>68</v>
       </c>
     </row>
@@ -2810,10 +2904,10 @@
       <c r="C39" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D39" s="11" t="s">
+      <c r="D39" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="E39" s="14" t="s">
+      <c r="E39" s="13" t="s">
         <v>68</v>
       </c>
     </row>
@@ -2827,10 +2921,10 @@
       <c r="C40" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D40" s="11" t="s">
+      <c r="D40" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="E40" s="14" t="s">
+      <c r="E40" s="13" t="s">
         <v>68</v>
       </c>
     </row>
@@ -2844,26 +2938,178 @@
       <c r="C41" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D41" s="11" t="s">
+      <c r="D41" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="E41" s="14" t="s">
+      <c r="E41" s="13" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="12" t="s">
+    <row r="42" spans="1:5" ht="49.5">
+      <c r="A42" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="C42" s="15"/>
+      <c r="D42" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="E42" s="14" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="49.5">
+      <c r="A43" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B43" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C43" s="15"/>
+      <c r="D43" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="E43" s="14" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="99">
+      <c r="A44" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B44" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C44" s="15"/>
+      <c r="D44" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="E44" s="14" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="49.5">
+      <c r="A45" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="B45" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C45" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D45" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="E45" s="14" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="99">
+      <c r="A46" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="B46" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C46" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="E46" s="14" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="132">
+      <c r="A47" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="B47" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C47" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="E47" s="14" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="66">
+      <c r="A48" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="B48" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C48" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D48" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="E48" s="14" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="66">
+      <c r="A49" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="B49" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C49" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="E49" s="14" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="49.5">
+      <c r="A50" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="B50" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C50" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="E50" s="14" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="11" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="12" t="s">
+      <c r="B51" s="19"/>
+      <c r="C51" s="19"/>
+      <c r="D51" s="20"/>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="D43" s="6"/>
+      <c r="B52" s="19"/>
+      <c r="C52" s="19"/>
+      <c r="D52" s="21"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D43" xr:uid="{05630F61-30FB-4CF7-B3FF-D0B93533C1C1}"/>
+  <autoFilter ref="A1:D52" xr:uid="{05630F61-30FB-4CF7-B3FF-D0B93533C1C1}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED345FBC-68FB-4B17-B456-E6C695C67CE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C134944D-2FC8-4A8D-8EBC-5EBB8ABC6347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-885" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
+    <workbookView xWindow="28680" yWindow="-135" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -485,11 +485,6 @@
 , 국내/해외 비중 체크</t>
   </si>
   <si>
-    <t>[지급수수료]
-외주개발용역비 누계 200백만(집행률 28%) — 예산 대비 524백만 미달 (New Aura/iWedia SW이슈로 지연)
-Charter B&amp;M Legal fee 7월 55백만 추가 집행 (누계 127백만)</t>
-  </si>
-  <si>
     <t>실적 특이사항 기재</t>
   </si>
   <si>
@@ -512,31 +507,41 @@
     <t>건물 비용 구성 및 예측, 실적 특이사항 기재</t>
   </si>
   <si>
-    <t>4월, 5월 트렌드 왜곡
- - STB License Fee/Nagra 4월 -84백만, 5월 +84백만 (선급비용 결산 조정 지연)
-1~5월 평균 대비 6월 60백만, 7월 45백만 초과
- - Charter B&amp;M Legal fee 7월 55백만 추가 집행 (누계 127백만)</t>
-  </si>
-  <si>
     <t>추이 상 특이점 기재 (증가)</t>
-  </si>
-  <si>
-    <t>1월, 5월, 7월 일회성 증가
- - 26년 외부감사 착수금 200백만(1월), 주식보상비용 34백만(3월) 216백만(5월)
-7월 880백만 — 1~6월 평균 611백만 대비 269백만 초과
- - 합병 자문·평가 수수료 350백만 집행</t>
   </si>
   <si>
     <t>계단식 감소: 1Q 월평균 278백만 → 2Q 월평균 126백만 · 7월 154백만
  - 분당 감가상각비 163백만 → 분당 임차료 월 45백만
  - 7월 티맥스수내타워 임대차 관리비 29백만 신규 반영</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4월, 5월 트렌드 왜곡
+ - STB License Fee/Nagra 4월 -84백만, 5월 +84백만 (선급비용 결산 조정 지연)
+1~5월 평균 476백만 대비 6월 60백만, 7월 45백만 초과
+ - Charter B&amp;M Legal fee 6월 72백만, 7월 55백만 집행 (누계 127백만)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1월, 3월, 5월, 7월 일회성 증가
+ - 1월: 26년 외부감사 착수금 200백만
+ - 3월, 5월: 주식보상비용 3월 34백만, 5월 216백만
+ - 7월: 합병 자문·평가 수수료 350백만 (KB증권, 이촌회계법인)
+1~6월 평균 611백만 대비 7월 269백만 초과</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[지급수수료]
+New Aura/iWedia 외주개발용역비 518백만 추가 집행 가능성 있음 (SW이슈로 지연)
+Charter Legal fee/B&amp;M Legal fee 127백만 집행 (소송 재개)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -612,8 +617,16 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -629,6 +642,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEEF2F7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -673,7 +692,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -716,9 +735,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -726,9 +742,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
@@ -739,6 +752,18 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2367,8 +2392,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05630F61-30FB-4CF7-B3FF-D0B93533C1C1}">
-  <dimension ref="A1:E52"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:I58"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.625" customWidth="1"/>
     <col min="2" max="2" width="12.625" customWidth="1"/>
@@ -2377,7 +2403,7 @@
     <col min="5" max="5" width="9" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2391,7 +2417,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="49.5" hidden="1">
+    <row r="2" spans="1:4" ht="49.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -2403,7 +2429,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="49.5" hidden="1">
+    <row r="3" spans="1:4" ht="49.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
@@ -2415,7 +2441,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="49.5" hidden="1">
+    <row r="4" spans="1:4" ht="49.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -2427,7 +2453,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="33" hidden="1">
+    <row r="5" spans="1:4" ht="33" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -2441,7 +2467,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="49.5" hidden="1">
+    <row r="6" spans="1:4" ht="49.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
@@ -2455,7 +2481,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="33" hidden="1">
+    <row r="7" spans="1:4" ht="33" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
@@ -2469,7 +2495,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="49.5" hidden="1">
+    <row r="8" spans="1:4" ht="49.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>4</v>
       </c>
@@ -2481,7 +2507,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="49.5" hidden="1">
+    <row r="9" spans="1:4" ht="49.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>4</v>
       </c>
@@ -2493,7 +2519,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="49.5" hidden="1">
+    <row r="10" spans="1:4" ht="49.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>5</v>
       </c>
@@ -2505,7 +2531,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="33" hidden="1">
+    <row r="11" spans="1:4" ht="33" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>6</v>
       </c>
@@ -2519,7 +2545,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="49.5" hidden="1">
+    <row r="12" spans="1:4" ht="49.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>6</v>
       </c>
@@ -2533,7 +2559,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="33" hidden="1">
+    <row r="13" spans="1:4" ht="33" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>6</v>
       </c>
@@ -2547,7 +2573,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="49.5" hidden="1">
+    <row r="14" spans="1:4" ht="49.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>4</v>
       </c>
@@ -2559,7 +2585,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="49.5" hidden="1">
+    <row r="15" spans="1:4" ht="49.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>4</v>
       </c>
@@ -2571,7 +2597,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="49.5" hidden="1">
+    <row r="16" spans="1:4" ht="49.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>5</v>
       </c>
@@ -2583,7 +2609,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="33" hidden="1">
+    <row r="17" spans="1:5" ht="33" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>6</v>
       </c>
@@ -2597,7 +2623,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="49.5" hidden="1">
+    <row r="18" spans="1:5" ht="49.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>6</v>
       </c>
@@ -2611,7 +2637,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="33" hidden="1">
+    <row r="19" spans="1:5" ht="33" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>6</v>
       </c>
@@ -2625,7 +2651,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="49.5" hidden="1">
+    <row r="20" spans="1:5" ht="49.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>4</v>
       </c>
@@ -2637,7 +2663,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="66" hidden="1">
+    <row r="21" spans="1:5" ht="66" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>4</v>
       </c>
@@ -2649,7 +2675,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="49.5" hidden="1">
+    <row r="22" spans="1:5" ht="49.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>5</v>
       </c>
@@ -2661,7 +2687,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="49.5" hidden="1">
+    <row r="23" spans="1:5" ht="49.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>6</v>
       </c>
@@ -2675,7 +2701,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="49.5" hidden="1">
+    <row r="24" spans="1:5" ht="49.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>6</v>
       </c>
@@ -2689,7 +2715,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="49.5" hidden="1">
+    <row r="25" spans="1:5" ht="49.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>6</v>
       </c>
@@ -2703,7 +2729,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="49.5" hidden="1">
+    <row r="26" spans="1:5" ht="49.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>4</v>
       </c>
@@ -2715,7 +2741,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="66" hidden="1">
+    <row r="27" spans="1:5" ht="66" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>4</v>
       </c>
@@ -2727,7 +2753,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="49.5" hidden="1">
+    <row r="28" spans="1:5" ht="49.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>5</v>
       </c>
@@ -2739,7 +2765,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="49.5" hidden="1">
+    <row r="29" spans="1:5" ht="49.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>6</v>
       </c>
@@ -2753,7 +2779,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="49.5" hidden="1">
+    <row r="30" spans="1:5" ht="49.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>6</v>
       </c>
@@ -2767,7 +2793,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="49.5" hidden="1">
+    <row r="31" spans="1:5" ht="49.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>6</v>
       </c>
@@ -2781,7 +2807,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>4</v>
       </c>
@@ -2796,7 +2822,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="49.5">
+    <row r="33" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>4</v>
       </c>
@@ -2811,7 +2837,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="49.5">
+    <row r="34" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>5</v>
       </c>
@@ -2826,7 +2852,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="33">
+    <row r="35" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>6</v>
       </c>
@@ -2843,7 +2869,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="66">
+    <row r="36" spans="1:5" ht="66" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
         <v>6</v>
       </c>
@@ -2860,7 +2886,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="115.5">
+    <row r="37" spans="1:5" ht="115.5" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>6</v>
       </c>
@@ -2877,7 +2903,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="33">
+    <row r="38" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>63</v>
       </c>
@@ -2894,7 +2920,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="66">
+    <row r="39" spans="1:5" ht="66" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>62</v>
       </c>
@@ -2911,7 +2937,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="33">
+    <row r="40" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
         <v>62</v>
       </c>
@@ -2928,7 +2954,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="33">
+    <row r="41" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>62</v>
       </c>
@@ -2945,171 +2971,226 @@
         <v>68</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="49.5">
-      <c r="A42" s="15" t="s">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="C42" s="15"/>
-      <c r="D42" s="16" t="s">
+      <c r="C42" s="14"/>
+      <c r="D42" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="E42" s="14" t="s">
+      <c r="E42" s="13" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="49.5">
-      <c r="A43" s="15" t="s">
+    <row r="43" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A43" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="B43" s="15" t="s">
+      <c r="B43" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="C43" s="15"/>
-      <c r="D43" s="16" t="s">
+      <c r="C43" s="14"/>
+      <c r="D43" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="E43" s="14" t="s">
+      <c r="E43" s="13" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="99">
-      <c r="A44" s="15" t="s">
+    <row r="44" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A44" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B44" s="15" t="s">
+      <c r="B44" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="C44" s="15"/>
-      <c r="D44" s="16" t="s">
+      <c r="C44" s="14"/>
+      <c r="D44" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="E44" s="14" t="s">
+      <c r="E44" s="13" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="49.5">
-      <c r="A45" s="15" t="s">
+    <row r="45" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A45" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B45" s="15" t="s">
+      <c r="B45" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="C45" s="15" t="s">
+      <c r="C45" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D45" s="16" t="s">
+      <c r="D45" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="E45" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="E45" s="14" t="s">
+    </row>
+    <row r="46" spans="1:5" ht="99" x14ac:dyDescent="0.3">
+      <c r="A46" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B46" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="C46" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="16" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" ht="99">
-      <c r="A46" s="15" t="s">
+      <c r="E46" s="13" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="132" x14ac:dyDescent="0.3">
+      <c r="A47" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B46" s="15" t="s">
+      <c r="B47" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="C46" s="15" t="s">
+      <c r="C47" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="E47" s="13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="66" x14ac:dyDescent="0.3">
+      <c r="A48" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="B48" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="C48" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D48" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="E48" s="13" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="A49" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="B49" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="C49" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D46" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="E46" s="14" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" ht="132">
-      <c r="A47" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="B47" s="15" t="s">
+      <c r="D49" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="E49" s="13" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A50" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="B50" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="C47" s="15" t="s">
+      <c r="C50" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D47" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="E47" s="14" t="s">
+      <c r="D50" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="E50" s="13" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="66">
-      <c r="A48" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="B48" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="C48" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D48" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="E48" s="14" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" ht="66">
-      <c r="A49" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="B49" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="C49" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D49" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="E49" s="14" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" ht="49.5">
-      <c r="A50" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="B50" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="C50" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="D50" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="E50" s="14" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="B51" s="19"/>
-      <c r="C51" s="19"/>
-      <c r="D51" s="20"/>
-    </row>
-    <row r="52" spans="1:5">
+      <c r="B51" s="17"/>
+      <c r="C51" s="17"/>
+      <c r="D51" s="18"/>
+    </row>
+    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="B52" s="19"/>
-      <c r="C52" s="19"/>
-      <c r="D52" s="21"/>
+      <c r="B52" s="17"/>
+      <c r="C52" s="17"/>
+      <c r="D52" s="19"/>
+      <c r="E52" s="20"/>
+      <c r="F52" s="21"/>
+      <c r="G52" s="21"/>
+      <c r="H52" s="21"/>
+      <c r="I52" s="21"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E53" s="20"/>
+      <c r="F53" s="21"/>
+      <c r="G53" s="21"/>
+      <c r="H53" s="21"/>
+      <c r="I53" s="21"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E54" s="20"/>
+      <c r="F54" s="21"/>
+      <c r="G54" s="21"/>
+      <c r="H54" s="21"/>
+      <c r="I54" s="21"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E55" s="20"/>
+      <c r="F55" s="21"/>
+      <c r="G55" s="21"/>
+      <c r="H55" s="21"/>
+      <c r="I55" s="21"/>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E56" s="20"/>
+      <c r="F56" s="21"/>
+      <c r="G56" s="21"/>
+      <c r="H56" s="21"/>
+      <c r="I56" s="21"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E57" s="20"/>
+      <c r="F57" s="21"/>
+      <c r="G57" s="21"/>
+      <c r="H57" s="21"/>
+      <c r="I57" s="21"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E58" s="20"/>
+      <c r="F58" s="21"/>
+      <c r="G58" s="21"/>
+      <c r="H58" s="21"/>
+      <c r="I58" s="21"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D52" xr:uid="{05630F61-30FB-4CF7-B3FF-D0B93533C1C1}"/>
+  <autoFilter ref="A1:D52" xr:uid="{05630F61-30FB-4CF7-B3FF-D0B93533C1C1}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="6월 누계"/>
+        <filter val="7월"/>
+        <filter val="7월 누계"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C134944D-2FC8-4A8D-8EBC-5EBB8ABC6347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66D795EB-6CF9-4175-9133-475156AD5231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-135" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
@@ -431,8 +431,74 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>예산 대비 실적 집행률: 합계 7,440백만(97%), 본사 5,487백만(95%), 법인 1,953백만(104%)
+국내/해외 비중: 1Q 국내 24%/해외 76%, 2Q 국내 29%/해외 71%
+ - 개발 그룹 리소스 투입 변화: 해외→국내</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7월</t>
+  </si>
+  <si>
+    <t>예산 대비 실적 집행률: 합계 2,661백만(102%), 본사 2,032백만(101%), 법인 628백만(107%)</t>
+  </si>
+  <si>
+    <t>예산 대비 실적 집행률 체크</t>
+  </si>
+  <si>
+    <t>7월 누계</t>
+  </si>
+  <si>
+    <t>예산 대비 실적 집행률: 합계 8,524백만(95%), 본사 6,335백만(92%), 법인 2,189백만(102%)
+국내/해외 비중: 1Q 국내 24%/해외 76%, 2Q 국내 29%/해외 71%, 7월 국내 28%/해외 72%
+ - 개발 그룹 리소스 투입 변화: 해외→국내</t>
+  </si>
+  <si>
+    <t>예산 대비 실적 집행률 체크
+, 국내/해외 비중 체크</t>
+  </si>
+  <si>
+    <t>실적 특이사항 기재</t>
+  </si>
+  <si>
+    <t>건물 비용 구성 및 예측, 실적 특이사항 기재</t>
+  </si>
+  <si>
+    <t>추이 상 특이점 기재 (증가)</t>
+  </si>
+  <si>
+    <t>4월, 5월 트렌드 왜곡
+ - STB License Fee/Nagra 4월 -84백만, 5월 +84백만 (선급비용 결산 조정 지연)
+1~5월 평균 476백만 대비 6월 60백만, 7월 45백만 초과
+ - Charter B&amp;M Legal fee 6월 72백만, 7월 55백만 집행 (누계 127백만)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1월, 3월, 5월, 7월 일회성 증가
+ - 1월: 26년 외부감사 착수금 200백만
+ - 3월, 5월: 주식보상비용 3월 34백만, 5월 216백만
+ - 7월: 합병 자문·평가 수수료 350백만 (KB증권, 이촌회계법인)
+1~6월 평균 611백만 대비 7월 269백만 초과</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[지급수수료]
+New Aura/iWedia 외주개발용역비 518백만 추가 집행 가능성 있음 (SW이슈로 지연)
+Charter Legal fee/B&amp;M Legal fee 127백만 집행 (소송 재개)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[인건비]
+주식보상비용 250백만 (예산 외, 일회성)
+[지급수수료]
+합병 자문·평가 수수료 350백만(7월) (예산 외, 일회성)
+ - KB증권 200백만, 이촌회계법인 150백만
+특허처리비 105백만 초과 집행 (VVC 예산 누락 영향)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <r>
-      <t xml:space="preserve">1Q 월평균 278백만 → 2Q 월평균 126백만로 감소 확인 (4월 임대차 계약 영향)
+      <t xml:space="preserve">1Q 월평균 278백만 → 2Q 월평균 126백만 (4월 한화 임대차 계약 영향)
 10월 사옥 이전 전까지 아래 비용 구조로 예상
  - Ex 6월 1.2억: 용인 0.8억(64%), 분당 0.4억(36%)
  - </t>
@@ -453,87 +519,24 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>예산 대비 실적 집행률: 합계 7,440백만(97%), 본사 5,487백만(95%), 법인 1,953백만(104%)
-국내/해외 비중: 1Q 국내 24%/해외 76%, 2Q 국내 29%/해외 71%
- - 개발 그룹 리소스 투입 변화: 해외→국내</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>7월</t>
-  </si>
-  <si>
-    <t>예산 대비 실적 집행률: 합계 2,661백만(102%), 본사 2,032백만(101%), 법인 628백만(107%)</t>
-  </si>
-  <si>
-    <t>예산 대비 실적 집행률 체크</t>
-  </si>
-  <si>
-    <t>7월 누계</t>
-  </si>
-  <si>
     <t>예산 대비 실적 집행률: 합계 18,210백만(98%), 본사 13,097백만(94%), 법인 5,112백만(111%)
  - 예산 초과: HUMAX(공통) 127%(합병 자문·평가 수수료, 주식보상 비용, VVC특허처리비 등) EVCS(국내) 108%
  - 예산 미달: 건물 64%(1Q 94%, 2Q 41%, 7월 50%), STB 94%, EVCS(해외) 91%</t>
-  </si>
-  <si>
-    <t>예산 대비 실적 집행률: 합계 8,524백만(95%), 본사 6,335백만(92%), 법인 2,189백만(102%)
-국내/해외 비중: 1Q 국내 24%/해외 76%, 2Q 국내 29%/해외 71%, 7월 국내 28%/해외 72%
- - 개발 그룹 리소스 투입 변화: 해외→국내</t>
-  </si>
-  <si>
-    <t>예산 대비 실적 집행률 체크
-, 국내/해외 비중 체크</t>
-  </si>
-  <si>
-    <t>실적 특이사항 기재</t>
-  </si>
-  <si>
-    <t>[인건비]
-주식보상비용 250백만 (예산 외, 일회성)
-[지급수수료]
-7월 합병 자문·평가 수수료 350백만 (예산 외, 일회성)
- - KB증권 200백만, 이촌회계법인 150백만
-특허처리비 105백만 초과 집행 (VVC 예산 누락 영향)</t>
-  </si>
-  <si>
-    <t>1Q 월평균 278백만 → 2Q 월평균 126백만로 감소 확인 (4월 임대차 계약 영향)
-7월 154백만 — 2Q 월평균 대비 29백만 증가 (티맥스수내타워 7월 임대차 관리비 신규 반영)
-10월 사옥 이전 전까지 아래 비용 구조로 예상
- - Ex 6월 1.2억: 용인 0.8억(64%), 분당 0.4억(36%)
- - 용인 0.8억(총 0.9억): 감가상각비 0.4억(총 0.45억), 건물관리수수료 0.27억(총 0.32억), 수도광열비 0.04억(총 0.07억), 보험료 0.06억
- - 분당 0.4억(총 1.9억): 임차료 0.45억(총 1.44억), 수광비 0.01억(총 0.05억: 챔버, 카페), 건물관리수수료 0.01억(총 0.4억: 관리비 0.6억 - 실비수입 0.2억), 보험료 -0.03억(환급)</t>
-  </si>
-  <si>
-    <t>건물 비용 구성 및 예측, 실적 특이사항 기재</t>
-  </si>
-  <si>
-    <t>추이 상 특이점 기재 (증가)</t>
-  </si>
-  <si>
-    <t>계단식 감소: 1Q 월평균 278백만 → 2Q 월평균 126백만 · 7월 154백만
- - 분당 감가상각비 163백만 → 분당 임차료 월 45백만
- - 7월 티맥스수내타워 임대차 관리비 29백만 신규 반영</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4월, 5월 트렌드 왜곡
- - STB License Fee/Nagra 4월 -84백만, 5월 +84백만 (선급비용 결산 조정 지연)
-1~5월 평균 476백만 대비 6월 60백만, 7월 45백만 초과
- - Charter B&amp;M Legal fee 6월 72백만, 7월 55백만 집행 (누계 127백만)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1월, 3월, 5월, 7월 일회성 증가
- - 1월: 26년 외부감사 착수금 200백만
- - 3월, 5월: 주식보상비용 3월 34백만, 5월 216백만
- - 7월: 합병 자문·평가 수수료 350백만 (KB증권, 이촌회계법인)
-1~6월 평균 611백만 대비 7월 269백만 초과</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[지급수수료]
-New Aura/iWedia 외주개발용역비 518백만 추가 집행 가능성 있음 (SW이슈로 지연)
-Charter Legal fee/B&amp;M Legal fee 127백만 집행 (소송 재개)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>계단식 감소: 1Q 월평균 278백만 → 2Q 월평균 126백만 → 7월 154백만
+ - 4월~: 분당 감가상각비 163백만 → 분당 임차료 월 45백만
+ - 7월~: 티맥스수내타워 임대차 관리비 29백만(총 58백만) 신규 반영</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1Q 월평균 278백만 → 2Q 월평균 126백만 → 7월 154백만
+ - 4월: 한화 임대차계약 체결로 구조 변경
+ - 7월: 티맥스수내타워 관리비 집행 시작
+7월 1.5억: 용인 0.8억(51%), 분당 0.8억(49%)
+ - 용인 0.8억(총 0.9억): 감가상각비 0.4억(총 0.45억), 건물관리수수료 0.27억(총 0.32억), 수도광열비 0.05억(총 0.08억), 보험료 0.06억(총 0.06억)
+ - 분당 0.8억(총 2.5억): 임차료 0.45억(총 1.44억), 수광비 0.01억(총 0.03억: 챔버, 카페), 건물관리수수료 0.01억(총 0.4억: 관리비 0.59억 - 실비수입 0.2억), 건물관리수수료(티맥스) 0.3억(총 0.58억)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -541,7 +544,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -625,8 +628,15 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -642,12 +652,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEEF2F7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -744,6 +748,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -759,10 +766,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2392,14 +2396,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05630F61-30FB-4CF7-B3FF-D0B93533C1C1}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:I58"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.625" customWidth="1"/>
     <col min="2" max="2" width="12.625" customWidth="1"/>
     <col min="3" max="3" width="18.625" customWidth="1"/>
-    <col min="4" max="4" width="95.625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="116.875" style="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="12"/>
   </cols>
   <sheetData>
@@ -2417,7 +2420,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="49.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -2429,7 +2432,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="49.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
@@ -2441,7 +2444,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="49.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -2453,7 +2456,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="33" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -2467,7 +2470,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="49.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
@@ -2481,7 +2484,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="33" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
@@ -2495,7 +2498,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="49.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>4</v>
       </c>
@@ -2507,7 +2510,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="49.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>4</v>
       </c>
@@ -2519,7 +2522,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="49.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>5</v>
       </c>
@@ -2531,7 +2534,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="33" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>6</v>
       </c>
@@ -2545,7 +2548,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="49.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>6</v>
       </c>
@@ -2559,7 +2562,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" ht="33" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>6</v>
       </c>
@@ -2573,7 +2576,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="49.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>4</v>
       </c>
@@ -2585,7 +2588,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="49.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>4</v>
       </c>
@@ -2597,7 +2600,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="49.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>5</v>
       </c>
@@ -2609,7 +2612,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>6</v>
       </c>
@@ -2623,7 +2626,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="49.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>6</v>
       </c>
@@ -2637,7 +2640,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>6</v>
       </c>
@@ -2651,7 +2654,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="49.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>4</v>
       </c>
@@ -2663,7 +2666,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="66" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" ht="66" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>4</v>
       </c>
@@ -2675,7 +2678,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="49.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>5</v>
       </c>
@@ -2687,7 +2690,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="49.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>6</v>
       </c>
@@ -2701,7 +2704,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="49.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>6</v>
       </c>
@@ -2715,7 +2718,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="49.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>6</v>
       </c>
@@ -2729,7 +2732,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="49.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>4</v>
       </c>
@@ -2741,7 +2744,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="66" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" ht="66" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>4</v>
       </c>
@@ -2753,7 +2756,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="49.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>5</v>
       </c>
@@ -2765,7 +2768,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="49.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>6</v>
       </c>
@@ -2779,7 +2782,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="49.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>6</v>
       </c>
@@ -2793,7 +2796,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="49.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>6</v>
       </c>
@@ -2807,7 +2810,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>4</v>
       </c>
@@ -2846,7 +2849,7 @@
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E34" s="13" t="s">
         <v>65</v>
@@ -2897,7 +2900,7 @@
         <v>9</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="E37" s="13" t="s">
         <v>67</v>
@@ -2976,14 +2979,14 @@
         <v>4</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C42" s="14"/>
       <c r="D42" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="E42" s="13" t="s">
         <v>73</v>
-      </c>
-      <c r="E42" s="13" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
@@ -2991,14 +2994,14 @@
         <v>4</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C43" s="14"/>
       <c r="D43" s="15" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
@@ -3006,14 +3009,14 @@
         <v>5</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C44" s="14"/>
       <c r="D44" s="15" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
@@ -3021,16 +3024,16 @@
         <v>6</v>
       </c>
       <c r="B45" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C45" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D45" s="23" t="s">
-        <v>87</v>
+      <c r="D45" s="15" t="s">
+        <v>82</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="99" x14ac:dyDescent="0.3">
@@ -3038,16 +3041,16 @@
         <v>6</v>
       </c>
       <c r="B46" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C46" s="14" t="s">
         <v>8</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="132" x14ac:dyDescent="0.3">
@@ -3055,16 +3058,16 @@
         <v>6</v>
       </c>
       <c r="B47" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C47" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D47" s="15" t="s">
-        <v>81</v>
+      <c r="D47" s="23" t="s">
+        <v>87</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="66" x14ac:dyDescent="0.3">
@@ -3072,16 +3075,16 @@
         <v>62</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C48" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D48" s="22" t="s">
-        <v>85</v>
+      <c r="D48" s="17" t="s">
+        <v>80</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="82.5" x14ac:dyDescent="0.3">
@@ -3089,16 +3092,16 @@
         <v>62</v>
       </c>
       <c r="B49" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C49" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D49" s="22" t="s">
-        <v>86</v>
+      <c r="D49" s="17" t="s">
+        <v>81</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
@@ -3106,91 +3109,83 @@
         <v>62</v>
       </c>
       <c r="B50" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C50" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D50" s="22" t="s">
-        <v>84</v>
+      <c r="D50" s="17" t="s">
+        <v>86</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="B51" s="17"/>
-      <c r="C51" s="17"/>
-      <c r="D51" s="18"/>
-    </row>
-    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B51" s="18"/>
+      <c r="C51" s="18"/>
+      <c r="D51" s="19"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="B52" s="17"/>
-      <c r="C52" s="17"/>
-      <c r="D52" s="19"/>
-      <c r="E52" s="20"/>
-      <c r="F52" s="21"/>
-      <c r="G52" s="21"/>
-      <c r="H52" s="21"/>
-      <c r="I52" s="21"/>
+      <c r="B52" s="18"/>
+      <c r="C52" s="18"/>
+      <c r="D52" s="20"/>
+      <c r="E52" s="21"/>
+      <c r="F52" s="22"/>
+      <c r="G52" s="22"/>
+      <c r="H52" s="22"/>
+      <c r="I52" s="22"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E53" s="20"/>
-      <c r="F53" s="21"/>
-      <c r="G53" s="21"/>
-      <c r="H53" s="21"/>
-      <c r="I53" s="21"/>
+      <c r="E53" s="21"/>
+      <c r="F53" s="22"/>
+      <c r="G53" s="22"/>
+      <c r="H53" s="22"/>
+      <c r="I53" s="22"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E54" s="20"/>
-      <c r="F54" s="21"/>
-      <c r="G54" s="21"/>
-      <c r="H54" s="21"/>
-      <c r="I54" s="21"/>
+      <c r="E54" s="21"/>
+      <c r="F54" s="22"/>
+      <c r="G54" s="22"/>
+      <c r="H54" s="22"/>
+      <c r="I54" s="22"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E55" s="20"/>
-      <c r="F55" s="21"/>
-      <c r="G55" s="21"/>
-      <c r="H55" s="21"/>
-      <c r="I55" s="21"/>
+      <c r="E55" s="21"/>
+      <c r="F55" s="22"/>
+      <c r="G55" s="22"/>
+      <c r="H55" s="22"/>
+      <c r="I55" s="22"/>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E56" s="20"/>
-      <c r="F56" s="21"/>
-      <c r="G56" s="21"/>
-      <c r="H56" s="21"/>
-      <c r="I56" s="21"/>
+      <c r="E56" s="21"/>
+      <c r="F56" s="22"/>
+      <c r="G56" s="22"/>
+      <c r="H56" s="22"/>
+      <c r="I56" s="22"/>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E57" s="20"/>
-      <c r="F57" s="21"/>
-      <c r="G57" s="21"/>
-      <c r="H57" s="21"/>
-      <c r="I57" s="21"/>
+      <c r="E57" s="21"/>
+      <c r="F57" s="22"/>
+      <c r="G57" s="22"/>
+      <c r="H57" s="22"/>
+      <c r="I57" s="22"/>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E58" s="20"/>
-      <c r="F58" s="21"/>
-      <c r="G58" s="21"/>
-      <c r="H58" s="21"/>
-      <c r="I58" s="21"/>
+      <c r="E58" s="21"/>
+      <c r="F58" s="22"/>
+      <c r="G58" s="22"/>
+      <c r="H58" s="22"/>
+      <c r="I58" s="22"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D52" xr:uid="{05630F61-30FB-4CF7-B3FF-D0B93533C1C1}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="6월 누계"/>
-        <filter val="7월"/>
-        <filter val="7월 누계"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:D52" xr:uid="{05630F61-30FB-4CF7-B3FF-D0B93533C1C1}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Summary 작성용.xlsx
+++ b/Summary 작성용.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyju\Desktop\클로드_고정비\fc-dashboard-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66D795EB-6CF9-4175-9133-475156AD5231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9508D8E-A5D9-46CB-822B-CC23D98950FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-135" windowWidth="29040" windowHeight="15720" xr2:uid="{C29230AE-43B5-4988-AB7A-BDE8403DF9F7}"/>
   </bookViews>
@@ -488,15 +488,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[인건비]
-주식보상비용 250백만 (예산 외, 일회성)
-[지급수수료]
-합병 자문·평가 수수료 350백만(7월) (예산 외, 일회성)
- - KB증권 200백만, 이촌회계법인 150백만
-특허처리비 105백만 초과 집행 (VVC 예산 누락 영향)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">1Q 월평균 278백만 → 2Q 월평균 126백만 (4월 한화 임대차 계약 영향)
 10월 사옥 이전 전까지 아래 비용 구조로 예상
@@ -537,6 +528,15 @@
 7월 1.5억: 용인 0.8억(51%), 분당 0.8억(49%)
  - 용인 0.8억(총 0.9억): 감가상각비 0.4억(총 0.45억), 건물관리수수료 0.27억(총 0.32억), 수도광열비 0.05억(총 0.08억), 보험료 0.06억(총 0.06억)
  - 분당 0.8억(총 2.5억): 임차료 0.45억(총 1.44억), 수광비 0.01억(총 0.03억: 챔버, 카페), 건물관리수수료 0.01억(총 0.4억: 관리비 0.59억 - 실비수입 0.2억), 건물관리수수료(티맥스) 0.3억(총 0.58억)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[인건비]
+주식보상비용 250백만 집행 (예산 외, 일회성)
+[지급수수료]
+합병 자문·평가 수수료 350백만 7월 집행 (예산 외, 일회성)
+ - KB증권 200백만, 이촌회계법인 150백만
+특허처리비 105백만 초과 집행 (VVC 예산 누락 영향)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2900,7 +2900,7 @@
         <v>9</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E37" s="13" t="s">
         <v>67</v>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C43" s="14"/>
       <c r="D43" s="15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E43" s="13" t="s">
         <v>73</v>
@@ -3047,7 +3047,7 @@
         <v>8</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E46" s="13" t="s">
         <v>77</v>
@@ -3064,7 +3064,7 @@
         <v>9</v>
       </c>
       <c r="D47" s="23" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E47" s="13" t="s">
         <v>78</v>
@@ -3115,7 +3115,7 @@
         <v>9</v>
       </c>
       <c r="D50" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E50" s="13" t="s">
         <v>79</v>
